--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0040E796-7830-4915-A448-209174219C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686797D1-77D7-41FD-BDA1-4A8EA612E8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31515" yWindow="1710" windowWidth="15585" windowHeight="13545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="157">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -335,10 +335,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0 ~ 7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0xA6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -415,22 +411,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>선택 Bar 점등 (Data = 0 → 전체 Bar 점등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택 Bar 소등 (Data = 0 → 전체 Bar 소등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택 Block 점등 (Data= 0 → 전체 Block 점등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택 Block 소등 (Data= 0 → 전체 Block 소등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Data field의 바이트 수, "2. Command 목록" 참조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -618,6 +598,34 @@
   </si>
   <si>
     <t>Data = 0xA5 →수신 양호 / Data = 0x5A → 수신 불량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 ~ 160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 Bar 점등 (Data = 0 → 전체 Bar 점등), "xc xd mapping" 시트 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 Bar 소등 (Data = 0 → 전체 Bar 소등), "xc xd mapping" 시트 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 Block 점등 (Data= 0 → 전체 Block 점등), "xc xd mapping" 시트 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 Block 소등 (Data= 0 → 전체 Block 소등), "xc xd mapping" 시트 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLOCK #141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XD #2 - ch4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -696,7 +704,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -706,12 +714,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -914,7 +916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1006,15 +1008,18 @@
     <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1027,17 +1032,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1325,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L54"/>
+  <dimension ref="B2:M54"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" style="6" customWidth="1"/>
@@ -1341,14 +1337,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="B3" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -1400,14 +1396,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -1419,14 +1415,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -1438,14 +1434,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
+      <c r="E9" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -1457,14 +1453,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
+      <c r="E10" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -1476,14 +1472,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="36"/>
+      <c r="E11" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="37"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -1495,14 +1491,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -1514,18 +1510,18 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="37"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -1541,13 +1537,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="F17" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
@@ -1562,13 +1558,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
+      <c r="F18" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
@@ -1583,34 +1579,34 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="38" t="s">
+      <c r="F19" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="D20" s="31" t="s">
+      <c r="B20" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
+      <c r="E20" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -1625,13 +1621,13 @@
       <c r="E21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
+      <c r="F21" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
@@ -1646,13 +1642,13 @@
       <c r="E22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
+      <c r="F22" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -1667,13 +1663,13 @@
       <c r="E23" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
+      <c r="F23" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -1686,15 +1682,15 @@
         <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
+        <v>150</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -1707,15 +1703,15 @@
         <v>5</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
+        <v>150</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
@@ -1724,14 +1720,14 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="37" t="s">
+      <c r="C29" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
@@ -1760,7 +1756,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="33" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -1773,17 +1769,17 @@
         <v>11</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H31" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="33" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="41"/>
+        <v>80</v>
+      </c>
+      <c r="C32" s="33"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -1791,18 +1787,18 @@
         <v>14</v>
       </c>
       <c r="F32" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G32" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H32" s="41"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H32" s="33"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="41"/>
+      <c r="C33" s="33"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -1810,18 +1806,18 @@
         <v>14</v>
       </c>
       <c r="F33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G33" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H33" s="41"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H33" s="33"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="41"/>
+        <v>83</v>
+      </c>
+      <c r="C34" s="33"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -1832,15 +1828,15 @@
         <v>24</v>
       </c>
       <c r="G34" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="33"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H34" s="41"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="41"/>
+      <c r="C35" s="33"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -1851,15 +1847,15 @@
         <v>14</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H35" s="33"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H35" s="41"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B36" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="41"/>
+      <c r="C36" s="33"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -1867,18 +1863,18 @@
         <v>21</v>
       </c>
       <c r="F36" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="33"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B37" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G36" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H36" s="41"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B37" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="41"/>
+      <c r="C37" s="33"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -1886,18 +1882,18 @@
         <v>18</v>
       </c>
       <c r="F37" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G37" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H37" s="41"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H37" s="33"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="41"/>
+        <v>91</v>
+      </c>
+      <c r="C38" s="33"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -1908,15 +1904,15 @@
         <v>11</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H38" s="41"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+      <c r="H38" s="33"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="41"/>
+      <c r="C39" s="33"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -1929,9 +1925,9 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="41"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H39" s="33"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
       <c r="D40" s="12"/>
       <c r="E40" s="11"/>
@@ -1939,12 +1935,12 @@
       <c r="G40" s="11"/>
       <c r="H40" s="11"/>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
         <v>48</v>
       </c>
@@ -1953,17 +1949,18 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
         <v>25</v>
       </c>
@@ -1980,25 +1977,28 @@
         <v>50</v>
       </c>
       <c r="G44" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="L44" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="H44" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="I44" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="K44" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="L44" s="19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M44" s="19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="9" t="s">
         <v>26</v>
       </c>
@@ -2030,8 +2030,11 @@
       <c r="L45" s="24" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M45" s="24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="9" t="s">
         <v>27</v>
       </c>
@@ -2050,7 +2053,7 @@
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="9" t="s">
         <v>28</v>
       </c>
@@ -2069,7 +2072,7 @@
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B48" s="9" t="s">
         <v>29</v>
       </c>
@@ -2202,13 +2205,7 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="C31:C39"/>
-    <mergeCell ref="H31:H39"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="F43:L43"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
     <mergeCell ref="E13:J13"/>
@@ -2223,6 +2220,12 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="C31:C39"/>
+    <mergeCell ref="H31:H39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2239,56 +2242,56 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
+      <c r="B2" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="43"/>
-      <c r="D3" s="33"/>
+      <c r="B3" s="41"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C4" s="29" t="s">
         <v>46</v>
@@ -2330,7 +2333,7 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="25" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>46</v>
@@ -2372,7 +2375,7 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="25" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C6" s="29" t="s">
         <v>46</v>
@@ -2414,7 +2417,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C7" s="29" t="s">
         <v>46</v>
@@ -2456,7 +2459,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="25" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>46</v>
@@ -2498,13 +2501,13 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="25" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E9" s="26">
         <v>6</v>
@@ -2540,13 +2543,13 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="25" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E10" s="26">
         <v>7</v>
@@ -2582,13 +2585,13 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="25" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C11" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E11" s="26">
         <v>8</v>
@@ -2624,13 +2627,13 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="25" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E12" s="26">
         <v>9</v>
@@ -2666,13 +2669,13 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="25" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C13" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E13" s="26">
         <v>10</v>
@@ -2708,13 +2711,13 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="25" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E14" s="26">
         <v>11</v>
@@ -2750,13 +2753,13 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="25" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E15" s="26">
         <v>12</v>
@@ -2792,13 +2795,13 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E16" s="26">
         <v>13</v>
@@ -2834,13 +2837,13 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="25" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C17" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E17" s="26">
         <v>14</v>
@@ -2876,13 +2879,13 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="25" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E18" s="26">
         <v>15</v>
@@ -2918,13 +2921,13 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="25" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C19" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E19" s="26">
         <v>16</v>
@@ -2960,7 +2963,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="25" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C20" s="29" t="s">
         <v>46</v>
@@ -3002,7 +3005,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="25" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>46</v>
@@ -3044,7 +3047,7 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="25" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>46</v>
@@ -3086,7 +3089,7 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C23" s="29" t="s">
         <v>46</v>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686797D1-77D7-41FD-BDA1-4A8EA612E8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E86885-FCAC-4C14-A129-4C24C4439BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31515" yWindow="1710" windowWidth="15585" windowHeight="13545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -1008,32 +1008,32 @@
     <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1337,14 +1337,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -1396,14 +1396,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -1415,14 +1415,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -1434,14 +1434,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -1453,14 +1453,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -1472,14 +1472,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="37"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -1491,14 +1491,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -1510,14 +1510,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="37"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
@@ -1537,13 +1537,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
@@ -1558,13 +1558,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
@@ -1579,13 +1579,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
@@ -1600,13 +1600,13 @@
       <c r="E20" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -1621,13 +1621,13 @@
       <c r="E21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="32" t="s">
+      <c r="F21" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
@@ -1642,13 +1642,13 @@
       <c r="E22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="32" t="s">
+      <c r="F22" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -1663,13 +1663,13 @@
       <c r="E23" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -1684,13 +1684,13 @@
       <c r="E24" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -1705,13 +1705,13 @@
       <c r="E25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
@@ -1720,14 +1720,14 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
@@ -1756,7 +1756,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="39" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -1771,7 +1771,7 @@
       <c r="G31" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H31" s="33" t="s">
+      <c r="H31" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       <c r="B32" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="33"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -1792,13 +1792,13 @@
       <c r="G32" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H32" s="33"/>
+      <c r="H32" s="39"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="33"/>
+      <c r="C33" s="39"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -1811,13 +1811,13 @@
       <c r="G33" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H33" s="33"/>
+      <c r="H33" s="39"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="33"/>
+      <c r="C34" s="39"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -1830,13 +1830,13 @@
       <c r="G34" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H34" s="33"/>
+      <c r="H34" s="39"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="33"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -1849,13 +1849,13 @@
       <c r="G35" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="H35" s="33"/>
+      <c r="H35" s="39"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="33"/>
+      <c r="C36" s="39"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -1868,13 +1868,13 @@
       <c r="G36" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H36" s="33"/>
+      <c r="H36" s="39"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="33"/>
+      <c r="C37" s="39"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -1887,13 +1887,13 @@
       <c r="G37" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="33"/>
+      <c r="H37" s="39"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C38" s="33"/>
+      <c r="C38" s="39"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -1906,13 +1906,13 @@
       <c r="G38" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="H38" s="33"/>
+      <c r="H38" s="39"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="33"/>
+      <c r="C39" s="39"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -1925,7 +1925,7 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="33"/>
+      <c r="H39" s="39"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
@@ -1949,16 +1949,16 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="31" t="s">
+      <c r="F43" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="31"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
@@ -2205,6 +2205,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="C31:C39"/>
+    <mergeCell ref="H31:H39"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
@@ -2220,12 +2226,6 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="C31:C39"/>
-    <mergeCell ref="H31:H39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2245,25 +2245,25 @@
       <c r="B2" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31" t="s">
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="41"/>
-      <c r="D3" s="31"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="7" t="s">
         <v>141</v>
       </c>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E86885-FCAC-4C14-A129-4C24C4439BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAB1733-0EF5-4E42-B81F-2BAFC20C8DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
     <sheet name="xc xd mapping" sheetId="2" r:id="rId2"/>
+    <sheet name="B'D check list" sheetId="3" r:id="rId3"/>
+    <sheet name="B'D connector summary" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="204">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -295,10 +297,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>XC24, XD04 전원 차단</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Length</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -375,10 +373,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>XC24, XD04 전원 인가 및 IC 레지스터 설정, LED 전류는 0mA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0xB7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -411,10 +405,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Data field의 바이트 수, "2. Command 목록" 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>수행할 명령 코드, "2. Command 목록" 참조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -626,6 +616,202 @@
   </si>
   <si>
     <t>XD #2 - ch4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test 항목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check Point 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check Point 2</t>
+  </si>
+  <si>
+    <t>Check Point 3</t>
+  </si>
+  <si>
+    <t>Check Point 4</t>
+  </si>
+  <si>
+    <t>Check Point 5</t>
+  </si>
+  <si>
+    <t>Quit 커맨드 전송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test 빈도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP69 (1.5V)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test 조건 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test 조건 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test 조건 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test. 2 이후 연속 시행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN1 12V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP25 (780kHz Pulse 파형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP50 (UART 파형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Status 커맨드 수신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED Bar 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED Bar 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW3 1회 누른 후 TP67, TP68에 VLED 인가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP67, TP68에 VLED 차단 후 SW3 1회 누르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW4 1회 누르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW1 레버 방향 아래</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SW2 레버 방향 아래</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN1 12V, J5 LED Bar 장착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test No.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보드 전원 검사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스위치 레버 위치 체크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RS232 동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24 고장 판정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP1 (12V)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP2 (9V), D1 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP3 (5V)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP4 (3.3V)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP9 (5V), D6 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP9 (0V), D6 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP10 (5V), D7 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP10 (0V), D7 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP13 (5V)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP13 (0V)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 종료 후 CN1 전원 off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control B'D &lt;-&gt; Interface B'D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control B'D &lt;-&gt; RS232</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control B'D &lt;-&gt; LED Bar (Control B'D 고장 판정을 위해 LED Bar 커넥터 실장)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24, XD04 전원 차단, VLED Off 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24, XD04 전원 인가, 레지스터 설정, LED 전류 0mA, VLED On 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data field의 바이트 수, "2. Command 목록" 참조, 최소 length = 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -704,7 +890,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -717,8 +903,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -912,11 +1104,289 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1008,6 +1478,105 @@
     <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1040,12 +1609,35 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1056,6 +1648,158 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390962</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>57948</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AF428C8-FCB6-4E15-B3EF-9B259FCD7D93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="419100"/>
+          <a:ext cx="3134162" cy="5715798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>178547</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B27CE97E-6C31-89E0-E8EC-256F877AC945}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4800600" y="419101"/>
+          <a:ext cx="9791700" cy="3321796"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>533399</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152964</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39518E68-4EF3-42B3-83F0-FB8B658574EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14556441" y="425824"/>
+          <a:ext cx="2584076" cy="2069169"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1326,7 +2070,8 @@
   <cols>
     <col min="1" max="1" width="2.625" style="6" customWidth="1"/>
     <col min="2" max="2" width="17.75" style="6" customWidth="1"/>
-    <col min="3" max="12" width="11.125" style="6" customWidth="1"/>
+    <col min="3" max="10" width="13.625" style="6" customWidth="1"/>
+    <col min="11" max="12" width="11.125" style="6" customWidth="1"/>
     <col min="13" max="13" width="11.5" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="6"/>
   </cols>
@@ -1337,21 +2082,21 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
+      <c r="B3" s="64" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1</v>
@@ -1396,14 +2141,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -1415,18 +2160,18 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
@@ -1434,14 +2179,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="34"/>
+      <c r="E9" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -1453,14 +2198,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
+      <c r="E10" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -1472,14 +2217,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="34"/>
+      <c r="E11" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -1491,14 +2236,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -1510,18 +2255,18 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="34"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="67"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -1532,18 +2277,18 @@
         <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
@@ -1558,13 +2303,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
+      <c r="F18" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="75"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
@@ -1579,34 +2324,34 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
+      <c r="F19" s="75" t="s">
+        <v>201</v>
+      </c>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="75"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
+        <v>145</v>
+      </c>
+      <c r="F20" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -1619,15 +2364,15 @@
         <v>5</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
+        <v>73</v>
+      </c>
+      <c r="F21" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
@@ -1640,15 +2385,15 @@
         <v>5</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
+        <v>74</v>
+      </c>
+      <c r="F22" s="70" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -1661,15 +2406,15 @@
         <v>5</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
+        <v>74</v>
+      </c>
+      <c r="F23" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -1682,15 +2427,15 @@
         <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="70" t="s">
         <v>150</v>
       </c>
-      <c r="F24" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -1703,41 +2448,41 @@
         <v>5</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
+        <v>147</v>
+      </c>
+      <c r="F25" s="70" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
+      <c r="C29" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>1</v>
@@ -1746,7 +2491,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>4</v>
@@ -1756,7 +2501,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="72" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -1769,17 +2514,17 @@
         <v>11</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H31" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" s="72" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="39"/>
+        <v>79</v>
+      </c>
+      <c r="C32" s="72"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -1787,18 +2532,18 @@
         <v>14</v>
       </c>
       <c r="F32" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="G32" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H32" s="39"/>
+      <c r="H32" s="72"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="39"/>
+        <v>71</v>
+      </c>
+      <c r="C33" s="72"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -1806,18 +2551,18 @@
         <v>14</v>
       </c>
       <c r="F33" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G33" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H33" s="39"/>
+      <c r="H33" s="72"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="39"/>
+        <v>82</v>
+      </c>
+      <c r="C34" s="72"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -1828,15 +2573,15 @@
         <v>24</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="39"/>
+        <v>83</v>
+      </c>
+      <c r="H34" s="72"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="39"/>
+        <v>84</v>
+      </c>
+      <c r="C35" s="72"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -1847,15 +2592,15 @@
         <v>14</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H35" s="39"/>
+        <v>85</v>
+      </c>
+      <c r="H35" s="72"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="39"/>
+        <v>86</v>
+      </c>
+      <c r="C36" s="72"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -1863,18 +2608,18 @@
         <v>21</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H36" s="39"/>
+        <v>78</v>
+      </c>
+      <c r="H36" s="72"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="39"/>
+        <v>88</v>
+      </c>
+      <c r="C37" s="72"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -1882,18 +2627,18 @@
         <v>18</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H37" s="39"/>
+        <v>91</v>
+      </c>
+      <c r="H37" s="72"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="39"/>
+        <v>89</v>
+      </c>
+      <c r="C38" s="72"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -1904,15 +2649,15 @@
         <v>11</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H38" s="39"/>
+        <v>92</v>
+      </c>
+      <c r="H38" s="72"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="39"/>
+      <c r="C39" s="72"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -1925,7 +2670,7 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="39"/>
+      <c r="H39" s="72"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
@@ -1937,7 +2682,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.3">
@@ -1949,16 +2694,16 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="38" t="s">
+      <c r="F43" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
-      <c r="K43" s="38"/>
-      <c r="L43" s="38"/>
-      <c r="M43" s="38"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
+      <c r="K43" s="71"/>
+      <c r="L43" s="71"/>
+      <c r="M43" s="71"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
@@ -1977,25 +2722,25 @@
         <v>50</v>
       </c>
       <c r="G44" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="J44" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="H44" s="18" t="s">
+      <c r="K44" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="I44" s="17" t="s">
+      <c r="L44" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="J44" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="K44" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="L44" s="19" t="s">
-        <v>140</v>
-      </c>
       <c r="M44" s="19" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.3">
@@ -2031,7 +2776,7 @@
         <v>61</v>
       </c>
       <c r="M45" s="24" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.3">
@@ -2242,56 +2987,56 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="D2" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
+      <c r="B2" s="73" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="41"/>
-      <c r="D3" s="38"/>
+      <c r="B3" s="74"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="I3" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="30" t="s">
         <v>141</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="L3" s="30" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C4" s="29" t="s">
         <v>46</v>
@@ -2333,7 +3078,7 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="25" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>46</v>
@@ -2375,7 +3120,7 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C6" s="29" t="s">
         <v>46</v>
@@ -2417,7 +3162,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C7" s="29" t="s">
         <v>46</v>
@@ -2459,7 +3204,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>46</v>
@@ -2501,13 +3246,13 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="25" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E9" s="26">
         <v>6</v>
@@ -2543,13 +3288,13 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="25" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E10" s="26">
         <v>7</v>
@@ -2585,13 +3330,13 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="25" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C11" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E11" s="26">
         <v>8</v>
@@ -2627,13 +3372,13 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="25" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E12" s="26">
         <v>9</v>
@@ -2669,13 +3414,13 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C13" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E13" s="26">
         <v>10</v>
@@ -2711,13 +3456,13 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E14" s="26">
         <v>11</v>
@@ -2753,13 +3498,13 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E15" s="26">
         <v>12</v>
@@ -2795,13 +3540,13 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E16" s="26">
         <v>13</v>
@@ -2837,13 +3582,13 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="25" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C17" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E17" s="26">
         <v>14</v>
@@ -2879,13 +3624,13 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="25" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E18" s="26">
         <v>15</v>
@@ -2921,13 +3666,13 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="25" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C19" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E19" s="26">
         <v>16</v>
@@ -2963,7 +3708,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="25" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C20" s="29" t="s">
         <v>46</v>
@@ -3005,7 +3750,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="25" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>46</v>
@@ -3047,7 +3792,7 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>46</v>
@@ -3089,7 +3834,7 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="25" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C23" s="29" t="s">
         <v>46</v>
@@ -3140,4 +3885,271 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5776C9-E522-4127-B982-E334D5A025FE}">
+  <dimension ref="B1:L8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="8.375" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.75" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.875" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.375" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.75" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.125" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" style="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.875" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.25" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="31"/>
+    <col min="14" max="14" width="9.25" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="K2" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="L2" s="42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="61">
+        <v>1</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="48"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="58" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="62">
+        <v>2</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="51"/>
+      <c r="G4" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="K4" s="56"/>
+      <c r="L4" s="59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="62">
+        <v>3</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="K5" s="56"/>
+      <c r="L5" s="59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="62">
+        <v>4</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="51"/>
+      <c r="G6" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="62">
+        <v>5</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="32"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="K7" s="56"/>
+      <c r="L7" s="59" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="63">
+        <v>6</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C2:K3 B2:B8 C4:H5 J4:K5 C6:K7 D8:F8">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="(?)">
+      <formula>NOT(ISERROR(SEARCH("(?)",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1D2CDE-03D0-4073-94E8-BF70397D701B}">
+  <dimension ref="B2:W2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H2" t="s">
+        <v>199</v>
+      </c>
+      <c r="W2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAB1733-0EF5-4E42-B81F-2BAFC20C8DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C90E9D-C957-43C9-BD57-0CE83129B839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
     <sheet name="xc xd mapping" sheetId="2" r:id="rId2"/>
     <sheet name="B'D check list" sheetId="3" r:id="rId3"/>
     <sheet name="B'D connector summary" sheetId="5" r:id="rId4"/>
+    <sheet name="example" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="219">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -812,6 +813,66 @@
   </si>
   <si>
     <t>Data field의 바이트 수, "2. Command 목록" 참조, 최소 length = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>command</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>current</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전류 100mA 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전류 50mA 설정; Block/BAR 선택 전이므로 아직 off 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xc, xd 초기화 진행, 초기 전류 0mA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 Bar 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 Block 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>61번 Block 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 Bar 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>81번 Block 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 Block 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전류 0mA 설정 (Block On 이지만 전류 0mA라 소등)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -890,7 +951,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -909,8 +970,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="37">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1382,11 +1455,84 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1577,9 +1723,93 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1598,29 +1828,56 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1797,6 +2054,74 @@
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2019300</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="화살표: 오른쪽 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0194FCD-52A0-0E45-790D-6F8BFBE5B488}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2562225" y="1076325"/>
+          <a:ext cx="1733550" cy="714375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>좌측 커맨드 실행 결과</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2082,14 +2407,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="89" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -2141,14 +2466,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -2160,14 +2485,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -2179,14 +2504,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="78"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -2198,14 +2523,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="98" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="70"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -2217,14 +2542,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="67"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -2236,14 +2561,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="70" t="s">
+      <c r="E12" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="70"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -2255,14 +2580,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="65" t="s">
+      <c r="E13" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="67"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
@@ -2282,13 +2607,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="69" t="s">
+      <c r="F17" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="97"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
@@ -2303,13 +2628,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="75" t="s">
+      <c r="F18" s="99" t="s">
         <v>202</v>
       </c>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="75"/>
+      <c r="G18" s="99"/>
+      <c r="H18" s="99"/>
+      <c r="I18" s="99"/>
+      <c r="J18" s="99"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
@@ -2324,13 +2649,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="99" t="s">
         <v>201</v>
       </c>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="75"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
+      <c r="J19" s="99"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
@@ -2345,13 +2670,13 @@
       <c r="E20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F20" s="70" t="s">
+      <c r="F20" s="98" t="s">
         <v>146</v>
       </c>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="98"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -2366,13 +2691,13 @@
       <c r="E21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="70" t="s">
+      <c r="F21" s="98" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="98"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
@@ -2387,13 +2712,13 @@
       <c r="E22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="70" t="s">
+      <c r="F22" s="98" t="s">
         <v>148</v>
       </c>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="70"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="98"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -2408,13 +2733,13 @@
       <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="70" t="s">
+      <c r="F23" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="70"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="98"/>
+      <c r="I23" s="98"/>
+      <c r="J23" s="98"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -2429,13 +2754,13 @@
       <c r="E24" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F24" s="70" t="s">
+      <c r="F24" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="70"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="98"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -2450,13 +2775,13 @@
       <c r="E25" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F25" s="70" t="s">
+      <c r="F25" s="98" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="98"/>
+      <c r="I25" s="98"/>
+      <c r="J25" s="98"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
@@ -2465,14 +2790,14 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="96" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
@@ -2501,7 +2826,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="72" t="s">
+      <c r="C31" s="101" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -2516,7 +2841,7 @@
       <c r="G31" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="72" t="s">
+      <c r="H31" s="101" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2524,7 +2849,7 @@
       <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="72"/>
+      <c r="C32" s="101"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -2537,13 +2862,13 @@
       <c r="G32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="72"/>
+      <c r="H32" s="101"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="72"/>
+      <c r="C33" s="101"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -2556,13 +2881,13 @@
       <c r="G33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H33" s="72"/>
+      <c r="H33" s="101"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="72"/>
+      <c r="C34" s="101"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -2575,13 +2900,13 @@
       <c r="G34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="72"/>
+      <c r="H34" s="101"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="72"/>
+      <c r="C35" s="101"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -2594,13 +2919,13 @@
       <c r="G35" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="72"/>
+      <c r="H35" s="101"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="72"/>
+      <c r="C36" s="101"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -2613,13 +2938,13 @@
       <c r="G36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="72"/>
+      <c r="H36" s="101"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="72"/>
+      <c r="C37" s="101"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -2632,13 +2957,13 @@
       <c r="G37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="72"/>
+      <c r="H37" s="101"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="72"/>
+      <c r="C38" s="101"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -2651,13 +2976,13 @@
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="72"/>
+      <c r="H38" s="101"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="72"/>
+      <c r="C39" s="101"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -2670,7 +2995,7 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="72"/>
+      <c r="H39" s="101"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
@@ -2694,16 +3019,16 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="71" t="s">
+      <c r="F43" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="71"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
-      <c r="K43" s="71"/>
-      <c r="L43" s="71"/>
-      <c r="M43" s="71"/>
+      <c r="G43" s="100"/>
+      <c r="H43" s="100"/>
+      <c r="I43" s="100"/>
+      <c r="J43" s="100"/>
+      <c r="K43" s="100"/>
+      <c r="L43" s="100"/>
+      <c r="M43" s="100"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
@@ -2987,28 +3312,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="102" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="100" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71" t="s">
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="74"/>
-      <c r="D3" s="71"/>
+      <c r="B3" s="103"/>
+      <c r="D3" s="100"/>
       <c r="E3" s="7" t="s">
         <v>138</v>
       </c>
@@ -4152,4 +4477,510 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57173FD-D29F-465B-B16F-5A3BAEE50DB9}">
+  <dimension ref="B1:N14"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="5.25" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="4.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="107" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="110" t="s">
+        <v>206</v>
+      </c>
+      <c r="D2" s="112" t="s">
+        <v>207</v>
+      </c>
+      <c r="F2" s="107" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="104" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B3" s="108"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="113"/>
+      <c r="F3" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="M3" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="N3" s="105"/>
+    </row>
+    <row r="4" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="109"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="114"/>
+      <c r="F4" s="74">
+        <v>1</v>
+      </c>
+      <c r="G4" s="75">
+        <f t="shared" ref="G4:M4" si="0">F4+20</f>
+        <v>21</v>
+      </c>
+      <c r="H4" s="75">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="I4" s="75">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="J4" s="75">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="K4" s="75">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+      <c r="L4" s="75">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="M4" s="77">
+        <f t="shared" si="0"/>
+        <v>141</v>
+      </c>
+      <c r="N4" s="106"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="70">
+        <v>1</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="72">
+        <v>0</v>
+      </c>
+      <c r="F5" s="70">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0</v>
+      </c>
+      <c r="H5" s="22">
+        <v>0</v>
+      </c>
+      <c r="I5" s="22">
+        <v>0</v>
+      </c>
+      <c r="J5" s="22">
+        <v>0</v>
+      </c>
+      <c r="K5" s="22">
+        <v>0</v>
+      </c>
+      <c r="L5" s="22">
+        <v>0</v>
+      </c>
+      <c r="M5" s="21">
+        <v>0</v>
+      </c>
+      <c r="N5" s="80" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="65">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="66">
+        <v>50</v>
+      </c>
+      <c r="F6" s="65">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="78">
+        <v>0</v>
+      </c>
+      <c r="N6" s="81" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="65">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="66">
+        <v>1</v>
+      </c>
+      <c r="F7" s="83">
+        <v>50</v>
+      </c>
+      <c r="G7" s="84">
+        <v>50</v>
+      </c>
+      <c r="H7" s="84">
+        <v>50</v>
+      </c>
+      <c r="I7" s="84">
+        <v>50</v>
+      </c>
+      <c r="J7" s="84">
+        <v>50</v>
+      </c>
+      <c r="K7" s="84">
+        <v>50</v>
+      </c>
+      <c r="L7" s="84">
+        <v>50</v>
+      </c>
+      <c r="M7" s="85">
+        <v>50</v>
+      </c>
+      <c r="N7" s="81" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="65">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="66">
+        <v>1</v>
+      </c>
+      <c r="F8" s="65">
+        <v>0</v>
+      </c>
+      <c r="G8" s="84">
+        <v>50</v>
+      </c>
+      <c r="H8" s="84">
+        <v>50</v>
+      </c>
+      <c r="I8" s="84">
+        <v>50</v>
+      </c>
+      <c r="J8" s="84">
+        <v>50</v>
+      </c>
+      <c r="K8" s="84">
+        <v>50</v>
+      </c>
+      <c r="L8" s="84">
+        <v>50</v>
+      </c>
+      <c r="M8" s="85">
+        <v>50</v>
+      </c>
+      <c r="N8" s="81" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="65">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="66">
+        <v>61</v>
+      </c>
+      <c r="F9" s="65">
+        <v>0</v>
+      </c>
+      <c r="G9" s="84">
+        <v>50</v>
+      </c>
+      <c r="H9" s="84">
+        <v>50</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="84">
+        <v>50</v>
+      </c>
+      <c r="K9" s="84">
+        <v>50</v>
+      </c>
+      <c r="L9" s="84">
+        <v>50</v>
+      </c>
+      <c r="M9" s="85">
+        <v>50</v>
+      </c>
+      <c r="N9" s="81" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="65">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="66">
+        <v>0</v>
+      </c>
+      <c r="F10" s="65">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="78">
+        <v>0</v>
+      </c>
+      <c r="N10" s="81" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="65">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="66">
+        <v>81</v>
+      </c>
+      <c r="F11" s="65">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+      <c r="J11" s="84">
+        <v>50</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0</v>
+      </c>
+      <c r="M11" s="78">
+        <v>0</v>
+      </c>
+      <c r="N11" s="81" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="65">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D12" s="66">
+        <v>100</v>
+      </c>
+      <c r="F12" s="65">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="87">
+        <v>100</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="78">
+        <v>0</v>
+      </c>
+      <c r="N12" s="81" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="65">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="66">
+        <v>0</v>
+      </c>
+      <c r="F13" s="86">
+        <v>100</v>
+      </c>
+      <c r="G13" s="87">
+        <v>100</v>
+      </c>
+      <c r="H13" s="87">
+        <v>100</v>
+      </c>
+      <c r="I13" s="87">
+        <v>100</v>
+      </c>
+      <c r="J13" s="87">
+        <v>100</v>
+      </c>
+      <c r="K13" s="87">
+        <v>100</v>
+      </c>
+      <c r="L13" s="87">
+        <v>100</v>
+      </c>
+      <c r="M13" s="88">
+        <v>100</v>
+      </c>
+      <c r="N13" s="81" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="67">
+        <v>10</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" s="69">
+        <v>0</v>
+      </c>
+      <c r="F14" s="67">
+        <v>0</v>
+      </c>
+      <c r="G14" s="73">
+        <v>0</v>
+      </c>
+      <c r="H14" s="73">
+        <v>0</v>
+      </c>
+      <c r="I14" s="73">
+        <v>0</v>
+      </c>
+      <c r="J14" s="73">
+        <v>0</v>
+      </c>
+      <c r="K14" s="73">
+        <v>0</v>
+      </c>
+      <c r="L14" s="73">
+        <v>0</v>
+      </c>
+      <c r="M14" s="79">
+        <v>0</v>
+      </c>
+      <c r="N14" s="82" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="J2:M2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C90E9D-C957-43C9-BD57-0CE83129B839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1D9883-1953-4D30-8ED2-56EE3CD08920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="220">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -873,6 +873,10 @@
   </si>
   <si>
     <t>전류 0mA 설정 (Block On 이지만 전류 0mA라 소등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D11 점멸 후 점등</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1798,6 +1802,15 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1825,17 +1838,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2407,14 +2411,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="92" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -2466,14 +2470,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="97" t="s">
+      <c r="E7" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -2485,14 +2489,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="98" t="s">
+      <c r="E8" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -2504,14 +2508,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="90" t="s">
+      <c r="E9" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -2523,14 +2527,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="98" t="s">
+      <c r="E10" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="90"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -2542,14 +2546,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="93" t="s">
+      <c r="E11" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="95"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -2561,14 +2565,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="98" t="s">
+      <c r="E12" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="90"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -2580,14 +2584,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="93" t="s">
+      <c r="E13" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="95"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
@@ -2607,13 +2611,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="97" t="s">
+      <c r="F17" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="97"/>
-      <c r="H17" s="97"/>
-      <c r="I17" s="97"/>
-      <c r="J17" s="97"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
@@ -2628,13 +2632,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="99" t="s">
+      <c r="F18" s="101" t="s">
         <v>202</v>
       </c>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="99"/>
-      <c r="J18" s="99"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="101"/>
+      <c r="J18" s="101"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
@@ -2649,13 +2653,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="99" t="s">
+      <c r="F19" s="101" t="s">
         <v>201</v>
       </c>
-      <c r="G19" s="99"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="99"/>
-      <c r="J19" s="99"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="101"/>
+      <c r="I19" s="101"/>
+      <c r="J19" s="101"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
@@ -2670,13 +2674,13 @@
       <c r="E20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F20" s="98" t="s">
+      <c r="F20" s="90" t="s">
         <v>146</v>
       </c>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -2691,13 +2695,13 @@
       <c r="E21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="98" t="s">
+      <c r="F21" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
@@ -2712,13 +2716,13 @@
       <c r="E22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="98" t="s">
+      <c r="F22" s="90" t="s">
         <v>148</v>
       </c>
-      <c r="G22" s="98"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -2733,13 +2737,13 @@
       <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="98" t="s">
+      <c r="F23" s="90" t="s">
         <v>149</v>
       </c>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -2754,13 +2758,13 @@
       <c r="E24" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F24" s="98" t="s">
+      <c r="F24" s="90" t="s">
         <v>150</v>
       </c>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="98"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -2775,13 +2779,13 @@
       <c r="E25" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F25" s="98" t="s">
+      <c r="F25" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="98"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
@@ -2790,14 +2794,14 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="96" t="s">
+      <c r="C29" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="96"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="96"/>
-      <c r="G29" s="96"/>
-      <c r="H29" s="96"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="99"/>
+      <c r="H29" s="99"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
@@ -2826,7 +2830,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="101" t="s">
+      <c r="C31" s="91" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -2841,7 +2845,7 @@
       <c r="G31" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="101" t="s">
+      <c r="H31" s="91" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2849,7 +2853,7 @@
       <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="101"/>
+      <c r="C32" s="91"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -2862,13 +2866,13 @@
       <c r="G32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="101"/>
+      <c r="H32" s="91"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="101"/>
+      <c r="C33" s="91"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -2881,13 +2885,13 @@
       <c r="G33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H33" s="101"/>
+      <c r="H33" s="91"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="101"/>
+      <c r="C34" s="91"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -2900,13 +2904,13 @@
       <c r="G34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="101"/>
+      <c r="H34" s="91"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="101"/>
+      <c r="C35" s="91"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -2919,13 +2923,13 @@
       <c r="G35" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="101"/>
+      <c r="H35" s="91"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="101"/>
+      <c r="C36" s="91"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -2938,13 +2942,13 @@
       <c r="G36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="101"/>
+      <c r="H36" s="91"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="101"/>
+      <c r="C37" s="91"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -2957,13 +2961,13 @@
       <c r="G37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="101"/>
+      <c r="H37" s="91"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="101"/>
+      <c r="C38" s="91"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -2976,13 +2980,13 @@
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="101"/>
+      <c r="H38" s="91"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="101"/>
+      <c r="C39" s="91"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -2995,7 +2999,7 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="101"/>
+      <c r="H39" s="91"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
@@ -3019,16 +3023,16 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="100" t="s">
+      <c r="F43" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="100"/>
-      <c r="H43" s="100"/>
-      <c r="I43" s="100"/>
-      <c r="J43" s="100"/>
-      <c r="K43" s="100"/>
-      <c r="L43" s="100"/>
-      <c r="M43" s="100"/>
+      <c r="G43" s="89"/>
+      <c r="H43" s="89"/>
+      <c r="I43" s="89"/>
+      <c r="J43" s="89"/>
+      <c r="K43" s="89"/>
+      <c r="L43" s="89"/>
+      <c r="M43" s="89"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
@@ -3275,12 +3279,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="C31:C39"/>
-    <mergeCell ref="H31:H39"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
@@ -3296,6 +3294,12 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="C31:C39"/>
+    <mergeCell ref="H31:H39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3315,25 +3319,25 @@
       <c r="B2" s="102" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="D2" s="89" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="E2" s="89" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100" t="s">
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="103"/>
-      <c r="D3" s="100"/>
+      <c r="D3" s="89"/>
       <c r="E3" s="7" t="s">
         <v>138</v>
       </c>
@@ -4226,7 +4230,8 @@
     <col min="7" max="7" width="24.75" style="31" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.125" style="31" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.625" style="31" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.875" style="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.875" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="31" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="31"/>
     <col min="14" max="14" width="9.25" style="31" bestFit="1" customWidth="1"/>
@@ -4407,7 +4412,9 @@
       <c r="J7" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="K7" s="56"/>
+      <c r="K7" s="56" t="s">
+        <v>219</v>
+      </c>
       <c r="L7" s="59" t="s">
         <v>163</v>
       </c>
@@ -4525,7 +4532,7 @@
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="108"/>
-      <c r="C3" s="100"/>
+      <c r="C3" s="89"/>
       <c r="D3" s="113"/>
       <c r="F3" s="64" t="s">
         <v>138</v>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1D9883-1953-4D30-8ED2-56EE3CD08920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A8DA65-A755-4000-A4C0-C0335DE2264A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -572,10 +572,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Status</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -804,14 +800,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>XC24, XD04 전원 차단, VLED Off 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC24, XD04 전원 인가, 레지스터 설정, LED 전류 0mA, VLED On 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Data field의 바이트 수, "2. Command 목록" 참조, 최소 length = 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -877,6 +865,18 @@
   </si>
   <si>
     <t>D11 점멸 후 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24, XD04 전원 인가, 레지스터 설정, LED 전류 0mA, VLED On 필요, 다음 명령어까지 50ms delay 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24, XD04 전원 차단, VLED Off 필요, 다음 명령어까지 50ms delay 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 1ms delay 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1802,45 +1802,42 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1882,6 +1879,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2399,10 +2399,9 @@
   <cols>
     <col min="1" max="1" width="2.625" style="6" customWidth="1"/>
     <col min="2" max="2" width="17.75" style="6" customWidth="1"/>
-    <col min="3" max="10" width="13.625" style="6" customWidth="1"/>
-    <col min="11" max="12" width="11.125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="11.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="6"/>
+    <col min="3" max="10" width="17.625" style="6" customWidth="1"/>
+    <col min="11" max="16" width="9" style="6" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
@@ -2411,14 +2410,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="92" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
+      <c r="B3" s="115" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -2470,14 +2469,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="100" t="s">
+      <c r="E7" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -2489,14 +2488,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="90" t="s">
+      <c r="E8" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -2508,14 +2507,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="93" t="s">
-        <v>203</v>
-      </c>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="95"/>
+      <c r="E9" s="89" t="s">
+        <v>200</v>
+      </c>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="91"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -2527,14 +2526,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="90" t="s">
+      <c r="E10" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="90"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -2546,14 +2545,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="E11" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="98"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -2565,14 +2564,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="90" t="s">
+      <c r="E12" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="90"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -2584,14 +2583,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="96" t="s">
+      <c r="E13" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
-      <c r="H13" s="97"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="98"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="94"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
@@ -2611,13 +2610,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="100" t="s">
+      <c r="F17" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
@@ -2632,13 +2631,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="101" t="s">
-        <v>202</v>
-      </c>
-      <c r="G18" s="101"/>
-      <c r="H18" s="101"/>
-      <c r="I18" s="101"/>
-      <c r="J18" s="101"/>
+      <c r="F18" s="98" t="s">
+        <v>217</v>
+      </c>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="98"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
@@ -2653,34 +2652,34 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="101" t="s">
-        <v>201</v>
-      </c>
-      <c r="G19" s="101"/>
-      <c r="H19" s="101"/>
-      <c r="I19" s="101"/>
-      <c r="J19" s="101"/>
+      <c r="F19" s="98" t="s">
+        <v>218</v>
+      </c>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="98"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" s="97" t="s">
         <v>145</v>
       </c>
-      <c r="F20" s="90" t="s">
-        <v>146</v>
-      </c>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="97"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -2695,13 +2694,13 @@
       <c r="E21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="90" t="s">
+      <c r="F21" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="90"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="90"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="97"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
@@ -2716,13 +2715,13 @@
       <c r="E22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="90" t="s">
-        <v>148</v>
-      </c>
-      <c r="G22" s="90"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="90"/>
-      <c r="J22" s="90"/>
+      <c r="F22" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="97"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="97"/>
+      <c r="J22" s="97"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -2737,13 +2736,13 @@
       <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="90" t="s">
-        <v>149</v>
-      </c>
-      <c r="G23" s="90"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="90"/>
+      <c r="F23" s="97" t="s">
+        <v>148</v>
+      </c>
+      <c r="G23" s="97"/>
+      <c r="H23" s="97"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="97"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -2756,15 +2755,15 @@
         <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F24" s="90" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="90"/>
+        <v>146</v>
+      </c>
+      <c r="F24" s="97" t="s">
+        <v>149</v>
+      </c>
+      <c r="G24" s="97"/>
+      <c r="H24" s="97"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="97"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -2777,15 +2776,15 @@
         <v>5</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F25" s="90" t="s">
-        <v>151</v>
-      </c>
-      <c r="G25" s="90"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="90"/>
+        <v>146</v>
+      </c>
+      <c r="F25" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="97"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="97"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
@@ -2794,14 +2793,14 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="99" t="s">
+      <c r="C29" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="99"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="99"/>
-      <c r="G29" s="99"/>
-      <c r="H29" s="99"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="95"/>
+      <c r="H29" s="95"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
@@ -2830,7 +2829,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="91" t="s">
+      <c r="C31" s="100" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -2845,7 +2844,7 @@
       <c r="G31" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="91" t="s">
+      <c r="H31" s="100" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2853,7 +2852,7 @@
       <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="91"/>
+      <c r="C32" s="100"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -2866,13 +2865,13 @@
       <c r="G32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="91"/>
+      <c r="H32" s="100"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="91"/>
+      <c r="C33" s="100"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -2885,13 +2884,13 @@
       <c r="G33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H33" s="91"/>
+      <c r="H33" s="100"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="91"/>
+      <c r="C34" s="100"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -2904,13 +2903,13 @@
       <c r="G34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="91"/>
+      <c r="H34" s="100"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="91"/>
+      <c r="C35" s="100"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -2923,13 +2922,13 @@
       <c r="G35" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="91"/>
+      <c r="H35" s="100"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="91"/>
+      <c r="C36" s="100"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -2942,13 +2941,13 @@
       <c r="G36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="91"/>
+      <c r="H36" s="100"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="91"/>
+      <c r="C37" s="100"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -2961,13 +2960,13 @@
       <c r="G37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="91"/>
+      <c r="H37" s="100"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="91"/>
+      <c r="C38" s="100"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -2980,13 +2979,13 @@
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="91"/>
+      <c r="H38" s="100"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="91"/>
+      <c r="C39" s="100"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -2999,7 +2998,7 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="91"/>
+      <c r="H39" s="100"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
@@ -3023,16 +3022,16 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="89" t="s">
+      <c r="F43" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="89"/>
-      <c r="H43" s="89"/>
-      <c r="I43" s="89"/>
-      <c r="J43" s="89"/>
-      <c r="K43" s="89"/>
-      <c r="L43" s="89"/>
-      <c r="M43" s="89"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
@@ -3069,7 +3068,7 @@
         <v>137</v>
       </c>
       <c r="M44" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.3">
@@ -3105,7 +3104,7 @@
         <v>61</v>
       </c>
       <c r="M45" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.3">
@@ -3279,6 +3278,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="C31:C39"/>
+    <mergeCell ref="H31:H39"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
@@ -3294,12 +3299,6 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="C31:C39"/>
-    <mergeCell ref="H31:H39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3316,28 +3315,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="101" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="99" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="89" t="s">
+      <c r="E2" s="99" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89" t="s">
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="103"/>
-      <c r="D3" s="89"/>
+      <c r="B3" s="102"/>
+      <c r="D3" s="99"/>
       <c r="E3" s="7" t="s">
         <v>138</v>
       </c>
@@ -4241,37 +4240,37 @@
     <row r="1" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C2" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="G2" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="D2" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="F2" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="G2" s="47" t="s">
+      <c r="H2" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="I2" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="J2" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="K2" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="K2" s="54" t="s">
-        <v>159</v>
-      </c>
       <c r="L2" s="42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
@@ -4279,22 +4278,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D3" s="48"/>
       <c r="E3" s="34"/>
       <c r="F3" s="49"/>
       <c r="G3" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" s="34" t="s">
         <v>178</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>179</v>
       </c>
       <c r="I3" s="34"/>
       <c r="J3" s="34"/>
       <c r="K3" s="55"/>
       <c r="L3" s="58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
@@ -4302,30 +4301,30 @@
         <v>2</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F4" s="51"/>
       <c r="G4" s="40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K4" s="56"/>
       <c r="L4" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
@@ -4333,32 +4332,32 @@
         <v>3</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K5" s="56"/>
       <c r="L5" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -4366,26 +4365,26 @@
         <v>4</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F6" s="51"/>
       <c r="G6" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="32" t="s">
         <v>171</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>172</v>
       </c>
       <c r="I6" s="32"/>
       <c r="J6" s="32"/>
       <c r="K6" s="56"/>
       <c r="L6" s="59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
@@ -4393,30 +4392,30 @@
         <v>5</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E7" s="32"/>
       <c r="F7" s="51"/>
       <c r="G7" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="H7" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="I7" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="I7" s="32" t="s">
+      <c r="J7" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="J7" s="32" t="s">
-        <v>189</v>
-      </c>
       <c r="K7" s="56" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L7" s="59" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4424,28 +4423,28 @@
         <v>6</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D8" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="G8" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="E8" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="G8" s="41" t="s">
-        <v>170</v>
-      </c>
       <c r="H8" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I8" s="33"/>
       <c r="J8" s="33"/>
       <c r="K8" s="57"/>
       <c r="L8" s="60" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4470,13 +4469,13 @@
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H2" t="s">
         <v>198</v>
       </c>
-      <c r="H2" t="s">
+      <c r="W2" t="s">
         <v>199</v>
-      </c>
-      <c r="W2" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4505,35 +4504,35 @@
   <sheetData>
     <row r="1" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="106" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="109" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="111" t="s">
         <v>204</v>
       </c>
-      <c r="C2" s="110" t="s">
-        <v>206</v>
-      </c>
-      <c r="D2" s="112" t="s">
-        <v>207</v>
-      </c>
-      <c r="F2" s="107" t="s">
+      <c r="F2" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110" t="s">
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="104" t="s">
-        <v>205</v>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="103" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="108"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="113"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="112"/>
       <c r="F3" s="64" t="s">
         <v>138</v>
       </c>
@@ -4558,12 +4557,12 @@
       <c r="M3" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="N3" s="105"/>
+      <c r="N3" s="104"/>
     </row>
     <row r="4" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="109"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="114"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="113"/>
       <c r="F4" s="74">
         <v>1</v>
       </c>
@@ -4595,7 +4594,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N4" s="106"/>
+      <c r="N4" s="105"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="70">
@@ -4632,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="80" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
@@ -4640,7 +4639,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D6" s="66">
         <v>50</v>
@@ -4670,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="81" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
@@ -4708,7 +4707,7 @@
         <v>50</v>
       </c>
       <c r="N7" s="81" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
@@ -4746,7 +4745,7 @@
         <v>50</v>
       </c>
       <c r="N8" s="81" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
@@ -4784,7 +4783,7 @@
         <v>50</v>
       </c>
       <c r="N9" s="81" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
@@ -4822,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="81" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
@@ -4860,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="81" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
@@ -4868,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D12" s="66">
         <v>100</v>
@@ -4898,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="81" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
@@ -4936,7 +4935,7 @@
         <v>100</v>
       </c>
       <c r="N13" s="81" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4944,7 +4943,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D14" s="69">
         <v>0</v>
@@ -4974,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="82" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A8DA65-A755-4000-A4C0-C0335DE2264A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D94B1B4-5E19-4B7E-B339-5098F81A2FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="234">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -877,6 +877,62 @@
   </si>
   <si>
     <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 1ms delay 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Example with LED Bar No. 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Example with LED Bar No. 12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전류 25mA 설정; Block/BAR 선택 전이므로 아직 off 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12번 Bar 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12번 Block 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>52번 Block 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>92번 Block 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12번 Bar 소등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>132번 Block 소등 (현재 단계에서 ABAB 패턴 구현)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전류 75mA 설정; 선택된 Block/BAR가 없으므로 off 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12번 Block 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>52번 Block 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>92번 Block 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>132번 Block 점등 (현재 단계에서 BABA 패턴 구현)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -955,7 +1011,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -986,8 +1042,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="42">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1532,11 +1594,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1802,6 +1927,54 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1859,29 +2032,32 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2069,13 +2245,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>2019300</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2084,6 +2260,69 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0194FCD-52A0-0E45-790D-6F8BFBE5B488}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2562225" y="1076325"/>
+          <a:ext cx="1733550" cy="714375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>좌측 커맨드 실행 결과</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2019300</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="화살표: 오른쪽 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{978CF594-026D-4309-883A-8D78CAABE886}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2410,14 +2649,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="115" t="s">
+      <c r="B3" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -2469,14 +2708,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="E7" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -2488,14 +2727,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="97" t="s">
+      <c r="E8" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="97"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="97"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -2507,14 +2746,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="89" t="s">
+      <c r="E9" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="91"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="107"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -2526,14 +2765,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="97" t="s">
+      <c r="E10" s="113" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97"/>
-      <c r="H10" s="97"/>
-      <c r="I10" s="97"/>
-      <c r="J10" s="97"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -2545,14 +2784,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="92" t="s">
+      <c r="E11" s="108" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="94"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="110"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -2564,14 +2803,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="97" t="s">
+      <c r="E12" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="97"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="97"/>
-      <c r="I12" s="97"/>
-      <c r="J12" s="97"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="113"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -2583,14 +2822,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="92" t="s">
+      <c r="E13" s="108" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="94"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="110"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
@@ -2610,13 +2849,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="96" t="s">
+      <c r="F17" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
@@ -2631,13 +2870,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="98" t="s">
+      <c r="F18" s="114" t="s">
         <v>217</v>
       </c>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
@@ -2652,13 +2891,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="98" t="s">
+      <c r="F19" s="114" t="s">
         <v>218</v>
       </c>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="114"/>
+      <c r="I19" s="114"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
@@ -2673,13 +2912,13 @@
       <c r="E20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F20" s="97" t="s">
+      <c r="F20" s="113" t="s">
         <v>145</v>
       </c>
-      <c r="G20" s="97"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="97"/>
-      <c r="J20" s="97"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="113"/>
+      <c r="J20" s="113"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -2694,13 +2933,13 @@
       <c r="E21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="97" t="s">
+      <c r="F21" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="97"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="97"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
@@ -2715,13 +2954,13 @@
       <c r="E22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="97" t="s">
+      <c r="F22" s="113" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="97"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="97"/>
-      <c r="J22" s="97"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="113"/>
+      <c r="J22" s="113"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -2736,13 +2975,13 @@
       <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="97" t="s">
+      <c r="F23" s="113" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="97"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="113"/>
+      <c r="J23" s="113"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -2757,13 +2996,13 @@
       <c r="E24" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="97" t="s">
+      <c r="F24" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="G24" s="97"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="97"/>
+      <c r="G24" s="113"/>
+      <c r="H24" s="113"/>
+      <c r="I24" s="113"/>
+      <c r="J24" s="113"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -2778,13 +3017,13 @@
       <c r="E25" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="97" t="s">
+      <c r="F25" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="97"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="113"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
@@ -2793,14 +3032,14 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="95"/>
-      <c r="E29" s="95"/>
-      <c r="F29" s="95"/>
-      <c r="G29" s="95"/>
-      <c r="H29" s="95"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="111"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
@@ -2829,7 +3068,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="100" t="s">
+      <c r="C31" s="116" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -2844,7 +3083,7 @@
       <c r="G31" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="100" t="s">
+      <c r="H31" s="116" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2852,7 +3091,7 @@
       <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="100"/>
+      <c r="C32" s="116"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -2865,13 +3104,13 @@
       <c r="G32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="100"/>
+      <c r="H32" s="116"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="100"/>
+      <c r="C33" s="116"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -2884,13 +3123,13 @@
       <c r="G33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H33" s="100"/>
+      <c r="H33" s="116"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="100"/>
+      <c r="C34" s="116"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -2903,13 +3142,13 @@
       <c r="G34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="100"/>
+      <c r="H34" s="116"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="100"/>
+      <c r="C35" s="116"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -2922,13 +3161,13 @@
       <c r="G35" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="100"/>
+      <c r="H35" s="116"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="100"/>
+      <c r="C36" s="116"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -2941,13 +3180,13 @@
       <c r="G36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="100"/>
+      <c r="H36" s="116"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="100"/>
+      <c r="C37" s="116"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -2960,13 +3199,13 @@
       <c r="G37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="100"/>
+      <c r="H37" s="116"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="100"/>
+      <c r="C38" s="116"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -2979,13 +3218,13 @@
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="100"/>
+      <c r="H38" s="116"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="100"/>
+      <c r="C39" s="116"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -2998,7 +3237,7 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="100"/>
+      <c r="H39" s="116"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
@@ -3022,16 +3261,16 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="99" t="s">
+      <c r="F43" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
+      <c r="G43" s="115"/>
+      <c r="H43" s="115"/>
+      <c r="I43" s="115"/>
+      <c r="J43" s="115"/>
+      <c r="K43" s="115"/>
+      <c r="L43" s="115"/>
+      <c r="M43" s="115"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
@@ -3315,28 +3554,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="99" t="s">
+      <c r="D2" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="99" t="s">
+      <c r="E2" s="115" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99" t="s">
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="102"/>
-      <c r="D3" s="99"/>
+      <c r="B3" s="118"/>
+      <c r="D3" s="115"/>
       <c r="E3" s="7" t="s">
         <v>138</v>
       </c>
@@ -4487,7 +4726,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57173FD-D29F-465B-B16F-5A3BAEE50DB9}">
-  <dimension ref="B1:N14"/>
+  <dimension ref="B2:N34"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" style="11" customWidth="1"/>
@@ -4495,233 +4734,197 @@
     <col min="3" max="3" width="13.625" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.875" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="5.25" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.875" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.125" style="11" customWidth="1"/>
     <col min="14" max="14" width="54.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="106" t="s">
+    <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="122" t="s">
         <v>201</v>
       </c>
-      <c r="C2" s="109" t="s">
+      <c r="C3" s="125" t="s">
         <v>203</v>
       </c>
-      <c r="D2" s="111" t="s">
+      <c r="D3" s="126" t="s">
         <v>204</v>
       </c>
-      <c r="F2" s="106" t="s">
+      <c r="F3" s="122" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109" t="s">
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125" t="s">
         <v>97</v>
       </c>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="103" t="s">
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="119" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="107"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="112"/>
-      <c r="F3" s="64" t="s">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="123"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="127"/>
+      <c r="F4" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="M3" s="76" t="s">
+      <c r="M4" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="N3" s="104"/>
-    </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="108"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="113"/>
-      <c r="F4" s="74">
+      <c r="N4" s="120"/>
+    </row>
+    <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="130"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="132"/>
+      <c r="F5" s="74">
         <v>1</v>
       </c>
-      <c r="G4" s="75">
-        <f t="shared" ref="G4:M4" si="0">F4+20</f>
+      <c r="G5" s="75">
+        <f t="shared" ref="G5:M5" si="0">F5+20</f>
         <v>21</v>
       </c>
-      <c r="H4" s="75">
+      <c r="H5" s="75">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="I4" s="75">
+      <c r="I5" s="75">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="J4" s="75">
+      <c r="J5" s="75">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="K4" s="75">
+      <c r="K5" s="75">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="L4" s="75">
+      <c r="L5" s="75">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="M4" s="77">
+      <c r="M5" s="77">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N4" s="105"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="70">
+      <c r="N5" s="121"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="70">
         <v>1</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C6" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="72">
-        <v>0</v>
-      </c>
-      <c r="F5" s="70">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0</v>
-      </c>
-      <c r="H5" s="22">
-        <v>0</v>
-      </c>
-      <c r="I5" s="22">
-        <v>0</v>
-      </c>
-      <c r="J5" s="22">
-        <v>0</v>
-      </c>
-      <c r="K5" s="22">
-        <v>0</v>
-      </c>
-      <c r="L5" s="22">
-        <v>0</v>
-      </c>
-      <c r="M5" s="21">
-        <v>0</v>
-      </c>
-      <c r="N5" s="80" t="s">
+      <c r="D6" s="72">
+        <v>0</v>
+      </c>
+      <c r="F6" s="70">
+        <v>0</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0</v>
+      </c>
+      <c r="H6" s="22">
+        <v>0</v>
+      </c>
+      <c r="I6" s="22">
+        <v>0</v>
+      </c>
+      <c r="J6" s="22">
+        <v>0</v>
+      </c>
+      <c r="K6" s="22">
+        <v>0</v>
+      </c>
+      <c r="L6" s="22">
+        <v>0</v>
+      </c>
+      <c r="M6" s="21">
+        <v>0</v>
+      </c>
+      <c r="N6" s="80" t="s">
         <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="65">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D6" s="66">
-        <v>50</v>
-      </c>
-      <c r="F6" s="65">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9">
-        <v>0</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0</v>
-      </c>
-      <c r="M6" s="78">
-        <v>0</v>
-      </c>
-      <c r="N6" s="81" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="D7" s="66">
-        <v>1</v>
-      </c>
-      <c r="F7" s="83">
         <v>50</v>
       </c>
-      <c r="G7" s="84">
-        <v>50</v>
-      </c>
-      <c r="H7" s="84">
-        <v>50</v>
-      </c>
-      <c r="I7" s="84">
-        <v>50</v>
-      </c>
-      <c r="J7" s="84">
-        <v>50</v>
-      </c>
-      <c r="K7" s="84">
-        <v>50</v>
-      </c>
-      <c r="L7" s="84">
-        <v>50</v>
-      </c>
-      <c r="M7" s="85">
-        <v>50</v>
+      <c r="F7" s="65">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9">
+        <v>0</v>
+      </c>
+      <c r="M7" s="78">
+        <v>0</v>
       </c>
       <c r="N7" s="81" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" s="66">
         <v>1</v>
       </c>
-      <c r="F8" s="65">
-        <v>0</v>
+      <c r="F8" s="83">
+        <v>50</v>
       </c>
       <c r="G8" s="84">
         <v>50</v>
@@ -4745,18 +4948,18 @@
         <v>50</v>
       </c>
       <c r="N8" s="81" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="66">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F9" s="65">
         <v>0</v>
@@ -4767,8 +4970,8 @@
       <c r="H9" s="84">
         <v>50</v>
       </c>
-      <c r="I9" s="9">
-        <v>0</v>
+      <c r="I9" s="84">
+        <v>50</v>
       </c>
       <c r="J9" s="84">
         <v>50</v>
@@ -4783,56 +4986,56 @@
         <v>50</v>
       </c>
       <c r="N9" s="81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D10" s="66">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F10" s="65">
         <v>0</v>
       </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
+      <c r="G10" s="84">
+        <v>50</v>
+      </c>
+      <c r="H10" s="84">
+        <v>50</v>
       </c>
       <c r="I10" s="9">
         <v>0</v>
       </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="78">
-        <v>0</v>
+      <c r="J10" s="84">
+        <v>50</v>
+      </c>
+      <c r="K10" s="84">
+        <v>50</v>
+      </c>
+      <c r="L10" s="84">
+        <v>50</v>
+      </c>
+      <c r="M10" s="85">
+        <v>50</v>
       </c>
       <c r="N10" s="81" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" s="66">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F11" s="65">
         <v>0</v>
@@ -4846,8 +5049,8 @@
       <c r="I11" s="9">
         <v>0</v>
       </c>
-      <c r="J11" s="84">
-        <v>50</v>
+      <c r="J11" s="9">
+        <v>0</v>
       </c>
       <c r="K11" s="9">
         <v>0</v>
@@ -4859,18 +5062,18 @@
         <v>0</v>
       </c>
       <c r="N11" s="81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="65">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>205</v>
+        <v>22</v>
       </c>
       <c r="D12" s="66">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="F12" s="65">
         <v>0</v>
@@ -4884,8 +5087,8 @@
       <c r="I12" s="9">
         <v>0</v>
       </c>
-      <c r="J12" s="87">
-        <v>100</v>
+      <c r="J12" s="84">
+        <v>50</v>
       </c>
       <c r="K12" s="9">
         <v>0</v>
@@ -4897,93 +5100,729 @@
         <v>0</v>
       </c>
       <c r="N12" s="81" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="65">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="D13" s="66">
-        <v>0</v>
-      </c>
-      <c r="F13" s="86">
         <v>100</v>
       </c>
-      <c r="G13" s="87">
-        <v>100</v>
-      </c>
-      <c r="H13" s="87">
-        <v>100</v>
-      </c>
-      <c r="I13" s="87">
-        <v>100</v>
+      <c r="F13" s="65">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
       </c>
       <c r="J13" s="87">
         <v>100</v>
       </c>
-      <c r="K13" s="87">
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="78">
+        <v>0</v>
+      </c>
+      <c r="N13" s="81" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14" s="65">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="66">
+        <v>0</v>
+      </c>
+      <c r="F14" s="86">
         <v>100</v>
       </c>
-      <c r="L13" s="87">
+      <c r="G14" s="87">
         <v>100</v>
       </c>
-      <c r="M13" s="88">
+      <c r="H14" s="87">
         <v>100</v>
       </c>
-      <c r="N13" s="81" t="s">
+      <c r="I14" s="87">
+        <v>100</v>
+      </c>
+      <c r="J14" s="87">
+        <v>100</v>
+      </c>
+      <c r="K14" s="87">
+        <v>100</v>
+      </c>
+      <c r="L14" s="87">
+        <v>100</v>
+      </c>
+      <c r="M14" s="88">
+        <v>100</v>
+      </c>
+      <c r="N14" s="81" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="67">
+    <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="67">
         <v>10</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C15" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="D14" s="69">
-        <v>0</v>
-      </c>
-      <c r="F14" s="67">
-        <v>0</v>
-      </c>
-      <c r="G14" s="73">
-        <v>0</v>
-      </c>
-      <c r="H14" s="73">
-        <v>0</v>
-      </c>
-      <c r="I14" s="73">
-        <v>0</v>
-      </c>
-      <c r="J14" s="73">
-        <v>0</v>
-      </c>
-      <c r="K14" s="73">
-        <v>0</v>
-      </c>
-      <c r="L14" s="73">
-        <v>0</v>
-      </c>
-      <c r="M14" s="79">
-        <v>0</v>
-      </c>
-      <c r="N14" s="82" t="s">
+      <c r="D15" s="69">
+        <v>0</v>
+      </c>
+      <c r="F15" s="67">
+        <v>0</v>
+      </c>
+      <c r="G15" s="73">
+        <v>0</v>
+      </c>
+      <c r="H15" s="73">
+        <v>0</v>
+      </c>
+      <c r="I15" s="73">
+        <v>0</v>
+      </c>
+      <c r="J15" s="73">
+        <v>0</v>
+      </c>
+      <c r="K15" s="73">
+        <v>0</v>
+      </c>
+      <c r="L15" s="73">
+        <v>0</v>
+      </c>
+      <c r="M15" s="79">
+        <v>0</v>
+      </c>
+      <c r="N15" s="82" t="s">
         <v>215</v>
       </c>
     </row>
+    <row r="18" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="122" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" s="125" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="126" t="s">
+        <v>204</v>
+      </c>
+      <c r="F19" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="125" t="s">
+        <v>97</v>
+      </c>
+      <c r="K19" s="125"/>
+      <c r="L19" s="125"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="119" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="123"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="127"/>
+      <c r="F20" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="M20" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="N20" s="120"/>
+    </row>
+    <row r="21" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="124"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="128"/>
+      <c r="F21" s="94">
+        <v>12</v>
+      </c>
+      <c r="G21" s="95">
+        <f t="shared" ref="G21" si="1">F21+20</f>
+        <v>32</v>
+      </c>
+      <c r="H21" s="95">
+        <f t="shared" ref="H21" si="2">G21+20</f>
+        <v>52</v>
+      </c>
+      <c r="I21" s="95">
+        <f t="shared" ref="I21" si="3">H21+20</f>
+        <v>72</v>
+      </c>
+      <c r="J21" s="95">
+        <f t="shared" ref="J21" si="4">I21+20</f>
+        <v>92</v>
+      </c>
+      <c r="K21" s="95">
+        <f t="shared" ref="K21" si="5">J21+20</f>
+        <v>112</v>
+      </c>
+      <c r="L21" s="95">
+        <f t="shared" ref="L21" si="6">K21+20</f>
+        <v>132</v>
+      </c>
+      <c r="M21" s="96">
+        <f t="shared" ref="M21" si="7">L21+20</f>
+        <v>152</v>
+      </c>
+      <c r="N21" s="121"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="89">
+        <v>1</v>
+      </c>
+      <c r="C22" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="91">
+        <v>0</v>
+      </c>
+      <c r="F22" s="89">
+        <v>0</v>
+      </c>
+      <c r="G22" s="98">
+        <v>0</v>
+      </c>
+      <c r="H22" s="98">
+        <v>0</v>
+      </c>
+      <c r="I22" s="98">
+        <v>0</v>
+      </c>
+      <c r="J22" s="98">
+        <v>0</v>
+      </c>
+      <c r="K22" s="98">
+        <v>0</v>
+      </c>
+      <c r="L22" s="98">
+        <v>0</v>
+      </c>
+      <c r="M22" s="91">
+        <v>0</v>
+      </c>
+      <c r="N22" s="92" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="65">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23" s="66">
+        <v>25</v>
+      </c>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9">
+        <v>0</v>
+      </c>
+      <c r="M23" s="66">
+        <v>0</v>
+      </c>
+      <c r="N23" s="93" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="65">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="66">
+        <v>12</v>
+      </c>
+      <c r="F24" s="83">
+        <v>50</v>
+      </c>
+      <c r="G24" s="84">
+        <v>50</v>
+      </c>
+      <c r="H24" s="84">
+        <v>50</v>
+      </c>
+      <c r="I24" s="84">
+        <v>50</v>
+      </c>
+      <c r="J24" s="84">
+        <v>50</v>
+      </c>
+      <c r="K24" s="84">
+        <v>50</v>
+      </c>
+      <c r="L24" s="84">
+        <v>50</v>
+      </c>
+      <c r="M24" s="99">
+        <v>50</v>
+      </c>
+      <c r="N24" s="93" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="65">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="66">
+        <v>12</v>
+      </c>
+      <c r="F25" s="65">
+        <v>0</v>
+      </c>
+      <c r="G25" s="84">
+        <v>50</v>
+      </c>
+      <c r="H25" s="84">
+        <v>50</v>
+      </c>
+      <c r="I25" s="84">
+        <v>50</v>
+      </c>
+      <c r="J25" s="84">
+        <v>50</v>
+      </c>
+      <c r="K25" s="84">
+        <v>50</v>
+      </c>
+      <c r="L25" s="84">
+        <v>50</v>
+      </c>
+      <c r="M25" s="99">
+        <v>50</v>
+      </c>
+      <c r="N25" s="93" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B26" s="65">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="66">
+        <v>52</v>
+      </c>
+      <c r="F26" s="65">
+        <v>0</v>
+      </c>
+      <c r="G26" s="84">
+        <v>50</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="84">
+        <v>50</v>
+      </c>
+      <c r="J26" s="84">
+        <v>50</v>
+      </c>
+      <c r="K26" s="84">
+        <v>50</v>
+      </c>
+      <c r="L26" s="84">
+        <v>50</v>
+      </c>
+      <c r="M26" s="99">
+        <v>50</v>
+      </c>
+      <c r="N26" s="93" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B27" s="65">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="66">
+        <v>92</v>
+      </c>
+      <c r="F27" s="65">
+        <v>0</v>
+      </c>
+      <c r="G27" s="84">
+        <v>50</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="84">
+        <v>50</v>
+      </c>
+      <c r="J27" s="9">
+        <v>0</v>
+      </c>
+      <c r="K27" s="84">
+        <v>50</v>
+      </c>
+      <c r="L27" s="84">
+        <v>50</v>
+      </c>
+      <c r="M27" s="99">
+        <v>50</v>
+      </c>
+      <c r="N27" s="93" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B28" s="65">
+        <v>7</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="66">
+        <v>132</v>
+      </c>
+      <c r="F28" s="65">
+        <v>0</v>
+      </c>
+      <c r="G28" s="84">
+        <v>50</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="84">
+        <v>50</v>
+      </c>
+      <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="84">
+        <v>50</v>
+      </c>
+      <c r="L28" s="9">
+        <v>0</v>
+      </c>
+      <c r="M28" s="99">
+        <v>50</v>
+      </c>
+      <c r="N28" s="93" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B29" s="65">
+        <v>8</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="66">
+        <v>12</v>
+      </c>
+      <c r="F29" s="65">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0</v>
+      </c>
+      <c r="J29" s="9">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9">
+        <v>0</v>
+      </c>
+      <c r="M29" s="66">
+        <v>0</v>
+      </c>
+      <c r="N29" s="93" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B30" s="65">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="66">
+        <v>75</v>
+      </c>
+      <c r="F30" s="65">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0</v>
+      </c>
+      <c r="M30" s="66">
+        <v>0</v>
+      </c>
+      <c r="N30" s="93" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B31" s="65">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="66">
+        <v>12</v>
+      </c>
+      <c r="F31" s="100">
+        <v>75</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9">
+        <v>0</v>
+      </c>
+      <c r="J31" s="9">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9">
+        <v>0</v>
+      </c>
+      <c r="L31" s="9">
+        <v>0</v>
+      </c>
+      <c r="M31" s="66">
+        <v>0</v>
+      </c>
+      <c r="N31" s="93" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B32" s="65">
+        <v>11</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="66">
+        <v>52</v>
+      </c>
+      <c r="F32" s="100">
+        <v>75</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="97">
+        <v>75</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9">
+        <v>0</v>
+      </c>
+      <c r="M32" s="66">
+        <v>0</v>
+      </c>
+      <c r="N32" s="93" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B33" s="65">
+        <v>12</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="66">
+        <v>92</v>
+      </c>
+      <c r="F33" s="100">
+        <v>75</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="97">
+        <v>75</v>
+      </c>
+      <c r="I33" s="9">
+        <v>0</v>
+      </c>
+      <c r="J33" s="97">
+        <v>75</v>
+      </c>
+      <c r="K33" s="9">
+        <v>0</v>
+      </c>
+      <c r="L33" s="9">
+        <v>0</v>
+      </c>
+      <c r="M33" s="66">
+        <v>0</v>
+      </c>
+      <c r="N33" s="93" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="67">
+        <v>13</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="69">
+        <v>132</v>
+      </c>
+      <c r="F34" s="101">
+        <v>75</v>
+      </c>
+      <c r="G34" s="73">
+        <v>0</v>
+      </c>
+      <c r="H34" s="102">
+        <v>75</v>
+      </c>
+      <c r="I34" s="73">
+        <v>0</v>
+      </c>
+      <c r="J34" s="102">
+        <v>75</v>
+      </c>
+      <c r="K34" s="73">
+        <v>0</v>
+      </c>
+      <c r="L34" s="102">
+        <v>75</v>
+      </c>
+      <c r="M34" s="69">
+        <v>0</v>
+      </c>
+      <c r="N34" s="103" t="s">
+        <v>233</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="J2:M2"/>
+  <mergeCells count="12">
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D94B1B4-5E19-4B7E-B339-5098F81A2FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2834588-FD73-4F04-89C2-4922D5CE9E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="238">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -864,18 +864,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>D11 점멸 후 점등</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC24, XD04 전원 인가, 레지스터 설정, LED 전류 0mA, VLED On 필요, 다음 명령어까지 50ms delay 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC24, XD04 전원 차단, VLED Off 필요, 다음 명령어까지 50ms delay 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 1ms delay 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -933,6 +921,34 @@
   </si>
   <si>
     <t>132번 Block 점등 (현재 단계에서 BABA 패턴 구현)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24, XD04 전원 인가, 레지스터 설정, LED 전류 0mA, VLED On 필요, 다음 명령어까지 최소 250ms delay 필요 (VDD Ramp-up &amp; Setting Time, IC Initial Time)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24, XD04 전원 차단, VLED Off 필요, 다음 명령어까지 최소 250ms delay 필요 (IC De-Initalize &amp; VDD Off Time)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. Example Screenshot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) RS232 --&gt; Control B'D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2) Control B'D --&gt; RS232 (Good Packet)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3) Control B'D --&gt; RS232 (Bad Packet ex. Wrong checksum)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D11 3초간 점멸 후 점등</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1972,6 +1988,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1999,18 +2024,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2032,31 +2048,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2088,6 +2104,1153 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>31432</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8B8C97B-5A41-4608-BA71-EA47D5D9FAC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="200025" y="9944100"/>
+          <a:ext cx="7772400" cy="5003482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="572849" cy="280205"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACC1104E-FE48-274F-F27D-9082C308C3FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="485775" y="11430000"/>
+          <a:ext cx="572849" cy="280205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>RS232</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="497059" cy="280205"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15B5F93B-ED2A-42D8-A840-794673294450}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="552450" y="13535025"/>
+          <a:ext cx="497059" cy="280205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MCU</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>31432</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB65DE1D-4CE0-47BD-AB8B-7954FAF8CFA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="200025" y="15430500"/>
+          <a:ext cx="7772400" cy="5003482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="572849" cy="280205"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4AD454C-52DC-4B71-8096-80882AB3FFBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="447675" y="16906875"/>
+          <a:ext cx="572849" cy="280205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>RS232</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="497059" cy="280205"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="TextBox 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4D244A-0724-4E54-A4DC-A74B4A5FED1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="561975" y="19040475"/>
+          <a:ext cx="497059" cy="280205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MCU</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="직선 화살표 연결선 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6383B1E1-A330-FD2A-BA16-A2D6CEE3E95E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3171825" y="18468975"/>
+          <a:ext cx="1047750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1590675</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="직선 화살표 연결선 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D73773B-A799-4922-8CD8-8A6E5C022ECA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4248150" y="18468975"/>
+          <a:ext cx="1047750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="701282" cy="436786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{488B84FA-1C68-E3F4-543C-5E835745D11D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3371850" y="18002250"/>
+          <a:ext cx="701282" cy="436786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Commad</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>status</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>537156</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1093826" cy="436786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E3ABB40-F3D0-4DBC-AB28-BFD43A2DC99D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4242381" y="17992725"/>
+          <a:ext cx="1093826" cy="436786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data (response)</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Good Packet</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>31432</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="그림 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77033AC0-FA41-471F-A676-8C197D532347}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="200025" y="20916900"/>
+          <a:ext cx="7772400" cy="5003482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="572849" cy="280205"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="TextBox 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F5E7AC7-4B14-4488-9251-6EB281C8FBFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438150" y="22336125"/>
+          <a:ext cx="572849" cy="280205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>RS232</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="497059" cy="280205"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="TextBox 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97D3359D-3FB7-4EAE-8D0E-872337029656}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="552450" y="24469725"/>
+          <a:ext cx="497059" cy="280205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MCU</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="직선 화살표 연결선 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D224A6C-AF41-456B-B4E5-CB32BE2AB517}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3162300" y="23898225"/>
+          <a:ext cx="1047750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1581150</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="직선 화살표 연결선 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1522E29-C238-484F-8F46-2F9449B54EAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4238625" y="23898225"/>
+          <a:ext cx="1047750" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="701282" cy="436786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="TextBox 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02DB9F24-E268-47CA-A23E-324A796868B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3362325" y="23431500"/>
+          <a:ext cx="701282" cy="436786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Commad</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>status</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>527629</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1093826" cy="436786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="TextBox 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{189B8362-FCBB-4B24-82B9-73B97A61ED12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4232854" y="23421975"/>
+          <a:ext cx="1093826" cy="436786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Data (response)</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Bad Packet</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2239,7 +3402,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2633,13 +3796,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M54"/>
+  <dimension ref="B2:M122"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="17.75" style="6" customWidth="1"/>
-    <col min="3" max="10" width="17.625" style="6" customWidth="1"/>
-    <col min="11" max="16" width="9" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="7" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="23.5" style="6" customWidth="1"/>
+    <col min="11" max="13" width="10.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9" style="6" customWidth="1"/>
     <col min="17" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
@@ -2649,14 +3816,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="104" t="s">
-        <v>219</v>
-      </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
+      <c r="B3" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -2708,14 +3875,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="112" t="s">
+      <c r="E7" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -2727,14 +3894,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="113" t="s">
+      <c r="E8" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -2746,14 +3913,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="105" t="s">
+      <c r="E9" s="108" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="107"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="109"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="110"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -2765,14 +3932,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="113" t="s">
+      <c r="E10" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -2784,14 +3951,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="108" t="s">
+      <c r="E11" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="110"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -2803,14 +3970,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="113" t="s">
+      <c r="E12" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -2822,14 +3989,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="108" t="s">
+      <c r="E13" s="111" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="110"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="113"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
@@ -2849,13 +4016,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="112" t="s">
+      <c r="F17" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="112"/>
-      <c r="J17" s="112"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="115"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
@@ -2870,13 +4037,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="G18" s="114"/>
-      <c r="H18" s="114"/>
-      <c r="I18" s="114"/>
-      <c r="J18" s="114"/>
+      <c r="F18" s="116" t="s">
+        <v>231</v>
+      </c>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="116"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
@@ -2891,13 +4058,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="114" t="s">
-        <v>218</v>
-      </c>
-      <c r="G19" s="114"/>
-      <c r="H19" s="114"/>
-      <c r="I19" s="114"/>
-      <c r="J19" s="114"/>
+      <c r="F19" s="116" t="s">
+        <v>232</v>
+      </c>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
@@ -2912,13 +4079,13 @@
       <c r="E20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F20" s="113" t="s">
+      <c r="F20" s="105" t="s">
         <v>145</v>
       </c>
-      <c r="G20" s="113"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="113"/>
-      <c r="J20" s="113"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -2933,13 +4100,13 @@
       <c r="E21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="113" t="s">
+      <c r="F21" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
-      <c r="J21" s="113"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
@@ -2954,13 +4121,13 @@
       <c r="E22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="113" t="s">
+      <c r="F22" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="113"/>
-      <c r="H22" s="113"/>
-      <c r="I22" s="113"/>
-      <c r="J22" s="113"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
@@ -2975,13 +4142,13 @@
       <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="113" t="s">
+      <c r="F23" s="105" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="113"/>
-      <c r="H23" s="113"/>
-      <c r="I23" s="113"/>
-      <c r="J23" s="113"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
@@ -2996,13 +4163,13 @@
       <c r="E24" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="113" t="s">
+      <c r="F24" s="105" t="s">
         <v>149</v>
       </c>
-      <c r="G24" s="113"/>
-      <c r="H24" s="113"/>
-      <c r="I24" s="113"/>
-      <c r="J24" s="113"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
@@ -3017,13 +4184,13 @@
       <c r="E25" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="113" t="s">
+      <c r="F25" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="113"/>
-      <c r="H25" s="113"/>
-      <c r="I25" s="113"/>
-      <c r="J25" s="113"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
@@ -3032,14 +4199,14 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="C29" s="111" t="s">
+      <c r="C29" s="114" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="114"/>
+      <c r="G29" s="114"/>
+      <c r="H29" s="114"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
@@ -3068,7 +4235,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="116" t="s">
+      <c r="C31" s="106" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -3083,7 +4250,7 @@
       <c r="G31" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="116" t="s">
+      <c r="H31" s="106" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3091,7 +4258,7 @@
       <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="116"/>
+      <c r="C32" s="106"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -3104,13 +4271,13 @@
       <c r="G32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="116"/>
+      <c r="H32" s="106"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="116"/>
+      <c r="C33" s="106"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -3123,13 +4290,13 @@
       <c r="G33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H33" s="116"/>
+      <c r="H33" s="106"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="116"/>
+      <c r="C34" s="106"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -3142,13 +4309,13 @@
       <c r="G34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="116"/>
+      <c r="H34" s="106"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="116"/>
+      <c r="C35" s="106"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -3161,13 +4328,13 @@
       <c r="G35" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="116"/>
+      <c r="H35" s="106"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="116"/>
+      <c r="C36" s="106"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -3180,13 +4347,13 @@
       <c r="G36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="116"/>
+      <c r="H36" s="106"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="116"/>
+      <c r="C37" s="106"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -3199,13 +4366,13 @@
       <c r="G37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="116"/>
+      <c r="H37" s="106"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="116"/>
+      <c r="C38" s="106"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -3218,13 +4385,13 @@
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="116"/>
+      <c r="H38" s="106"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="116"/>
+      <c r="C39" s="106"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -3237,7 +4404,7 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="116"/>
+      <c r="H39" s="106"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
@@ -3261,16 +4428,16 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="115" t="s">
+      <c r="F43" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="115"/>
-      <c r="H43" s="115"/>
-      <c r="I43" s="115"/>
-      <c r="J43" s="115"/>
-      <c r="K43" s="115"/>
-      <c r="L43" s="115"/>
-      <c r="M43" s="115"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="104"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
@@ -3515,14 +4682,28 @@
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>
     </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B57" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B58" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B90" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B122" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="C31:C39"/>
-    <mergeCell ref="H31:H39"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
@@ -3538,9 +4719,16 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="C31:C39"/>
+    <mergeCell ref="H31:H39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3557,25 +4745,25 @@
       <c r="B2" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="115" t="s">
+      <c r="D2" s="104" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="115" t="s">
+      <c r="E2" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115" t="s">
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="118"/>
-      <c r="D3" s="115"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="7" t="s">
         <v>138</v>
       </c>
@@ -4469,7 +5657,7 @@
     <col min="8" max="8" width="23.125" style="31" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.625" style="31" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.875" style="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.75" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="31" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="31"/>
     <col min="14" max="14" width="9.25" style="31" bestFit="1" customWidth="1"/>
@@ -4651,7 +5839,7 @@
         <v>188</v>
       </c>
       <c r="K7" s="56" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="L7" s="59" t="s">
         <v>162</v>
@@ -4741,7 +5929,7 @@
   <sheetData>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4751,7 +5939,7 @@
       <c r="C3" s="125" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="126" t="s">
+      <c r="D3" s="127" t="s">
         <v>204</v>
       </c>
       <c r="F3" s="122" t="s">
@@ -4765,15 +5953,15 @@
       </c>
       <c r="K3" s="125"/>
       <c r="L3" s="125"/>
-      <c r="M3" s="129"/>
+      <c r="M3" s="130"/>
       <c r="N3" s="119" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="123"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="127"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="128"/>
       <c r="F4" s="64" t="s">
         <v>138</v>
       </c>
@@ -4801,9 +5989,9 @@
       <c r="N4" s="120"/>
     </row>
     <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="130"/>
-      <c r="C5" s="131"/>
-      <c r="D5" s="132"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="129"/>
       <c r="F5" s="74">
         <v>1</v>
       </c>
@@ -5219,7 +6407,7 @@
     </row>
     <row r="18" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
@@ -5229,7 +6417,7 @@
       <c r="C19" s="125" t="s">
         <v>203</v>
       </c>
-      <c r="D19" s="126" t="s">
+      <c r="D19" s="127" t="s">
         <v>204</v>
       </c>
       <c r="F19" s="122" t="s">
@@ -5243,15 +6431,15 @@
       </c>
       <c r="K19" s="125"/>
       <c r="L19" s="125"/>
-      <c r="M19" s="129"/>
+      <c r="M19" s="130"/>
       <c r="N19" s="119" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="123"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="127"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="128"/>
       <c r="F20" s="64" t="s">
         <v>138</v>
       </c>
@@ -5279,9 +6467,9 @@
       <c r="N20" s="120"/>
     </row>
     <row r="21" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="124"/>
+      <c r="B21" s="131"/>
       <c r="C21" s="117"/>
-      <c r="D21" s="128"/>
+      <c r="D21" s="132"/>
       <c r="F21" s="94">
         <v>12</v>
       </c>
@@ -5388,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="93" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.3">
@@ -5426,7 +6614,7 @@
         <v>50</v>
       </c>
       <c r="N24" s="93" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.3">
@@ -5464,7 +6652,7 @@
         <v>50</v>
       </c>
       <c r="N25" s="93" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
@@ -5502,7 +6690,7 @@
         <v>50</v>
       </c>
       <c r="N26" s="93" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.3">
@@ -5540,7 +6728,7 @@
         <v>50</v>
       </c>
       <c r="N27" s="93" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.3">
@@ -5578,7 +6766,7 @@
         <v>50</v>
       </c>
       <c r="N28" s="93" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.3">
@@ -5616,7 +6804,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="93" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.3">
@@ -5654,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="93" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.3">
@@ -5692,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="93" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.3">
@@ -5730,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="93" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.3">
@@ -5768,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="93" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5806,23 +6994,23 @@
         <v>0</v>
       </c>
       <c r="N34" s="103" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="J19:M19"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2834588-FD73-4F04-89C2-4922D5CE9E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A04715-4FC1-4984-9BEE-262662D7AA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="241">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -676,14 +676,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TP25 (780kHz Pulse 파형)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TP50 (UART 파형)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Status 커맨드 수신</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -924,10 +916,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>XC24, XD04 전원 인가, 레지스터 설정, LED 전류 0mA, VLED On 필요, 다음 명령어까지 최소 250ms delay 필요 (VDD Ramp-up &amp; Setting Time, IC Initial Time)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>XC24, XD04 전원 차단, VLED Off 필요, 다음 명령어까지 최소 250ms delay 필요 (IC De-Initalize &amp; VDD Off Time)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -949,6 +937,30 @@
   </si>
   <si>
     <t>D11 3초간 점멸 후 점등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24, XD04 전원 인가, 레지스터 설정, LED 전류 0mA, VLED On 필요, 다음 명령어까지 최소 250ms delay 필요 (VDD Ramp-up &amp; Settling Time, IC Initial)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP28 (780kHz Pulse 파형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R86 0옴 부착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명시된 Check Point의 값 대비 ±3% 이내 값이 측정된다면 OK, 이상 벗어나는 경우 NG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ex) TP9 (5V)의 경우 5V ± 3% = 4.85 ~ 5.15V 사이의 값이 측정되면 OK. 이외의 값이면 NG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP65 (UART 파형)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1677,7 +1689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1799,234 +1811,237 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2048,31 +2063,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3797,35 +3812,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M122"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" style="6" customWidth="1"/>
     <col min="3" max="3" width="7" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="23.5" style="6" customWidth="1"/>
-    <col min="11" max="13" width="10.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="10.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="9" style="6" customWidth="1"/>
     <col min="17" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="107" t="s">
-        <v>216</v>
-      </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B3" s="105" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3845,7 +3860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -3865,7 +3880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>62</v>
       </c>
@@ -3875,16 +3890,16 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="115" t="s">
+      <c r="E7" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="113"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
         <v>0</v>
       </c>
@@ -3894,16 +3909,16 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="105" t="s">
+      <c r="E8" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F8" s="114"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="114"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
         <v>66</v>
       </c>
@@ -3913,16 +3928,16 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="108" t="s">
-        <v>200</v>
-      </c>
-      <c r="F9" s="109"/>
-      <c r="G9" s="109"/>
-      <c r="H9" s="109"/>
-      <c r="I9" s="109"/>
-      <c r="J9" s="110"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E9" s="106" t="s">
+        <v>198</v>
+      </c>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="108"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
@@ -3932,16 +3947,16 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="105" t="s">
+      <c r="E10" s="114" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F10" s="114"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
@@ -3951,16 +3966,16 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="111" t="s">
+      <c r="E11" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="111"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
@@ -3970,16 +3985,16 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="105" t="s">
+      <c r="E12" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F12" s="114"/>
+      <c r="G12" s="114"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="114"/>
+      <c r="J12" s="114"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
@@ -3989,21 +4004,21 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="111" t="s">
+      <c r="E13" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="112"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="113"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="111"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
@@ -4016,15 +4031,15 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="115" t="s">
+      <c r="F17" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
@@ -4037,15 +4052,15 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="116" t="s">
-        <v>231</v>
-      </c>
-      <c r="G18" s="116"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F18" s="115" t="s">
+        <v>235</v>
+      </c>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
@@ -4058,15 +4073,15 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="116" t="s">
-        <v>232</v>
-      </c>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F19" s="115" t="s">
+        <v>229</v>
+      </c>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>142</v>
       </c>
@@ -4079,15 +4094,15 @@
       <c r="E20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F20" s="105" t="s">
+      <c r="F20" s="114" t="s">
         <v>145</v>
       </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G20" s="114"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="114"/>
+      <c r="J20" s="114"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
@@ -4100,15 +4115,15 @@
       <c r="E21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="105" t="s">
+      <c r="F21" s="114" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G21" s="114"/>
+      <c r="H21" s="114"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="114"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
@@ -4121,15 +4136,15 @@
       <c r="E22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="105" t="s">
+      <c r="F22" s="114" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="114"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
@@ -4142,15 +4157,15 @@
       <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="105" t="s">
+      <c r="F23" s="114" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="105"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="105"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="114"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>22</v>
       </c>
@@ -4163,15 +4178,15 @@
       <c r="E24" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="105" t="s">
+      <c r="F24" s="114" t="s">
         <v>149</v>
       </c>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G24" s="114"/>
+      <c r="H24" s="114"/>
+      <c r="I24" s="114"/>
+      <c r="J24" s="114"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>23</v>
       </c>
@@ -4184,31 +4199,31 @@
       <c r="E25" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="105" t="s">
+      <c r="F25" s="114" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G25" s="114"/>
+      <c r="H25" s="114"/>
+      <c r="I25" s="114"/>
+      <c r="J25" s="114"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B28" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B29" s="1"/>
-      <c r="C29" s="114" t="s">
+      <c r="C29" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="114"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="114"/>
-      <c r="G29" s="114"/>
-      <c r="H29" s="114"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
+      <c r="H29" s="112"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B30" s="1" t="s">
         <v>68</v>
       </c>
@@ -4231,11 +4246,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="106" t="s">
+      <c r="C31" s="117" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -4250,15 +4265,15 @@
       <c r="G31" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="106" t="s">
+      <c r="H31" s="117" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="106"/>
+      <c r="C32" s="117"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -4271,13 +4286,13 @@
       <c r="G32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="106"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H32" s="117"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="106"/>
+      <c r="C33" s="117"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4290,13 +4305,13 @@
       <c r="G33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H33" s="106"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H33" s="117"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="106"/>
+      <c r="C34" s="117"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -4309,13 +4324,13 @@
       <c r="G34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="106"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H34" s="117"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="106"/>
+      <c r="C35" s="117"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -4328,13 +4343,13 @@
       <c r="G35" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="106"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H35" s="117"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="106"/>
+      <c r="C36" s="117"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -4347,13 +4362,13 @@
       <c r="G36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="106"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H36" s="117"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="106"/>
+      <c r="C37" s="117"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4366,13 +4381,13 @@
       <c r="G37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="106"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H37" s="117"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="106"/>
+      <c r="C38" s="117"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -4385,13 +4400,13 @@
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="106"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H38" s="117"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="106"/>
+      <c r="C39" s="117"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -4404,9 +4419,9 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="106"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H39" s="117"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.45">
       <c r="C40" s="11"/>
       <c r="D40" s="12"/>
       <c r="E40" s="11"/>
@@ -4414,12 +4429,12 @@
       <c r="G40" s="11"/>
       <c r="H40" s="11"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B42" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B43" s="7" t="s">
         <v>48</v>
       </c>
@@ -4428,18 +4443,18 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="104" t="s">
+      <c r="F43" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="104"/>
-      <c r="H43" s="104"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="104"/>
-      <c r="K43" s="104"/>
-      <c r="L43" s="104"/>
-      <c r="M43" s="104"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="G43" s="116"/>
+      <c r="H43" s="116"/>
+      <c r="I43" s="116"/>
+      <c r="J43" s="116"/>
+      <c r="K43" s="116"/>
+      <c r="L43" s="116"/>
+      <c r="M43" s="116"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B44" s="9" t="s">
         <v>25</v>
       </c>
@@ -4477,7 +4492,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B45" s="9" t="s">
         <v>26</v>
       </c>
@@ -4513,7 +4528,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B46" s="9" t="s">
         <v>27</v>
       </c>
@@ -4532,7 +4547,7 @@
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B47" s="9" t="s">
         <v>28</v>
       </c>
@@ -4551,7 +4566,7 @@
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B48" s="9" t="s">
         <v>29</v>
       </c>
@@ -4570,7 +4585,7 @@
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B49" s="9" t="s">
         <v>35</v>
       </c>
@@ -4587,7 +4602,7 @@
       <c r="K49" s="11"/>
       <c r="L49" s="11"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B50" s="9" t="s">
         <v>34</v>
       </c>
@@ -4606,7 +4621,7 @@
       <c r="K50" s="11"/>
       <c r="L50" s="11"/>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B51" s="9" t="s">
         <v>33</v>
       </c>
@@ -4625,7 +4640,7 @@
       <c r="K51" s="11"/>
       <c r="L51" s="11"/>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B52" s="9" t="s">
         <v>32</v>
       </c>
@@ -4644,7 +4659,7 @@
       <c r="K52" s="11"/>
       <c r="L52" s="11"/>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B53" s="9" t="s">
         <v>31</v>
       </c>
@@ -4663,7 +4678,7 @@
       <c r="K53" s="11"/>
       <c r="L53" s="11"/>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B54" s="9" t="s">
         <v>30</v>
       </c>
@@ -4682,28 +4697,34 @@
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B57" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B58" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B90" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B122" s="6" t="s">
         <v>233</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B58" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B90" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B122" s="6" t="s">
-        <v>236</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="C31:C39"/>
+    <mergeCell ref="H31:H39"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
@@ -4719,12 +4740,6 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="C31:C39"/>
-    <mergeCell ref="H31:H39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4735,35 +4750,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CADB1EA6-99AD-4FE8-82D9-732EE4C0DA8F}">
   <dimension ref="B2:L23"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="11" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="2.58203125" style="11" customWidth="1"/>
+    <col min="2" max="4" width="9" style="11"/>
+    <col min="5" max="5" width="9" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="117" t="s">
+    <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="104" t="s">
+      <c r="D2" s="116" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="116" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104" t="s">
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="118"/>
-      <c r="D3" s="104"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B3" s="119"/>
+      <c r="D3" s="116"/>
       <c r="E3" s="7" t="s">
         <v>138</v>
       </c>
@@ -4789,7 +4806,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B4" s="25" t="s">
         <v>130</v>
       </c>
@@ -4831,7 +4848,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B5" s="25" t="s">
         <v>129</v>
       </c>
@@ -4873,7 +4890,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B6" s="25" t="s">
         <v>128</v>
       </c>
@@ -4915,7 +4932,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B7" s="25" t="s">
         <v>127</v>
       </c>
@@ -4957,7 +4974,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B8" s="25" t="s">
         <v>126</v>
       </c>
@@ -4999,7 +5016,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" s="25" t="s">
         <v>125</v>
       </c>
@@ -5041,7 +5058,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" s="25" t="s">
         <v>124</v>
       </c>
@@ -5083,7 +5100,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B11" s="25" t="s">
         <v>123</v>
       </c>
@@ -5125,7 +5142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B12" s="25" t="s">
         <v>122</v>
       </c>
@@ -5167,7 +5184,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B13" s="25" t="s">
         <v>121</v>
       </c>
@@ -5209,7 +5226,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B14" s="25" t="s">
         <v>120</v>
       </c>
@@ -5251,7 +5268,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B15" s="25" t="s">
         <v>119</v>
       </c>
@@ -5293,7 +5310,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B16" s="25" t="s">
         <v>118</v>
       </c>
@@ -5335,7 +5352,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B17" s="25" t="s">
         <v>117</v>
       </c>
@@ -5377,7 +5394,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B18" s="25" t="s">
         <v>116</v>
       </c>
@@ -5419,7 +5436,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B19" s="25" t="s">
         <v>115</v>
       </c>
@@ -5461,7 +5478,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B20" s="25" t="s">
         <v>114</v>
       </c>
@@ -5503,7 +5520,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B21" s="25" t="s">
         <v>113</v>
       </c>
@@ -5545,7 +5562,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B22" s="25" t="s">
         <v>112</v>
       </c>
@@ -5587,7 +5604,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B23" s="25" t="s">
         <v>111</v>
       </c>
@@ -5644,19 +5661,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5776C9-E522-4127-B982-E334D5A025FE}">
-  <dimension ref="B1:L8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:L11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="31" customWidth="1"/>
-    <col min="2" max="2" width="8.375" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.375" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="31" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.75" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.875" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.375" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" style="31" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.75" style="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.125" style="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" style="31" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.875" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.08203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.58203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" style="31" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.75" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="31" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="31"/>
@@ -5664,12 +5681,12 @@
     <col min="15" max="16384" width="9" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="42" t="s">
-        <v>180</v>
-      </c>
-      <c r="C2" s="43" t="s">
+    <row r="1" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="42" t="s">
         <v>153</v>
       </c>
       <c r="D2" s="35" t="s">
@@ -5681,7 +5698,7 @@
       <c r="F2" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="46" t="s">
         <v>154</v>
       </c>
       <c r="H2" s="37" t="s">
@@ -5693,185 +5710,197 @@
       <c r="J2" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="L2" s="42" t="s">
+      <c r="L2" s="41" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="61">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B3" s="60">
         <v>1</v>
       </c>
-      <c r="C3" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="D3" s="48"/>
+      <c r="C3" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="47"/>
       <c r="E3" s="34"/>
-      <c r="F3" s="49"/>
+      <c r="F3" s="48"/>
       <c r="G3" s="39" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I3" s="34"/>
       <c r="J3" s="34"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="58" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="62">
+      <c r="K3" s="54"/>
+      <c r="L3" s="57" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B4" s="61">
         <v>2</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F4" s="51"/>
+      <c r="F4" s="50" t="s">
+        <v>237</v>
+      </c>
       <c r="G4" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="I4" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>193</v>
-      </c>
       <c r="J4" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="K4" s="56"/>
-      <c r="L4" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="K4" s="55"/>
+      <c r="L4" s="58" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="62">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B5" s="61">
         <v>3</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="50" t="s">
         <v>167</v>
       </c>
       <c r="G5" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="I5" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="I5" s="32" t="s">
-        <v>194</v>
-      </c>
       <c r="J5" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="K5" s="56"/>
-      <c r="L5" s="59" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" s="55"/>
+      <c r="L5" s="58" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="62">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B6" s="61">
         <v>4</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" s="50" t="s">
+      <c r="C6" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="49" t="s">
         <v>168</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="40" t="s">
-        <v>170</v>
+      <c r="F6" s="50"/>
+      <c r="G6" s="104" t="s">
+        <v>240</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I6" s="32"/>
       <c r="J6" s="32"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="59" t="s">
+      <c r="K6" s="55"/>
+      <c r="L6" s="58" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="62">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B7" s="61">
         <v>5</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" s="50" t="s">
+      <c r="C7" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" s="49" t="s">
         <v>168</v>
       </c>
       <c r="E7" s="32"/>
-      <c r="F7" s="51"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="J7" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="I7" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="K7" s="56" t="s">
-        <v>237</v>
-      </c>
-      <c r="L7" s="59" t="s">
+      <c r="K7" s="55" t="s">
+        <v>234</v>
+      </c>
+      <c r="L7" s="58" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="63">
+    <row r="8" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="62">
         <v>6</v>
       </c>
-      <c r="C8" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="52" t="s">
+      <c r="C8" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="51" t="s">
         <v>168</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="G8" s="41" t="s">
-        <v>169</v>
+        <v>174</v>
+      </c>
+      <c r="F8" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="G8" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>161</v>
       </c>
       <c r="I8" s="33"/>
       <c r="J8" s="33"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="60" t="s">
+      <c r="K8" s="56"/>
+      <c r="L8" s="59" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" s="31" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B11" s="31" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -5889,20 +5918,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1D2CDE-03D0-4073-94E8-BF70397D701B}">
   <dimension ref="B2:W2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H2" t="s">
+        <v>196</v>
+      </c>
+      <c r="W2" t="s">
         <v>197</v>
-      </c>
-      <c r="H2" t="s">
-        <v>198</v>
-      </c>
-      <c r="W2" t="s">
-        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -5915,54 +5944,54 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57173FD-D29F-465B-B16F-5A3BAEE50DB9}">
   <dimension ref="B2:N34"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="11" customWidth="1"/>
     <col min="2" max="2" width="8.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.875" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.875" style="11" customWidth="1"/>
-    <col min="6" max="13" width="6.125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="13.58203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" style="11" customWidth="1"/>
+    <col min="6" max="13" width="6.08203125" style="11" customWidth="1"/>
     <col min="14" max="14" width="54.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="122" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="123" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="125" t="s">
-        <v>203</v>
-      </c>
       <c r="D3" s="127" t="s">
-        <v>204</v>
-      </c>
-      <c r="F3" s="122" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125" t="s">
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126" t="s">
         <v>97</v>
       </c>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
       <c r="M3" s="130"/>
-      <c r="N3" s="119" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="123"/>
-      <c r="C4" s="104"/>
+      <c r="N3" s="120" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B4" s="124"/>
+      <c r="C4" s="116"/>
       <c r="D4" s="128"/>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="63" t="s">
         <v>138</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -5983,59 +6012,59 @@
       <c r="L4" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="M4" s="76" t="s">
+      <c r="M4" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="N4" s="120"/>
-    </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="124"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="129"/>
-      <c r="F5" s="74">
+      <c r="N4" s="121"/>
+    </row>
+    <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="131"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="133"/>
+      <c r="F5" s="73">
         <v>1</v>
       </c>
-      <c r="G5" s="75">
+      <c r="G5" s="74">
         <f t="shared" ref="G5:M5" si="0">F5+20</f>
         <v>21</v>
       </c>
-      <c r="H5" s="75">
+      <c r="H5" s="74">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="74">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="J5" s="75">
+      <c r="J5" s="74">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="K5" s="75">
+      <c r="K5" s="74">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="L5" s="75">
+      <c r="L5" s="74">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="M5" s="77">
+      <c r="M5" s="76">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="121"/>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="70">
+      <c r="N5" s="122"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B6" s="69">
         <v>1</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="72">
-        <v>0</v>
-      </c>
-      <c r="F6" s="70">
+      <c r="D6" s="71">
+        <v>0</v>
+      </c>
+      <c r="F6" s="69">
         <v>0</v>
       </c>
       <c r="G6" s="22">
@@ -6059,173 +6088,173 @@
       <c r="M6" s="21">
         <v>0</v>
       </c>
-      <c r="N6" s="80" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="65">
+      <c r="N6" s="79" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B7" s="64">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="65">
+        <v>50</v>
+      </c>
+      <c r="F7" s="64">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9">
+        <v>0</v>
+      </c>
+      <c r="M7" s="77">
+        <v>0</v>
+      </c>
+      <c r="N7" s="80" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="66">
-        <v>50</v>
-      </c>
-      <c r="F7" s="65">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="78">
-        <v>0</v>
-      </c>
-      <c r="N7" s="81" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="65">
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B8" s="64">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="66">
+      <c r="D8" s="65">
         <v>1</v>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="82">
         <v>50</v>
       </c>
-      <c r="G8" s="84">
+      <c r="G8" s="83">
         <v>50</v>
       </c>
-      <c r="H8" s="84">
+      <c r="H8" s="83">
         <v>50</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="83">
         <v>50</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="83">
         <v>50</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="83">
         <v>50</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="83">
         <v>50</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="84">
         <v>50</v>
       </c>
-      <c r="N8" s="81" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="65">
+      <c r="N8" s="80" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B9" s="64">
         <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="65">
         <v>1</v>
       </c>
-      <c r="F9" s="65">
-        <v>0</v>
-      </c>
-      <c r="G9" s="84">
+      <c r="F9" s="64">
+        <v>0</v>
+      </c>
+      <c r="G9" s="83">
         <v>50</v>
       </c>
-      <c r="H9" s="84">
+      <c r="H9" s="83">
         <v>50</v>
       </c>
-      <c r="I9" s="84">
+      <c r="I9" s="83">
         <v>50</v>
       </c>
-      <c r="J9" s="84">
+      <c r="J9" s="83">
         <v>50</v>
       </c>
-      <c r="K9" s="84">
+      <c r="K9" s="83">
         <v>50</v>
       </c>
-      <c r="L9" s="84">
+      <c r="L9" s="83">
         <v>50</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="84">
         <v>50</v>
       </c>
-      <c r="N9" s="81" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="65">
+      <c r="N9" s="80" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B10" s="64">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="66">
+      <c r="D10" s="65">
         <v>61</v>
       </c>
-      <c r="F10" s="65">
-        <v>0</v>
-      </c>
-      <c r="G10" s="84">
+      <c r="F10" s="64">
+        <v>0</v>
+      </c>
+      <c r="G10" s="83">
         <v>50</v>
       </c>
-      <c r="H10" s="84">
+      <c r="H10" s="83">
         <v>50</v>
       </c>
       <c r="I10" s="9">
         <v>0</v>
       </c>
-      <c r="J10" s="84">
+      <c r="J10" s="83">
         <v>50</v>
       </c>
-      <c r="K10" s="84">
+      <c r="K10" s="83">
         <v>50</v>
       </c>
-      <c r="L10" s="84">
+      <c r="L10" s="83">
         <v>50</v>
       </c>
-      <c r="M10" s="85">
+      <c r="M10" s="84">
         <v>50</v>
       </c>
-      <c r="N10" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="65">
+      <c r="N10" s="80" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B11" s="64">
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="66">
-        <v>0</v>
-      </c>
-      <c r="F11" s="65">
+      <c r="D11" s="65">
+        <v>0</v>
+      </c>
+      <c r="F11" s="64">
         <v>0</v>
       </c>
       <c r="G11" s="9">
@@ -6246,24 +6275,24 @@
       <c r="L11" s="9">
         <v>0</v>
       </c>
-      <c r="M11" s="78">
-        <v>0</v>
-      </c>
-      <c r="N11" s="81" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="65">
+      <c r="M11" s="77">
+        <v>0</v>
+      </c>
+      <c r="N11" s="80" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B12" s="64">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="65">
         <v>81</v>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="64">
         <v>0</v>
       </c>
       <c r="G12" s="9">
@@ -6275,7 +6304,7 @@
       <c r="I12" s="9">
         <v>0</v>
       </c>
-      <c r="J12" s="84">
+      <c r="J12" s="83">
         <v>50</v>
       </c>
       <c r="K12" s="9">
@@ -6284,24 +6313,24 @@
       <c r="L12" s="9">
         <v>0</v>
       </c>
-      <c r="M12" s="78">
-        <v>0</v>
-      </c>
-      <c r="N12" s="81" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="65">
+      <c r="M12" s="77">
+        <v>0</v>
+      </c>
+      <c r="N12" s="80" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B13" s="64">
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D13" s="66">
+        <v>203</v>
+      </c>
+      <c r="D13" s="65">
         <v>100</v>
       </c>
-      <c r="F13" s="65">
+      <c r="F13" s="64">
         <v>0</v>
       </c>
       <c r="G13" s="9">
@@ -6313,7 +6342,7 @@
       <c r="I13" s="9">
         <v>0</v>
       </c>
-      <c r="J13" s="87">
+      <c r="J13" s="86">
         <v>100</v>
       </c>
       <c r="K13" s="9">
@@ -6322,125 +6351,125 @@
       <c r="L13" s="9">
         <v>0</v>
       </c>
-      <c r="M13" s="78">
-        <v>0</v>
-      </c>
-      <c r="N13" s="81" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="65">
+      <c r="M13" s="77">
+        <v>0</v>
+      </c>
+      <c r="N13" s="80" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B14" s="64">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="66">
-        <v>0</v>
-      </c>
-      <c r="F14" s="86">
+      <c r="D14" s="65">
+        <v>0</v>
+      </c>
+      <c r="F14" s="85">
         <v>100</v>
       </c>
-      <c r="G14" s="87">
+      <c r="G14" s="86">
         <v>100</v>
       </c>
-      <c r="H14" s="87">
+      <c r="H14" s="86">
         <v>100</v>
       </c>
-      <c r="I14" s="87">
+      <c r="I14" s="86">
         <v>100</v>
       </c>
-      <c r="J14" s="87">
+      <c r="J14" s="86">
         <v>100</v>
       </c>
-      <c r="K14" s="87">
+      <c r="K14" s="86">
         <v>100</v>
       </c>
-      <c r="L14" s="87">
+      <c r="L14" s="86">
         <v>100</v>
       </c>
-      <c r="M14" s="88">
+      <c r="M14" s="87">
         <v>100</v>
       </c>
-      <c r="N14" s="81" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="67">
+      <c r="N14" s="80" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B15" s="66">
         <v>10</v>
       </c>
-      <c r="C15" s="68" t="s">
-        <v>205</v>
-      </c>
-      <c r="D15" s="69">
-        <v>0</v>
-      </c>
-      <c r="F15" s="67">
-        <v>0</v>
-      </c>
-      <c r="G15" s="73">
-        <v>0</v>
-      </c>
-      <c r="H15" s="73">
-        <v>0</v>
-      </c>
-      <c r="I15" s="73">
-        <v>0</v>
-      </c>
-      <c r="J15" s="73">
-        <v>0</v>
-      </c>
-      <c r="K15" s="73">
-        <v>0</v>
-      </c>
-      <c r="L15" s="73">
-        <v>0</v>
-      </c>
-      <c r="M15" s="79">
-        <v>0</v>
-      </c>
-      <c r="N15" s="82" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="68">
+        <v>0</v>
+      </c>
+      <c r="F15" s="66">
+        <v>0</v>
+      </c>
+      <c r="G15" s="72">
+        <v>0</v>
+      </c>
+      <c r="H15" s="72">
+        <v>0</v>
+      </c>
+      <c r="I15" s="72">
+        <v>0</v>
+      </c>
+      <c r="J15" s="72">
+        <v>0</v>
+      </c>
+      <c r="K15" s="72">
+        <v>0</v>
+      </c>
+      <c r="L15" s="72">
+        <v>0</v>
+      </c>
+      <c r="M15" s="78">
+        <v>0</v>
+      </c>
+      <c r="N15" s="81" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B19" s="122" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B19" s="123" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="C19" s="125" t="s">
-        <v>203</v>
-      </c>
       <c r="D19" s="127" t="s">
-        <v>204</v>
-      </c>
-      <c r="F19" s="122" t="s">
+        <v>202</v>
+      </c>
+      <c r="F19" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="125" t="s">
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126" t="s">
         <v>97</v>
       </c>
-      <c r="K19" s="125"/>
-      <c r="L19" s="125"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
       <c r="M19" s="130"/>
-      <c r="N19" s="119" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="123"/>
-      <c r="C20" s="104"/>
+      <c r="N19" s="120" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B20" s="124"/>
+      <c r="C20" s="116"/>
       <c r="D20" s="128"/>
-      <c r="F20" s="64" t="s">
+      <c r="F20" s="63" t="s">
         <v>138</v>
       </c>
       <c r="G20" s="7" t="s">
@@ -6461,97 +6490,97 @@
       <c r="L20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="M20" s="76" t="s">
+      <c r="M20" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="N20" s="120"/>
-    </row>
-    <row r="21" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="131"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="132"/>
-      <c r="F21" s="94">
+      <c r="N20" s="121"/>
+    </row>
+    <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="125"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="129"/>
+      <c r="F21" s="93">
         <v>12</v>
       </c>
-      <c r="G21" s="95">
+      <c r="G21" s="94">
         <f t="shared" ref="G21" si="1">F21+20</f>
         <v>32</v>
       </c>
-      <c r="H21" s="95">
+      <c r="H21" s="94">
         <f t="shared" ref="H21" si="2">G21+20</f>
         <v>52</v>
       </c>
-      <c r="I21" s="95">
+      <c r="I21" s="94">
         <f t="shared" ref="I21" si="3">H21+20</f>
         <v>72</v>
       </c>
-      <c r="J21" s="95">
+      <c r="J21" s="94">
         <f t="shared" ref="J21" si="4">I21+20</f>
         <v>92</v>
       </c>
-      <c r="K21" s="95">
+      <c r="K21" s="94">
         <f t="shared" ref="K21" si="5">J21+20</f>
         <v>112</v>
       </c>
-      <c r="L21" s="95">
+      <c r="L21" s="94">
         <f t="shared" ref="L21" si="6">K21+20</f>
         <v>132</v>
       </c>
-      <c r="M21" s="96">
+      <c r="M21" s="95">
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="121"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" s="89">
+      <c r="N21" s="122"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B22" s="88">
         <v>1</v>
       </c>
-      <c r="C22" s="90" t="s">
+      <c r="C22" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="91">
-        <v>0</v>
-      </c>
-      <c r="F22" s="89">
-        <v>0</v>
-      </c>
-      <c r="G22" s="98">
-        <v>0</v>
-      </c>
-      <c r="H22" s="98">
-        <v>0</v>
-      </c>
-      <c r="I22" s="98">
-        <v>0</v>
-      </c>
-      <c r="J22" s="98">
-        <v>0</v>
-      </c>
-      <c r="K22" s="98">
-        <v>0</v>
-      </c>
-      <c r="L22" s="98">
-        <v>0</v>
-      </c>
-      <c r="M22" s="91">
-        <v>0</v>
-      </c>
-      <c r="N22" s="92" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B23" s="65">
+      <c r="D22" s="90">
+        <v>0</v>
+      </c>
+      <c r="F22" s="88">
+        <v>0</v>
+      </c>
+      <c r="G22" s="97">
+        <v>0</v>
+      </c>
+      <c r="H22" s="97">
+        <v>0</v>
+      </c>
+      <c r="I22" s="97">
+        <v>0</v>
+      </c>
+      <c r="J22" s="97">
+        <v>0</v>
+      </c>
+      <c r="K22" s="97">
+        <v>0</v>
+      </c>
+      <c r="L22" s="97">
+        <v>0</v>
+      </c>
+      <c r="M22" s="90">
+        <v>0</v>
+      </c>
+      <c r="N22" s="91" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B23" s="64">
         <v>2</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D23" s="66">
+        <v>203</v>
+      </c>
+      <c r="D23" s="65">
         <v>25</v>
       </c>
-      <c r="F23" s="65">
+      <c r="F23" s="64">
         <v>0</v>
       </c>
       <c r="G23" s="9">
@@ -6572,214 +6601,214 @@
       <c r="L23" s="9">
         <v>0</v>
       </c>
-      <c r="M23" s="66">
-        <v>0</v>
-      </c>
-      <c r="N23" s="93" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B24" s="65">
+      <c r="M23" s="65">
+        <v>0</v>
+      </c>
+      <c r="N23" s="92" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B24" s="64">
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="66">
+      <c r="D24" s="65">
         <v>12</v>
       </c>
-      <c r="F24" s="83">
-        <v>50</v>
-      </c>
-      <c r="G24" s="84">
-        <v>50</v>
-      </c>
-      <c r="H24" s="84">
-        <v>50</v>
-      </c>
-      <c r="I24" s="84">
-        <v>50</v>
-      </c>
-      <c r="J24" s="84">
-        <v>50</v>
-      </c>
-      <c r="K24" s="84">
-        <v>50</v>
-      </c>
-      <c r="L24" s="84">
-        <v>50</v>
-      </c>
-      <c r="M24" s="99">
-        <v>50</v>
-      </c>
-      <c r="N24" s="93" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B25" s="65">
+      <c r="F24" s="82">
+        <v>25</v>
+      </c>
+      <c r="G24" s="83">
+        <v>25</v>
+      </c>
+      <c r="H24" s="83">
+        <v>25</v>
+      </c>
+      <c r="I24" s="83">
+        <v>25</v>
+      </c>
+      <c r="J24" s="83">
+        <v>25</v>
+      </c>
+      <c r="K24" s="83">
+        <v>25</v>
+      </c>
+      <c r="L24" s="83">
+        <v>25</v>
+      </c>
+      <c r="M24" s="98">
+        <v>25</v>
+      </c>
+      <c r="N24" s="92" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B25" s="64">
         <v>4</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="66">
+      <c r="D25" s="65">
         <v>12</v>
       </c>
-      <c r="F25" s="65">
-        <v>0</v>
-      </c>
-      <c r="G25" s="84">
-        <v>50</v>
-      </c>
-      <c r="H25" s="84">
-        <v>50</v>
-      </c>
-      <c r="I25" s="84">
-        <v>50</v>
-      </c>
-      <c r="J25" s="84">
-        <v>50</v>
-      </c>
-      <c r="K25" s="84">
-        <v>50</v>
-      </c>
-      <c r="L25" s="84">
-        <v>50</v>
-      </c>
-      <c r="M25" s="99">
-        <v>50</v>
-      </c>
-      <c r="N25" s="93" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B26" s="65">
+      <c r="F25" s="64">
+        <v>0</v>
+      </c>
+      <c r="G25" s="83">
+        <v>25</v>
+      </c>
+      <c r="H25" s="83">
+        <v>25</v>
+      </c>
+      <c r="I25" s="83">
+        <v>25</v>
+      </c>
+      <c r="J25" s="83">
+        <v>25</v>
+      </c>
+      <c r="K25" s="83">
+        <v>25</v>
+      </c>
+      <c r="L25" s="83">
+        <v>25</v>
+      </c>
+      <c r="M25" s="98">
+        <v>25</v>
+      </c>
+      <c r="N25" s="92" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B26" s="64">
         <v>5</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="66">
+      <c r="D26" s="65">
         <v>52</v>
       </c>
-      <c r="F26" s="65">
-        <v>0</v>
-      </c>
-      <c r="G26" s="84">
-        <v>50</v>
+      <c r="F26" s="64">
+        <v>0</v>
+      </c>
+      <c r="G26" s="83">
+        <v>25</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
       </c>
-      <c r="I26" s="84">
-        <v>50</v>
-      </c>
-      <c r="J26" s="84">
-        <v>50</v>
-      </c>
-      <c r="K26" s="84">
-        <v>50</v>
-      </c>
-      <c r="L26" s="84">
-        <v>50</v>
-      </c>
-      <c r="M26" s="99">
-        <v>50</v>
-      </c>
-      <c r="N26" s="93" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B27" s="65">
+      <c r="I26" s="83">
+        <v>25</v>
+      </c>
+      <c r="J26" s="83">
+        <v>25</v>
+      </c>
+      <c r="K26" s="83">
+        <v>25</v>
+      </c>
+      <c r="L26" s="83">
+        <v>25</v>
+      </c>
+      <c r="M26" s="98">
+        <v>25</v>
+      </c>
+      <c r="N26" s="92" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B27" s="64">
         <v>6</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="66">
+      <c r="D27" s="65">
         <v>92</v>
       </c>
-      <c r="F27" s="65">
-        <v>0</v>
-      </c>
-      <c r="G27" s="84">
-        <v>50</v>
+      <c r="F27" s="64">
+        <v>0</v>
+      </c>
+      <c r="G27" s="83">
+        <v>25</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
       </c>
-      <c r="I27" s="84">
-        <v>50</v>
+      <c r="I27" s="83">
+        <v>25</v>
       </c>
       <c r="J27" s="9">
         <v>0</v>
       </c>
-      <c r="K27" s="84">
-        <v>50</v>
-      </c>
-      <c r="L27" s="84">
-        <v>50</v>
-      </c>
-      <c r="M27" s="99">
-        <v>50</v>
-      </c>
-      <c r="N27" s="93" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B28" s="65">
+      <c r="K27" s="83">
+        <v>25</v>
+      </c>
+      <c r="L27" s="83">
+        <v>25</v>
+      </c>
+      <c r="M27" s="98">
+        <v>25</v>
+      </c>
+      <c r="N27" s="92" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B28" s="64">
         <v>7</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="66">
+      <c r="D28" s="65">
         <v>132</v>
       </c>
-      <c r="F28" s="65">
-        <v>0</v>
-      </c>
-      <c r="G28" s="84">
-        <v>50</v>
+      <c r="F28" s="64">
+        <v>0</v>
+      </c>
+      <c r="G28" s="83">
+        <v>25</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
       </c>
-      <c r="I28" s="84">
-        <v>50</v>
+      <c r="I28" s="83">
+        <v>25</v>
       </c>
       <c r="J28" s="9">
         <v>0</v>
       </c>
-      <c r="K28" s="84">
-        <v>50</v>
+      <c r="K28" s="83">
+        <v>25</v>
       </c>
       <c r="L28" s="9">
         <v>0</v>
       </c>
-      <c r="M28" s="99">
-        <v>50</v>
-      </c>
-      <c r="N28" s="93" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B29" s="65">
+      <c r="M28" s="98">
+        <v>25</v>
+      </c>
+      <c r="N28" s="92" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B29" s="64">
         <v>8</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="66">
+      <c r="D29" s="65">
         <v>12</v>
       </c>
-      <c r="F29" s="65">
+      <c r="F29" s="64">
         <v>0</v>
       </c>
       <c r="G29" s="9">
@@ -6800,62 +6829,62 @@
       <c r="L29" s="9">
         <v>0</v>
       </c>
-      <c r="M29" s="66">
-        <v>0</v>
-      </c>
-      <c r="N29" s="93" t="s">
+      <c r="M29" s="65">
+        <v>0</v>
+      </c>
+      <c r="N29" s="92" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B30" s="64">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="65">
+        <v>75</v>
+      </c>
+      <c r="F30" s="64">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0</v>
+      </c>
+      <c r="M30" s="65">
+        <v>0</v>
+      </c>
+      <c r="N30" s="92" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B30" s="65">
-        <v>9</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D30" s="66">
-        <v>75</v>
-      </c>
-      <c r="F30" s="65">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9">
-        <v>0</v>
-      </c>
-      <c r="H30" s="9">
-        <v>0</v>
-      </c>
-      <c r="I30" s="9">
-        <v>0</v>
-      </c>
-      <c r="J30" s="9">
-        <v>0</v>
-      </c>
-      <c r="K30" s="9">
-        <v>0</v>
-      </c>
-      <c r="L30" s="9">
-        <v>0</v>
-      </c>
-      <c r="M30" s="66">
-        <v>0</v>
-      </c>
-      <c r="N30" s="93" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B31" s="65">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B31" s="64">
         <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="66">
+      <c r="D31" s="65">
         <v>12</v>
       </c>
-      <c r="F31" s="100">
+      <c r="F31" s="99">
         <v>75</v>
       </c>
       <c r="G31" s="9">
@@ -6876,30 +6905,30 @@
       <c r="L31" s="9">
         <v>0</v>
       </c>
-      <c r="M31" s="66">
-        <v>0</v>
-      </c>
-      <c r="N31" s="93" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B32" s="65">
+      <c r="M31" s="65">
+        <v>0</v>
+      </c>
+      <c r="N31" s="92" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B32" s="64">
         <v>11</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="66">
+      <c r="D32" s="65">
         <v>52</v>
       </c>
-      <c r="F32" s="100">
+      <c r="F32" s="99">
         <v>75</v>
       </c>
       <c r="G32" s="9">
         <v>0</v>
       </c>
-      <c r="H32" s="97">
+      <c r="H32" s="96">
         <v>75</v>
       </c>
       <c r="I32" s="9">
@@ -6914,36 +6943,36 @@
       <c r="L32" s="9">
         <v>0</v>
       </c>
-      <c r="M32" s="66">
-        <v>0</v>
-      </c>
-      <c r="N32" s="93" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B33" s="65">
+      <c r="M32" s="65">
+        <v>0</v>
+      </c>
+      <c r="N32" s="92" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B33" s="64">
         <v>12</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="66">
+      <c r="D33" s="65">
         <v>92</v>
       </c>
-      <c r="F33" s="100">
+      <c r="F33" s="99">
         <v>75</v>
       </c>
       <c r="G33" s="9">
         <v>0</v>
       </c>
-      <c r="H33" s="97">
+      <c r="H33" s="96">
         <v>75</v>
       </c>
       <c r="I33" s="9">
         <v>0</v>
       </c>
-      <c r="J33" s="97">
+      <c r="J33" s="96">
         <v>75</v>
       </c>
       <c r="K33" s="9">
@@ -6952,65 +6981,65 @@
       <c r="L33" s="9">
         <v>0</v>
       </c>
-      <c r="M33" s="66">
-        <v>0</v>
-      </c>
-      <c r="N33" s="93" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="67">
+      <c r="M33" s="65">
+        <v>0</v>
+      </c>
+      <c r="N33" s="92" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B34" s="66">
         <v>13</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="69">
+      <c r="D34" s="68">
         <v>132</v>
       </c>
-      <c r="F34" s="101">
+      <c r="F34" s="100">
         <v>75</v>
       </c>
-      <c r="G34" s="73">
-        <v>0</v>
-      </c>
-      <c r="H34" s="102">
+      <c r="G34" s="72">
+        <v>0</v>
+      </c>
+      <c r="H34" s="101">
         <v>75</v>
       </c>
-      <c r="I34" s="73">
-        <v>0</v>
-      </c>
-      <c r="J34" s="102">
+      <c r="I34" s="72">
+        <v>0</v>
+      </c>
+      <c r="J34" s="101">
         <v>75</v>
       </c>
-      <c r="K34" s="73">
-        <v>0</v>
-      </c>
-      <c r="L34" s="102">
+      <c r="K34" s="72">
+        <v>0</v>
+      </c>
+      <c r="L34" s="101">
         <v>75</v>
       </c>
-      <c r="M34" s="69">
-        <v>0</v>
-      </c>
-      <c r="N34" s="103" t="s">
-        <v>230</v>
+      <c r="M34" s="68">
+        <v>0</v>
+      </c>
+      <c r="N34" s="102" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="N19:N21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A04715-4FC1-4984-9BEE-262662D7AA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A8592F-3AE8-40D3-836F-67D08AD7B212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -1039,7 +1039,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1049,12 +1049,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1934,6 +1928,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1941,15 +1944,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1976,22 +1970,22 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2000,20 +1994,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2030,65 +2018,71 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3831,14 +3825,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="129" t="s">
         <v>214</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3890,14 +3884,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="113" t="s">
+      <c r="E7" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="113"/>
-      <c r="G7" s="113"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3909,14 +3903,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="114" t="s">
+      <c r="E8" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="114"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="114"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3928,14 +3922,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="130" t="s">
         <v>198</v>
       </c>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="108"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="131"/>
+      <c r="J9" s="132"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3947,14 +3941,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="114" t="s">
+      <c r="E10" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="114"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="114"/>
-      <c r="I10" s="114"/>
-      <c r="J10" s="114"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3966,14 +3960,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="109" t="s">
+      <c r="E11" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="111"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3985,14 +3979,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="114" t="s">
+      <c r="E12" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="114"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="114"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -4004,14 +3998,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="109" t="s">
+      <c r="E13" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="111"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="109"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -4031,13 +4025,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="113" t="s">
+      <c r="F17" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="113"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="113"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="111"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -4052,13 +4046,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="115" t="s">
+      <c r="F18" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="133"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4073,13 +4067,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="115" t="s">
+      <c r="F19" s="133" t="s">
         <v>229</v>
       </c>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="133"/>
+      <c r="J19" s="133"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -4094,13 +4088,13 @@
       <c r="E20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F20" s="114" t="s">
+      <c r="F20" s="105" t="s">
         <v>145</v>
       </c>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="114"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -4115,13 +4109,13 @@
       <c r="E21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="114" t="s">
+      <c r="F21" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4136,13 +4130,13 @@
       <c r="E22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="114" t="s">
+      <c r="F22" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="114"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4157,13 +4151,13 @@
       <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="114" t="s">
+      <c r="F23" s="105" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="114"/>
-      <c r="H23" s="114"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="114"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4178,13 +4172,13 @@
       <c r="E24" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="114" t="s">
+      <c r="F24" s="105" t="s">
         <v>149</v>
       </c>
-      <c r="G24" s="114"/>
-      <c r="H24" s="114"/>
-      <c r="I24" s="114"/>
-      <c r="J24" s="114"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4199,13 +4193,13 @@
       <c r="E25" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="114" t="s">
+      <c r="F25" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="114"/>
-      <c r="H25" s="114"/>
-      <c r="I25" s="114"/>
-      <c r="J25" s="114"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B28" s="5" t="s">
@@ -4214,14 +4208,14 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B29" s="1"/>
-      <c r="C29" s="112" t="s">
+      <c r="C29" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="112"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="112"/>
-      <c r="G29" s="112"/>
-      <c r="H29" s="112"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B30" s="1" t="s">
@@ -4250,7 +4244,7 @@
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="117" t="s">
+      <c r="C31" s="106" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -4265,7 +4259,7 @@
       <c r="G31" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="117" t="s">
+      <c r="H31" s="106" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4273,7 +4267,7 @@
       <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="117"/>
+      <c r="C32" s="106"/>
       <c r="D32" s="9" t="s">
         <v>14</v>
       </c>
@@ -4286,13 +4280,13 @@
       <c r="G32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="117"/>
+      <c r="H32" s="106"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="117"/>
+      <c r="C33" s="106"/>
       <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
@@ -4305,13 +4299,13 @@
       <c r="G33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H33" s="117"/>
+      <c r="H33" s="106"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="117"/>
+      <c r="C34" s="106"/>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
@@ -4324,13 +4318,13 @@
       <c r="G34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="117"/>
+      <c r="H34" s="106"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="117"/>
+      <c r="C35" s="106"/>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
@@ -4343,13 +4337,13 @@
       <c r="G35" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="117"/>
+      <c r="H35" s="106"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="117"/>
+      <c r="C36" s="106"/>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
@@ -4362,13 +4356,13 @@
       <c r="G36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="117"/>
+      <c r="H36" s="106"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="117"/>
+      <c r="C37" s="106"/>
       <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4381,13 +4375,13 @@
       <c r="G37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="117"/>
+      <c r="H37" s="106"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="117"/>
+      <c r="C38" s="106"/>
       <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
@@ -4400,13 +4394,13 @@
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="117"/>
+      <c r="H38" s="106"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="117"/>
+      <c r="C39" s="106"/>
       <c r="D39" s="10" t="s">
         <v>14</v>
       </c>
@@ -4419,7 +4413,7 @@
       <c r="G39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H39" s="117"/>
+      <c r="H39" s="106"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.45">
       <c r="C40" s="11"/>
@@ -4443,16 +4437,16 @@
         <v>47</v>
       </c>
       <c r="E43" s="13"/>
-      <c r="F43" s="116" t="s">
+      <c r="F43" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="116"/>
-      <c r="H43" s="116"/>
-      <c r="I43" s="116"/>
-      <c r="J43" s="116"/>
-      <c r="K43" s="116"/>
-      <c r="L43" s="116"/>
-      <c r="M43" s="116"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="104"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B44" s="9" t="s">
@@ -4719,12 +4713,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="C31:C39"/>
-    <mergeCell ref="H31:H39"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
@@ -4740,6 +4728,12 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="C31:C39"/>
+    <mergeCell ref="H31:H39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4759,28 +4753,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="112" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="116" t="s">
+      <c r="D2" s="104" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="116" t="s">
+      <c r="E2" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116" t="s">
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="119"/>
-      <c r="D3" s="116"/>
+      <c r="B3" s="113"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="7" t="s">
         <v>138</v>
       </c>
@@ -5820,7 +5814,7 @@
         <v>159</v>
       </c>
       <c r="F6" s="50"/>
-      <c r="G6" s="104" t="s">
+      <c r="G6" s="128" t="s">
         <v>240</v>
       </c>
       <c r="H6" s="32" t="s">
@@ -5962,35 +5956,35 @@
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="123" t="s">
+      <c r="B3" s="117" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="126" t="s">
+      <c r="C3" s="120" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="127" t="s">
+      <c r="D3" s="122" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="123" t="s">
+      <c r="F3" s="117" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126" t="s">
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120" t="s">
         <v>97</v>
       </c>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="120" t="s">
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="114" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="124"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="128"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="123"/>
       <c r="F4" s="63" t="s">
         <v>138</v>
       </c>
@@ -6015,12 +6009,12 @@
       <c r="M4" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="N4" s="121"/>
+      <c r="N4" s="115"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="131"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="133"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="124"/>
       <c r="F5" s="73">
         <v>1</v>
       </c>
@@ -6052,7 +6046,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="122"/>
+      <c r="N5" s="116"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="69">
@@ -6440,35 +6434,35 @@
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="123" t="s">
+      <c r="B19" s="117" t="s">
         <v>199</v>
       </c>
-      <c r="C19" s="126" t="s">
+      <c r="C19" s="120" t="s">
         <v>201</v>
       </c>
-      <c r="D19" s="127" t="s">
+      <c r="D19" s="122" t="s">
         <v>202</v>
       </c>
-      <c r="F19" s="123" t="s">
+      <c r="F19" s="117" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="126"/>
-      <c r="H19" s="126"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="126" t="s">
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="120" t="s">
         <v>97</v>
       </c>
-      <c r="K19" s="126"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="130"/>
-      <c r="N19" s="120" t="s">
+      <c r="K19" s="120"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="125"/>
+      <c r="N19" s="114" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="124"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="128"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="123"/>
       <c r="F20" s="63" t="s">
         <v>138</v>
       </c>
@@ -6493,12 +6487,12 @@
       <c r="M20" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="N20" s="121"/>
+      <c r="N20" s="115"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="125"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="129"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="127"/>
       <c r="F21" s="93">
         <v>12</v>
       </c>
@@ -6530,7 +6524,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="122"/>
+      <c r="N21" s="116"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="88">
@@ -7028,18 +7022,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="J19:M19"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A8592F-3AE8-40D3-836F-67D08AD7B212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650E12E2-5D5D-4C76-871F-E1DA29146CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="218">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -302,30 +302,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3. Example Frames</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scenario</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Checksum </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LEN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Current 50mA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Protocol Fields</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0 ~ 128</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -334,78 +310,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0xA6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LED 전류 설정 (1mA 단위 조절)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0x32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0xD9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Current 10mA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0xB1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Current 128mA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bar #1 On</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0xB7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bar #19 Off</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block #5 On</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block All Off</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0xEB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>수행할 명령 코드, "2. Command 목록" 참조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -418,10 +326,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4. Control B'D &lt;==&gt; LED Bar Mapping ("xc xd mapping" sheet 참조할것)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>XD #2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -920,10 +824,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5. Example Screenshot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1) RS232 --&gt; Control B'D</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -961,6 +861,14 @@
   </si>
   <si>
     <t>TP65 (UART 파형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Control B'D &lt;==&gt; LED Bar Mapping ("xc xd mapping" sheet 참조할것)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Example Screenshot</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -972,7 +880,7 @@
     <numFmt numFmtId="176" formatCode="&quot;B-&quot;0"/>
     <numFmt numFmtId="177" formatCode="&quot;Blk-&quot;0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1003,13 +911,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1683,7 +1584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1706,15 +1607,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1727,7 +1622,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1766,13 +1661,13 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1994,29 +1889,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2039,50 +1931,32 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2118,14 +1992,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>31432</xdr:rowOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>28258</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2168,7 +2042,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2239,7 +2113,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2312,14 +2186,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>31432</xdr:rowOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>28257</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2362,7 +2236,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2433,7 +2307,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2506,13 +2380,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2563,13 +2437,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1590675</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2620,7 +2494,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -2703,7 +2577,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>537156</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -2786,14 +2660,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>151</xdr:row>
-      <xdr:rowOff>31432</xdr:rowOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>28256</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2836,7 +2710,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2907,7 +2781,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2980,13 +2854,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3037,13 +2911,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1581150</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3094,7 +2968,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>136</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -3177,7 +3051,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>527629</xdr:colOff>
-      <xdr:row>136</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -3805,7 +3679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M122"/>
+  <dimension ref="B2:M108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="6" customWidth="1"/>
@@ -3825,14 +3699,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="129" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
+      <c r="B3" s="102" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3884,14 +3758,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="111" t="s">
+      <c r="E7" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3903,14 +3777,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="105" t="s">
+      <c r="E8" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3922,14 +3796,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="130" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
-      <c r="J9" s="132"/>
+      <c r="E9" s="103" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="105"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3941,14 +3815,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="105" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
+      <c r="E10" s="107" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="107"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="107"/>
+      <c r="J10" s="107"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3960,14 +3834,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="107" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
+      <c r="E11" s="103" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="105"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3979,14 +3853,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="105" t="s">
+      <c r="E12" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="107"/>
+      <c r="J12" s="107"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3998,21 +3872,21 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="107" t="s">
+      <c r="E13" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="109"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
@@ -4025,15 +3899,15 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="111" t="s">
+      <c r="F17" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
@@ -4046,15 +3920,15 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="133" t="s">
-        <v>235</v>
-      </c>
-      <c r="G18" s="133"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="133"/>
-      <c r="J18" s="133"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="F18" s="107" t="s">
+        <v>210</v>
+      </c>
+      <c r="G18" s="107"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="107"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
@@ -4067,36 +3941,36 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="133" t="s">
-        <v>229</v>
-      </c>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
-      <c r="J19" s="133"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="F19" s="107" t="s">
+        <v>205</v>
+      </c>
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F20" s="105" t="s">
-        <v>145</v>
-      </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F20" s="107" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
@@ -4107,17 +3981,17 @@
         <v>5</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="105" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+      <c r="F21" s="107" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
@@ -4128,17 +4002,17 @@
         <v>5</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="105" t="s">
-        <v>147</v>
-      </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+        <v>68</v>
+      </c>
+      <c r="F22" s="107" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" s="107"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
@@ -4149,17 +4023,17 @@
         <v>5</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" s="105"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="105"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+        <v>68</v>
+      </c>
+      <c r="F23" s="107" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="107"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>22</v>
       </c>
@@ -4170,17 +4044,17 @@
         <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F24" s="105" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F24" s="107" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>23</v>
       </c>
@@ -4191,533 +4065,322 @@
         <v>5</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F25" s="105" t="s">
-        <v>150</v>
-      </c>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F25" s="107" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="107"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B28" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B29" s="1"/>
-      <c r="C29" s="110" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="110"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B30" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>0</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="108" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="106" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H31" s="106" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B32" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="106"/>
-      <c r="D32" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H32" s="106"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B33" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="106"/>
-      <c r="D33" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H33" s="106"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B34" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="106"/>
-      <c r="D34" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="106"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B35" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="106"/>
-      <c r="D35" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" s="106"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="106"/>
-      <c r="D36" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H36" s="106"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B37" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="106"/>
-      <c r="D37" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H37" s="106"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B38" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" s="106"/>
-      <c r="D38" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H38" s="106"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="106"/>
-      <c r="D39" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="H39" s="106"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="C40" s="11"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B42" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B43" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="104" t="s">
-        <v>47</v>
-      </c>
-      <c r="G43" s="104"/>
-      <c r="H43" s="104"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="104"/>
-      <c r="K43" s="104"/>
-      <c r="L43" s="104"/>
-      <c r="M43" s="104"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B44" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C44" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="M30" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B31" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="I44" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="K44" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="L44" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="M44" s="19" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C45" s="14" t="s">
+      <c r="D31" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="J31" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="M31" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="20"/>
-      <c r="F45" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="I45" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="J45" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="K45" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="L45" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="M45" s="24" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B46" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46" s="14" t="s">
+      <c r="D32" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B47" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C47" s="14" t="s">
+      <c r="D33" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B48" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C48" s="14" t="s">
+      <c r="D34" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="D35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B36" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B49" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B50" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="14" t="s">
+      <c r="D36" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B37" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B51" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" s="14" t="s">
+      <c r="D37" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B38" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-    </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B52" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="14" t="s">
+      <c r="D38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B53" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="14" t="s">
+      <c r="D39" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B40" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B54" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="9" t="s">
+      <c r="D40" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B57" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B58" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B90" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B122" s="6" t="s">
-        <v>233</v>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B43" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B44" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B76" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B108" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="18">
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
     <mergeCell ref="E13:J13"/>
-    <mergeCell ref="C29:H29"/>
     <mergeCell ref="F17:J17"/>
     <mergeCell ref="F24:J24"/>
     <mergeCell ref="F23:J23"/>
@@ -4728,12 +4391,6 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F43:M43"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="C31:C39"/>
-    <mergeCell ref="H31:H39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4746,896 +4403,896 @@
   <dimension ref="B2:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.58203125" style="11" customWidth="1"/>
-    <col min="2" max="4" width="9" style="11"/>
-    <col min="5" max="5" width="9" style="11" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="2.58203125" style="9" customWidth="1"/>
+    <col min="2" max="4" width="9" style="9"/>
+    <col min="5" max="5" width="9" style="9" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="112" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" s="104" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="104" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104" t="s">
-        <v>97</v>
-      </c>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
+      <c r="B2" s="109" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="108" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="108" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="113"/>
-      <c r="D3" s="104"/>
+      <c r="B3" s="110"/>
+      <c r="D3" s="108"/>
       <c r="E3" s="7" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="L3" s="30" t="s">
-        <v>141</v>
+        <v>116</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B4" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="24">
         <v>1</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="25">
         <f t="shared" ref="F4:L13" si="0">E4+20</f>
         <v>21</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="25">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="25">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="25">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="25">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="25">
         <f t="shared" ref="K4:K23" si="1">J4+20</f>
         <v>121</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="26">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B5" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="29" t="s">
+      <c r="B5" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="24">
         <v>2</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="25">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="25">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="25">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="25">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="25">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="25">
         <f t="shared" si="1"/>
         <v>122</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="26">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B6" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="29" t="s">
+      <c r="B6" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="24">
         <v>3</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="25">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="25">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="25">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="25">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="25">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="26">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B7" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="29" t="s">
+      <c r="B7" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="24">
         <v>4</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="25">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="25">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="25">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="25">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="25">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="25">
         <f t="shared" si="1"/>
         <v>124</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="26">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B8" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="29" t="s">
+      <c r="B8" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="24">
         <v>5</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="25">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="25">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="25">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="25">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="25">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="25">
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="26">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="29" t="s">
+      <c r="B9" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="26">
+      <c r="D9" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="24">
         <v>6</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="25">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="25">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="25">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="25">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="25">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="25">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="26">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="29" t="s">
+      <c r="B10" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="26">
+      <c r="D10" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="24">
         <v>7</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="25">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="25">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="25">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="25">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="25">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="25">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="26">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B11" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="29" t="s">
+      <c r="B11" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" s="26">
+      <c r="D11" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="24">
         <v>8</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="25">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="25">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="25">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="25">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="25">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="25">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="26">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B12" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="29" t="s">
+      <c r="B12" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="26">
+      <c r="D12" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="24">
         <v>9</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="25">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="25">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="25">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="25">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="25">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="25">
         <f t="shared" si="1"/>
         <v>129</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="26">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B13" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" s="29" t="s">
+      <c r="B13" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="26">
+      <c r="D13" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="24">
         <v>10</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="25">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="25">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="25">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="25">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="25">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="25">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="26">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B14" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="29" t="s">
+      <c r="B14" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="26">
+      <c r="D14" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="24">
         <v>11</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="25">
         <f t="shared" ref="F14:L23" si="2">E14+20</f>
         <v>31</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="25">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="25">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="25">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="25">
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="25">
         <f t="shared" si="1"/>
         <v>131</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="26">
         <f t="shared" si="2"/>
         <v>151</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B15" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="29" t="s">
+      <c r="B15" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="26">
+      <c r="D15" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="24">
         <v>12</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="25">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="25">
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="25">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="25">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="25">
         <f t="shared" si="2"/>
         <v>112</v>
       </c>
-      <c r="K15" s="27">
+      <c r="K15" s="25">
         <f t="shared" si="1"/>
         <v>132</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="26">
         <f t="shared" si="2"/>
         <v>152</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B16" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="29" t="s">
+      <c r="B16" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="26">
+      <c r="D16" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="24">
         <v>13</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="25">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="25">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="25">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="25">
         <f t="shared" si="2"/>
         <v>93</v>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="25">
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="25">
         <f t="shared" si="1"/>
         <v>133</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="26">
         <f t="shared" si="2"/>
         <v>153</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B17" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="29" t="s">
+      <c r="B17" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" s="26">
+      <c r="D17" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="24">
         <v>14</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="25">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="25">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="25">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="25">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="25">
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="25">
         <f t="shared" si="1"/>
         <v>134</v>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="26">
         <f t="shared" si="2"/>
         <v>154</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B18" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="B18" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="26">
+      <c r="D18" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="24">
         <v>15</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="25">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="25">
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="25">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="25">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="J18" s="27">
+      <c r="J18" s="25">
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
-      <c r="K18" s="27">
+      <c r="K18" s="25">
         <f t="shared" si="1"/>
         <v>135</v>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="26">
         <f t="shared" si="2"/>
         <v>155</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B19" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" s="29" t="s">
+      <c r="B19" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="26">
+      <c r="D19" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="24">
         <v>16</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="25">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="25">
         <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="25">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="25">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
-      <c r="J19" s="27">
+      <c r="J19" s="25">
         <f t="shared" si="2"/>
         <v>116</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="25">
         <f t="shared" si="1"/>
         <v>136</v>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="26">
         <f t="shared" si="2"/>
         <v>156</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B20" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="29" t="s">
+      <c r="B20" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="24">
         <v>17</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="25">
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="25">
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="25">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="25">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="25">
         <f t="shared" si="2"/>
         <v>117</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="25">
         <f t="shared" si="1"/>
         <v>137</v>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="26">
         <f t="shared" si="2"/>
         <v>157</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B21" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="29" t="s">
+      <c r="B21" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="24">
         <v>18</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="25">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="25">
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="25">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="25">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
-      <c r="J21" s="27">
+      <c r="J21" s="25">
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
-      <c r="K21" s="27">
+      <c r="K21" s="25">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="26">
         <f t="shared" si="2"/>
         <v>158</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B22" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="29" t="s">
+      <c r="B22" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="24">
         <v>19</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="25">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="25">
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="25">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="25">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="J22" s="27">
+      <c r="J22" s="25">
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K22" s="25">
         <f t="shared" si="1"/>
         <v>139</v>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="26">
         <f t="shared" si="2"/>
         <v>159</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B23" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="29" t="s">
+      <c r="B23" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="24">
         <v>20</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="25">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="25">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="25">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="25">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="25">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="K23" s="27">
+      <c r="K23" s="25">
         <f t="shared" si="1"/>
         <v>140</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="26">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
@@ -5658,243 +5315,243 @@
   <dimension ref="B1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.58203125" style="31" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.75" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.83203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.75" style="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.08203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.58203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.75" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.25" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="31"/>
-    <col min="14" max="14" width="9.25" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="31"/>
+    <col min="1" max="1" width="2.58203125" style="29" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.75" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.75" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.08203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.58203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.75" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.25" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="29"/>
+    <col min="14" max="14" width="9.25" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="42" t="s">
+      <c r="B2" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H2" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="J2" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B3" s="58">
+        <v>1</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="45"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B4" s="59">
+        <v>2</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="E4" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>212</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="K4" s="53"/>
+      <c r="L4" s="56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B5" s="59">
+        <v>3</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="E2" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="F2" s="38" t="s">
+      <c r="H5" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="G2" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="H2" s="37" t="s">
+      <c r="I5" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="K5" s="53"/>
+      <c r="L5" s="56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B6" s="59">
+        <v>4</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="48"/>
+      <c r="G6" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B7" s="59">
+        <v>5</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="I2" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="K2" s="53" t="s">
+      <c r="D7" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="30"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="K7" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="L7" s="56" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="60">
+        <v>6</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="L2" s="41" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="60">
-        <v>1</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="57" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B4" s="61">
-        <v>2</v>
-      </c>
-      <c r="C4" s="44" t="s">
+      <c r="D8" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="F4" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="G4" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="K4" s="55"/>
-      <c r="L4" s="58" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B5" s="61">
-        <v>3</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>171</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="F5" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="I5" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="J5" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="K5" s="55"/>
-      <c r="L5" s="58" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B6" s="61">
-        <v>4</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="128" t="s">
-        <v>240</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="58" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B7" s="61">
-        <v>5</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="K7" s="55" t="s">
-        <v>234</v>
-      </c>
-      <c r="L7" s="58" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="62">
-        <v>6</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="G8" s="103" t="s">
-        <v>236</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="59" t="s">
-        <v>162</v>
+      <c r="G8" s="101" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="57" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" s="31" t="s">
-        <v>238</v>
+      <c r="B10" s="29" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B11" s="31" t="s">
-        <v>239</v>
+      <c r="B11" s="29" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -5919,13 +5576,13 @@
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="H2" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="W2" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -5940,1100 +5597,1100 @@
   <dimension ref="B2:N34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.58203125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="8.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.58203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.83203125" style="11" customWidth="1"/>
-    <col min="6" max="13" width="6.08203125" style="11" customWidth="1"/>
-    <col min="14" max="14" width="54.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="2.58203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.58203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" style="9" customWidth="1"/>
+    <col min="6" max="13" width="6.08203125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="54.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="6" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="117" t="s">
-        <v>199</v>
-      </c>
-      <c r="C3" s="120" t="s">
-        <v>201</v>
-      </c>
-      <c r="D3" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="F3" s="117" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120" t="s">
-        <v>97</v>
-      </c>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="114" t="s">
-        <v>200</v>
+      <c r="B3" s="114" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" s="117" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" s="114" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="117"/>
+      <c r="L3" s="117"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="111" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="118"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="123"/>
-      <c r="F4" s="63" t="s">
-        <v>138</v>
+      <c r="B4" s="115"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="119"/>
+      <c r="F4" s="61" t="s">
+        <v>114</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="M4" s="75" t="s">
-        <v>141</v>
-      </c>
-      <c r="N4" s="115"/>
+        <v>116</v>
+      </c>
+      <c r="M4" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="N4" s="112"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="119"/>
-      <c r="C5" s="121"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="123"/>
       <c r="D5" s="124"/>
-      <c r="F5" s="73">
+      <c r="F5" s="71">
         <v>1</v>
       </c>
-      <c r="G5" s="74">
+      <c r="G5" s="72">
         <f t="shared" ref="G5:M5" si="0">F5+20</f>
         <v>21</v>
       </c>
-      <c r="H5" s="74">
+      <c r="H5" s="72">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="I5" s="74">
+      <c r="I5" s="72">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="J5" s="74">
+      <c r="J5" s="72">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="K5" s="74">
+      <c r="K5" s="72">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="L5" s="74">
+      <c r="L5" s="72">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="M5" s="76">
+      <c r="M5" s="74">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="116"/>
+      <c r="N5" s="113"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B6" s="69">
+      <c r="B6" s="67">
         <v>1</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="71">
-        <v>0</v>
-      </c>
-      <c r="F6" s="69">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0</v>
-      </c>
-      <c r="H6" s="22">
-        <v>0</v>
-      </c>
-      <c r="I6" s="22">
-        <v>0</v>
-      </c>
-      <c r="J6" s="22">
-        <v>0</v>
-      </c>
-      <c r="K6" s="22">
-        <v>0</v>
-      </c>
-      <c r="L6" s="22">
-        <v>0</v>
-      </c>
-      <c r="M6" s="21">
-        <v>0</v>
-      </c>
-      <c r="N6" s="79" t="s">
-        <v>206</v>
+      <c r="D6" s="69">
+        <v>0</v>
+      </c>
+      <c r="F6" s="67">
+        <v>0</v>
+      </c>
+      <c r="G6" s="20">
+        <v>0</v>
+      </c>
+      <c r="H6" s="20">
+        <v>0</v>
+      </c>
+      <c r="I6" s="20">
+        <v>0</v>
+      </c>
+      <c r="J6" s="20">
+        <v>0</v>
+      </c>
+      <c r="K6" s="20">
+        <v>0</v>
+      </c>
+      <c r="L6" s="20">
+        <v>0</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0</v>
+      </c>
+      <c r="N6" s="77" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B7" s="64">
+      <c r="B7" s="62">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D7" s="65">
+        <v>179</v>
+      </c>
+      <c r="D7" s="63">
         <v>50</v>
       </c>
-      <c r="F7" s="64">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="77">
-        <v>0</v>
-      </c>
-      <c r="N7" s="80" t="s">
-        <v>205</v>
+      <c r="F7" s="62">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="75">
+        <v>0</v>
+      </c>
+      <c r="N7" s="78" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B8" s="64">
+      <c r="B8" s="62">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="65">
+      <c r="D8" s="63">
         <v>1</v>
       </c>
-      <c r="F8" s="82">
+      <c r="F8" s="80">
         <v>50</v>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="81">
         <v>50</v>
       </c>
-      <c r="H8" s="83">
+      <c r="H8" s="81">
         <v>50</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="81">
         <v>50</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="81">
         <v>50</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="81">
         <v>50</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="81">
         <v>50</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="82">
         <v>50</v>
       </c>
-      <c r="N8" s="80" t="s">
-        <v>207</v>
+      <c r="N8" s="78" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B9" s="64">
+      <c r="B9" s="62">
         <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="65">
+      <c r="D9" s="63">
         <v>1</v>
       </c>
-      <c r="F9" s="64">
-        <v>0</v>
-      </c>
-      <c r="G9" s="83">
+      <c r="F9" s="62">
+        <v>0</v>
+      </c>
+      <c r="G9" s="81">
         <v>50</v>
       </c>
-      <c r="H9" s="83">
+      <c r="H9" s="81">
         <v>50</v>
       </c>
-      <c r="I9" s="83">
+      <c r="I9" s="81">
         <v>50</v>
       </c>
-      <c r="J9" s="83">
+      <c r="J9" s="81">
         <v>50</v>
       </c>
-      <c r="K9" s="83">
+      <c r="K9" s="81">
         <v>50</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="81">
         <v>50</v>
       </c>
-      <c r="M9" s="84">
+      <c r="M9" s="82">
         <v>50</v>
       </c>
-      <c r="N9" s="80" t="s">
-        <v>208</v>
+      <c r="N9" s="78" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B10" s="64">
+      <c r="B10" s="62">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="65">
+      <c r="D10" s="63">
         <v>61</v>
       </c>
-      <c r="F10" s="64">
-        <v>0</v>
-      </c>
-      <c r="G10" s="83">
+      <c r="F10" s="62">
+        <v>0</v>
+      </c>
+      <c r="G10" s="81">
         <v>50</v>
       </c>
-      <c r="H10" s="83">
+      <c r="H10" s="81">
         <v>50</v>
       </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="83">
+      <c r="I10" s="8">
+        <v>0</v>
+      </c>
+      <c r="J10" s="81">
         <v>50</v>
       </c>
-      <c r="K10" s="83">
+      <c r="K10" s="81">
         <v>50</v>
       </c>
-      <c r="L10" s="83">
+      <c r="L10" s="81">
         <v>50</v>
       </c>
-      <c r="M10" s="84">
+      <c r="M10" s="82">
         <v>50</v>
       </c>
-      <c r="N10" s="80" t="s">
-        <v>209</v>
+      <c r="N10" s="78" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B11" s="64">
+      <c r="B11" s="62">
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="65">
-        <v>0</v>
-      </c>
-      <c r="F11" s="64">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9">
-        <v>0</v>
-      </c>
-      <c r="M11" s="77">
-        <v>0</v>
-      </c>
-      <c r="N11" s="80" t="s">
-        <v>210</v>
+      <c r="D11" s="63">
+        <v>0</v>
+      </c>
+      <c r="F11" s="62">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="75">
+        <v>0</v>
+      </c>
+      <c r="N11" s="78" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B12" s="64">
+      <c r="B12" s="62">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="63">
         <v>81</v>
       </c>
-      <c r="F12" s="64">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="83">
+      <c r="F12" s="62">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="81">
         <v>50</v>
       </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0</v>
-      </c>
-      <c r="M12" s="77">
-        <v>0</v>
-      </c>
-      <c r="N12" s="80" t="s">
-        <v>211</v>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="75">
+        <v>0</v>
+      </c>
+      <c r="N12" s="78" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B13" s="64">
+      <c r="B13" s="62">
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D13" s="65">
+        <v>179</v>
+      </c>
+      <c r="D13" s="63">
         <v>100</v>
       </c>
-      <c r="F13" s="64">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>0</v>
-      </c>
-      <c r="I13" s="9">
-        <v>0</v>
-      </c>
-      <c r="J13" s="86">
+      <c r="F13" s="62">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="84">
         <v>100</v>
       </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0</v>
-      </c>
-      <c r="M13" s="77">
-        <v>0</v>
-      </c>
-      <c r="N13" s="80" t="s">
-        <v>204</v>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="75">
+        <v>0</v>
+      </c>
+      <c r="N13" s="78" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B14" s="64">
+      <c r="B14" s="62">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="65">
-        <v>0</v>
-      </c>
-      <c r="F14" s="85">
+      <c r="D14" s="63">
+        <v>0</v>
+      </c>
+      <c r="F14" s="83">
         <v>100</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="84">
         <v>100</v>
       </c>
-      <c r="H14" s="86">
+      <c r="H14" s="84">
         <v>100</v>
       </c>
-      <c r="I14" s="86">
+      <c r="I14" s="84">
         <v>100</v>
       </c>
-      <c r="J14" s="86">
+      <c r="J14" s="84">
         <v>100</v>
       </c>
-      <c r="K14" s="86">
+      <c r="K14" s="84">
         <v>100</v>
       </c>
-      <c r="L14" s="86">
+      <c r="L14" s="84">
         <v>100</v>
       </c>
-      <c r="M14" s="87">
+      <c r="M14" s="85">
         <v>100</v>
       </c>
-      <c r="N14" s="80" t="s">
-        <v>212</v>
+      <c r="N14" s="78" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="66">
+      <c r="B15" s="64">
         <v>10</v>
       </c>
-      <c r="C15" s="67" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" s="68">
-        <v>0</v>
-      </c>
-      <c r="F15" s="66">
-        <v>0</v>
-      </c>
-      <c r="G15" s="72">
-        <v>0</v>
-      </c>
-      <c r="H15" s="72">
-        <v>0</v>
-      </c>
-      <c r="I15" s="72">
-        <v>0</v>
-      </c>
-      <c r="J15" s="72">
-        <v>0</v>
-      </c>
-      <c r="K15" s="72">
-        <v>0</v>
-      </c>
-      <c r="L15" s="72">
-        <v>0</v>
-      </c>
-      <c r="M15" s="78">
-        <v>0</v>
-      </c>
-      <c r="N15" s="81" t="s">
-        <v>213</v>
+      <c r="C15" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="66">
+        <v>0</v>
+      </c>
+      <c r="F15" s="64">
+        <v>0</v>
+      </c>
+      <c r="G15" s="70">
+        <v>0</v>
+      </c>
+      <c r="H15" s="70">
+        <v>0</v>
+      </c>
+      <c r="I15" s="70">
+        <v>0</v>
+      </c>
+      <c r="J15" s="70">
+        <v>0</v>
+      </c>
+      <c r="K15" s="70">
+        <v>0</v>
+      </c>
+      <c r="L15" s="70">
+        <v>0</v>
+      </c>
+      <c r="M15" s="76">
+        <v>0</v>
+      </c>
+      <c r="N15" s="79" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="6" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="117" t="s">
-        <v>199</v>
-      </c>
-      <c r="C19" s="120" t="s">
-        <v>201</v>
-      </c>
-      <c r="D19" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="F19" s="117" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120" t="s">
-        <v>97</v>
-      </c>
-      <c r="K19" s="120"/>
-      <c r="L19" s="120"/>
-      <c r="M19" s="125"/>
-      <c r="N19" s="114" t="s">
-        <v>200</v>
+      <c r="B19" s="114" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="117" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="114" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="111" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="118"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="123"/>
-      <c r="F20" s="63" t="s">
-        <v>138</v>
+      <c r="B20" s="115"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="119"/>
+      <c r="F20" s="61" t="s">
+        <v>114</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="M20" s="75" t="s">
-        <v>141</v>
-      </c>
-      <c r="N20" s="115"/>
+        <v>116</v>
+      </c>
+      <c r="M20" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="N20" s="112"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="126"/>
-      <c r="C21" s="112"/>
-      <c r="D21" s="127"/>
-      <c r="F21" s="93">
+      <c r="B21" s="116"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="120"/>
+      <c r="F21" s="91">
         <v>12</v>
       </c>
-      <c r="G21" s="94">
+      <c r="G21" s="92">
         <f t="shared" ref="G21" si="1">F21+20</f>
         <v>32</v>
       </c>
-      <c r="H21" s="94">
+      <c r="H21" s="92">
         <f t="shared" ref="H21" si="2">G21+20</f>
         <v>52</v>
       </c>
-      <c r="I21" s="94">
+      <c r="I21" s="92">
         <f t="shared" ref="I21" si="3">H21+20</f>
         <v>72</v>
       </c>
-      <c r="J21" s="94">
+      <c r="J21" s="92">
         <f t="shared" ref="J21" si="4">I21+20</f>
         <v>92</v>
       </c>
-      <c r="K21" s="94">
+      <c r="K21" s="92">
         <f t="shared" ref="K21" si="5">J21+20</f>
         <v>112</v>
       </c>
-      <c r="L21" s="94">
+      <c r="L21" s="92">
         <f t="shared" ref="L21" si="6">K21+20</f>
         <v>132</v>
       </c>
-      <c r="M21" s="95">
+      <c r="M21" s="93">
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="116"/>
+      <c r="N21" s="113"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B22" s="88">
+      <c r="B22" s="86">
         <v>1</v>
       </c>
-      <c r="C22" s="89" t="s">
+      <c r="C22" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="90">
-        <v>0</v>
-      </c>
-      <c r="F22" s="88">
-        <v>0</v>
-      </c>
-      <c r="G22" s="97">
-        <v>0</v>
-      </c>
-      <c r="H22" s="97">
-        <v>0</v>
-      </c>
-      <c r="I22" s="97">
-        <v>0</v>
-      </c>
-      <c r="J22" s="97">
-        <v>0</v>
-      </c>
-      <c r="K22" s="97">
-        <v>0</v>
-      </c>
-      <c r="L22" s="97">
-        <v>0</v>
-      </c>
-      <c r="M22" s="90">
-        <v>0</v>
-      </c>
-      <c r="N22" s="91" t="s">
-        <v>206</v>
+      <c r="D22" s="88">
+        <v>0</v>
+      </c>
+      <c r="F22" s="86">
+        <v>0</v>
+      </c>
+      <c r="G22" s="95">
+        <v>0</v>
+      </c>
+      <c r="H22" s="95">
+        <v>0</v>
+      </c>
+      <c r="I22" s="95">
+        <v>0</v>
+      </c>
+      <c r="J22" s="95">
+        <v>0</v>
+      </c>
+      <c r="K22" s="95">
+        <v>0</v>
+      </c>
+      <c r="L22" s="95">
+        <v>0</v>
+      </c>
+      <c r="M22" s="88">
+        <v>0</v>
+      </c>
+      <c r="N22" s="89" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B23" s="64">
+      <c r="B23" s="62">
         <v>2</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D23" s="65">
+        <v>179</v>
+      </c>
+      <c r="D23" s="63">
         <v>25</v>
       </c>
-      <c r="F23" s="64">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>0</v>
-      </c>
-      <c r="I23" s="9">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0</v>
-      </c>
-      <c r="M23" s="65">
-        <v>0</v>
-      </c>
-      <c r="N23" s="92" t="s">
-        <v>217</v>
+      <c r="F23" s="62">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0</v>
+      </c>
+      <c r="M23" s="63">
+        <v>0</v>
+      </c>
+      <c r="N23" s="90" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B24" s="64">
+      <c r="B24" s="62">
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="65">
+      <c r="D24" s="63">
         <v>12</v>
       </c>
-      <c r="F24" s="82">
+      <c r="F24" s="80">
         <v>25</v>
       </c>
-      <c r="G24" s="83">
+      <c r="G24" s="81">
         <v>25</v>
       </c>
-      <c r="H24" s="83">
+      <c r="H24" s="81">
         <v>25</v>
       </c>
-      <c r="I24" s="83">
+      <c r="I24" s="81">
         <v>25</v>
       </c>
-      <c r="J24" s="83">
+      <c r="J24" s="81">
         <v>25</v>
       </c>
-      <c r="K24" s="83">
+      <c r="K24" s="81">
         <v>25</v>
       </c>
-      <c r="L24" s="83">
+      <c r="L24" s="81">
         <v>25</v>
       </c>
-      <c r="M24" s="98">
+      <c r="M24" s="96">
         <v>25</v>
       </c>
-      <c r="N24" s="92" t="s">
-        <v>218</v>
+      <c r="N24" s="90" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B25" s="64">
+      <c r="B25" s="62">
         <v>4</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="65">
+      <c r="D25" s="63">
         <v>12</v>
       </c>
-      <c r="F25" s="64">
-        <v>0</v>
-      </c>
-      <c r="G25" s="83">
+      <c r="F25" s="62">
+        <v>0</v>
+      </c>
+      <c r="G25" s="81">
         <v>25</v>
       </c>
-      <c r="H25" s="83">
+      <c r="H25" s="81">
         <v>25</v>
       </c>
-      <c r="I25" s="83">
+      <c r="I25" s="81">
         <v>25</v>
       </c>
-      <c r="J25" s="83">
+      <c r="J25" s="81">
         <v>25</v>
       </c>
-      <c r="K25" s="83">
+      <c r="K25" s="81">
         <v>25</v>
       </c>
-      <c r="L25" s="83">
+      <c r="L25" s="81">
         <v>25</v>
       </c>
-      <c r="M25" s="98">
+      <c r="M25" s="96">
         <v>25</v>
       </c>
-      <c r="N25" s="92" t="s">
-        <v>219</v>
+      <c r="N25" s="90" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B26" s="64">
+      <c r="B26" s="62">
         <v>5</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="65">
+      <c r="D26" s="63">
         <v>52</v>
       </c>
-      <c r="F26" s="64">
-        <v>0</v>
-      </c>
-      <c r="G26" s="83">
+      <c r="F26" s="62">
+        <v>0</v>
+      </c>
+      <c r="G26" s="81">
         <v>25</v>
       </c>
-      <c r="H26" s="9">
-        <v>0</v>
-      </c>
-      <c r="I26" s="83">
+      <c r="H26" s="8">
+        <v>0</v>
+      </c>
+      <c r="I26" s="81">
         <v>25</v>
       </c>
-      <c r="J26" s="83">
+      <c r="J26" s="81">
         <v>25</v>
       </c>
-      <c r="K26" s="83">
+      <c r="K26" s="81">
         <v>25</v>
       </c>
-      <c r="L26" s="83">
+      <c r="L26" s="81">
         <v>25</v>
       </c>
-      <c r="M26" s="98">
+      <c r="M26" s="96">
         <v>25</v>
       </c>
-      <c r="N26" s="92" t="s">
-        <v>220</v>
+      <c r="N26" s="90" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B27" s="64">
+      <c r="B27" s="62">
         <v>6</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="65">
+      <c r="D27" s="63">
         <v>92</v>
       </c>
-      <c r="F27" s="64">
-        <v>0</v>
-      </c>
-      <c r="G27" s="83">
+      <c r="F27" s="62">
+        <v>0</v>
+      </c>
+      <c r="G27" s="81">
         <v>25</v>
       </c>
-      <c r="H27" s="9">
-        <v>0</v>
-      </c>
-      <c r="I27" s="83">
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="81">
         <v>25</v>
       </c>
-      <c r="J27" s="9">
-        <v>0</v>
-      </c>
-      <c r="K27" s="83">
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="81">
         <v>25</v>
       </c>
-      <c r="L27" s="83">
+      <c r="L27" s="81">
         <v>25</v>
       </c>
-      <c r="M27" s="98">
+      <c r="M27" s="96">
         <v>25</v>
       </c>
-      <c r="N27" s="92" t="s">
-        <v>221</v>
+      <c r="N27" s="90" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B28" s="64">
+      <c r="B28" s="62">
         <v>7</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="65">
+      <c r="D28" s="63">
         <v>132</v>
       </c>
-      <c r="F28" s="64">
-        <v>0</v>
-      </c>
-      <c r="G28" s="83">
+      <c r="F28" s="62">
+        <v>0</v>
+      </c>
+      <c r="G28" s="81">
         <v>25</v>
       </c>
-      <c r="H28" s="9">
-        <v>0</v>
-      </c>
-      <c r="I28" s="83">
+      <c r="H28" s="8">
+        <v>0</v>
+      </c>
+      <c r="I28" s="81">
         <v>25</v>
       </c>
-      <c r="J28" s="9">
-        <v>0</v>
-      </c>
-      <c r="K28" s="83">
+      <c r="J28" s="8">
+        <v>0</v>
+      </c>
+      <c r="K28" s="81">
         <v>25</v>
       </c>
-      <c r="L28" s="9">
-        <v>0</v>
-      </c>
-      <c r="M28" s="98">
+      <c r="L28" s="8">
+        <v>0</v>
+      </c>
+      <c r="M28" s="96">
         <v>25</v>
       </c>
-      <c r="N28" s="92" t="s">
-        <v>223</v>
+      <c r="N28" s="90" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B29" s="64">
+      <c r="B29" s="62">
         <v>8</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="65">
+      <c r="D29" s="63">
         <v>12</v>
       </c>
-      <c r="F29" s="64">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0</v>
-      </c>
-      <c r="H29" s="9">
-        <v>0</v>
-      </c>
-      <c r="I29" s="9">
-        <v>0</v>
-      </c>
-      <c r="J29" s="9">
-        <v>0</v>
-      </c>
-      <c r="K29" s="9">
-        <v>0</v>
-      </c>
-      <c r="L29" s="9">
-        <v>0</v>
-      </c>
-      <c r="M29" s="65">
-        <v>0</v>
-      </c>
-      <c r="N29" s="92" t="s">
-        <v>222</v>
+      <c r="F29" s="62">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0</v>
+      </c>
+      <c r="M29" s="63">
+        <v>0</v>
+      </c>
+      <c r="N29" s="90" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B30" s="64">
+      <c r="B30" s="62">
         <v>9</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D30" s="65">
+        <v>179</v>
+      </c>
+      <c r="D30" s="63">
         <v>75</v>
       </c>
-      <c r="F30" s="64">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9">
-        <v>0</v>
-      </c>
-      <c r="H30" s="9">
-        <v>0</v>
-      </c>
-      <c r="I30" s="9">
-        <v>0</v>
-      </c>
-      <c r="J30" s="9">
-        <v>0</v>
-      </c>
-      <c r="K30" s="9">
-        <v>0</v>
-      </c>
-      <c r="L30" s="9">
-        <v>0</v>
-      </c>
-      <c r="M30" s="65">
-        <v>0</v>
-      </c>
-      <c r="N30" s="92" t="s">
-        <v>224</v>
+      <c r="F30" s="62">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8">
+        <v>0</v>
+      </c>
+      <c r="I30" s="8">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0</v>
+      </c>
+      <c r="K30" s="8">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0</v>
+      </c>
+      <c r="M30" s="63">
+        <v>0</v>
+      </c>
+      <c r="N30" s="90" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B31" s="64">
+      <c r="B31" s="62">
         <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="65">
+      <c r="D31" s="63">
         <v>12</v>
       </c>
-      <c r="F31" s="99">
+      <c r="F31" s="97">
         <v>75</v>
       </c>
-      <c r="G31" s="9">
-        <v>0</v>
-      </c>
-      <c r="H31" s="9">
-        <v>0</v>
-      </c>
-      <c r="I31" s="9">
-        <v>0</v>
-      </c>
-      <c r="J31" s="9">
-        <v>0</v>
-      </c>
-      <c r="K31" s="9">
-        <v>0</v>
-      </c>
-      <c r="L31" s="9">
-        <v>0</v>
-      </c>
-      <c r="M31" s="65">
-        <v>0</v>
-      </c>
-      <c r="N31" s="92" t="s">
-        <v>225</v>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="63">
+        <v>0</v>
+      </c>
+      <c r="N31" s="90" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B32" s="64">
+      <c r="B32" s="62">
         <v>11</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="65">
+      <c r="D32" s="63">
         <v>52</v>
       </c>
-      <c r="F32" s="99">
+      <c r="F32" s="97">
         <v>75</v>
       </c>
-      <c r="G32" s="9">
-        <v>0</v>
-      </c>
-      <c r="H32" s="96">
+      <c r="G32" s="8">
+        <v>0</v>
+      </c>
+      <c r="H32" s="94">
         <v>75</v>
       </c>
-      <c r="I32" s="9">
-        <v>0</v>
-      </c>
-      <c r="J32" s="9">
-        <v>0</v>
-      </c>
-      <c r="K32" s="9">
-        <v>0</v>
-      </c>
-      <c r="L32" s="9">
-        <v>0</v>
-      </c>
-      <c r="M32" s="65">
-        <v>0</v>
-      </c>
-      <c r="N32" s="92" t="s">
-        <v>226</v>
+      <c r="I32" s="8">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8">
+        <v>0</v>
+      </c>
+      <c r="M32" s="63">
+        <v>0</v>
+      </c>
+      <c r="N32" s="90" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B33" s="64">
+      <c r="B33" s="62">
         <v>12</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="65">
+      <c r="D33" s="63">
         <v>92</v>
       </c>
-      <c r="F33" s="99">
+      <c r="F33" s="97">
         <v>75</v>
       </c>
-      <c r="G33" s="9">
-        <v>0</v>
-      </c>
-      <c r="H33" s="96">
+      <c r="G33" s="8">
+        <v>0</v>
+      </c>
+      <c r="H33" s="94">
         <v>75</v>
       </c>
-      <c r="I33" s="9">
-        <v>0</v>
-      </c>
-      <c r="J33" s="96">
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="94">
         <v>75</v>
       </c>
-      <c r="K33" s="9">
-        <v>0</v>
-      </c>
-      <c r="L33" s="9">
-        <v>0</v>
-      </c>
-      <c r="M33" s="65">
-        <v>0</v>
-      </c>
-      <c r="N33" s="92" t="s">
-        <v>227</v>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="63">
+        <v>0</v>
+      </c>
+      <c r="N33" s="90" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="66">
+      <c r="B34" s="64">
         <v>13</v>
       </c>
-      <c r="C34" s="67" t="s">
+      <c r="C34" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="68">
+      <c r="D34" s="66">
         <v>132</v>
       </c>
-      <c r="F34" s="100">
+      <c r="F34" s="98">
         <v>75</v>
       </c>
-      <c r="G34" s="72">
-        <v>0</v>
-      </c>
-      <c r="H34" s="101">
+      <c r="G34" s="70">
+        <v>0</v>
+      </c>
+      <c r="H34" s="99">
         <v>75</v>
       </c>
-      <c r="I34" s="72">
-        <v>0</v>
-      </c>
-      <c r="J34" s="101">
+      <c r="I34" s="70">
+        <v>0</v>
+      </c>
+      <c r="J34" s="99">
         <v>75</v>
       </c>
-      <c r="K34" s="72">
-        <v>0</v>
-      </c>
-      <c r="L34" s="101">
+      <c r="K34" s="70">
+        <v>0</v>
+      </c>
+      <c r="L34" s="99">
         <v>75</v>
       </c>
-      <c r="M34" s="68">
-        <v>0</v>
-      </c>
-      <c r="N34" s="102" t="s">
-        <v>228</v>
+      <c r="M34" s="66">
+        <v>0</v>
+      </c>
+      <c r="N34" s="100" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="N19:N21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650E12E2-5D5D-4C76-871F-E1DA29146CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C41DD0-566B-4DF8-9084-6AA270834C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -1889,6 +1889,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1900,15 +1909,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3137,55 +3137,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>390962</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>57948</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AF428C8-FCB6-4E15-B3EF-9B259FCD7D93}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="419100"/>
-          <a:ext cx="3134162" cy="5715798"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
@@ -3211,7 +3162,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3260,7 +3211,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3269,6 +3220,55 @@
         <a:xfrm>
           <a:off x="14556441" y="425824"/>
           <a:ext cx="2584076" cy="2069169"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>398417</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5B563BE-9D30-29E7-1714-52D2610371E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="204107" y="435430"/>
+          <a:ext cx="3664131" cy="6857999"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3699,14 +3699,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="105" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3758,14 +3758,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="106" t="s">
+      <c r="E7" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3777,14 +3777,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="107" t="s">
+      <c r="E8" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="107"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="102"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3796,14 +3796,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="103" t="s">
+      <c r="E9" s="106" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="105"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="108"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3815,14 +3815,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="107" t="s">
+      <c r="E10" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="107"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3834,14 +3834,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="103" t="s">
+      <c r="E11" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="105"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="108"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3853,14 +3853,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="107" t="s">
+      <c r="E12" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="107"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="107"/>
-      <c r="I12" s="107"/>
-      <c r="J12" s="107"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3872,14 +3872,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="103" t="s">
+      <c r="E13" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="108"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -3899,13 +3899,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="F17" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="103"/>
+      <c r="J17" s="103"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -3920,13 +3920,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="107" t="s">
+      <c r="F18" s="102" t="s">
         <v>210</v>
       </c>
-      <c r="G18" s="107"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="107"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -3941,13 +3941,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="107" t="s">
+      <c r="F19" s="102" t="s">
         <v>205</v>
       </c>
-      <c r="G19" s="107"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="107"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -3962,13 +3962,13 @@
       <c r="E20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="107" t="s">
+      <c r="F20" s="102" t="s">
         <v>121</v>
       </c>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="107"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="102"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -3983,13 +3983,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="107" t="s">
+      <c r="F21" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="107"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="102"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4004,13 +4004,13 @@
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="107" t="s">
+      <c r="F22" s="102" t="s">
         <v>123</v>
       </c>
-      <c r="G22" s="107"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4025,13 +4025,13 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="107" t="s">
+      <c r="F23" s="102" t="s">
         <v>124</v>
       </c>
-      <c r="G23" s="107"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="107"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="102"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4046,13 +4046,13 @@
       <c r="E24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F24" s="107" t="s">
+      <c r="F24" s="102" t="s">
         <v>125</v>
       </c>
-      <c r="G24" s="107"/>
-      <c r="H24" s="107"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="107"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="102"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4067,13 +4067,13 @@
       <c r="E25" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F25" s="107" t="s">
+      <c r="F25" s="102" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="107"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.45">
       <c r="C26" s="9"/>
@@ -4097,16 +4097,16 @@
         <v>47</v>
       </c>
       <c r="E29" s="11"/>
-      <c r="F29" s="108" t="s">
+      <c r="F29" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="108"/>
-      <c r="H29" s="108"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="108"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="104"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B30" s="8" t="s">
@@ -4373,15 +4373,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="E12:J12"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
     <mergeCell ref="E13:J13"/>
     <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E12:J12"/>
     <mergeCell ref="F24:J24"/>
     <mergeCell ref="F23:J23"/>
     <mergeCell ref="F22:J22"/>
@@ -4389,8 +4391,6 @@
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F20:J20"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="E7:J7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4413,25 +4413,25 @@
       <c r="B2" s="109" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="104" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108" t="s">
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="110"/>
-      <c r="D3" s="108"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="7" t="s">
         <v>114</v>
       </c>
@@ -5640,7 +5640,7 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B4" s="115"/>
-      <c r="C4" s="108"/>
+      <c r="C4" s="104"/>
       <c r="D4" s="119"/>
       <c r="F4" s="61" t="s">
         <v>114</v>
@@ -6118,7 +6118,7 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="115"/>
-      <c r="C20" s="108"/>
+      <c r="C20" s="104"/>
       <c r="D20" s="119"/>
       <c r="F20" s="61" t="s">
         <v>114</v>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C41DD0-566B-4DF8-9084-6AA270834C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC6695B-A9AE-43F7-BD66-6B47B3AB8B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -1889,26 +1889,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1931,31 +1931,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3699,14 +3699,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="102" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3758,14 +3758,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="103" t="s">
+      <c r="E7" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="103"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3777,14 +3777,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3796,14 +3796,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="103" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="108"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="105"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3815,14 +3815,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="107" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="107"/>
+      <c r="J10" s="107"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3834,14 +3834,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="106" t="s">
+      <c r="E11" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="107"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="107"/>
-      <c r="I11" s="107"/>
-      <c r="J11" s="108"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="105"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3853,14 +3853,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="102"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="107"/>
+      <c r="J12" s="107"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3872,14 +3872,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="106" t="s">
+      <c r="E13" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="108"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -3899,13 +3899,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="103" t="s">
+      <c r="F17" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="103"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -3920,13 +3920,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="102" t="s">
+      <c r="F18" s="107" t="s">
         <v>210</v>
       </c>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="102"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="107"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -3941,13 +3941,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="102" t="s">
+      <c r="F19" s="107" t="s">
         <v>205</v>
       </c>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -3962,13 +3962,13 @@
       <c r="E20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="102" t="s">
+      <c r="F20" s="107" t="s">
         <v>121</v>
       </c>
-      <c r="G20" s="102"/>
-      <c r="H20" s="102"/>
-      <c r="I20" s="102"/>
-      <c r="J20" s="102"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -3983,13 +3983,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="102" t="s">
+      <c r="F21" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="102"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4004,13 +4004,13 @@
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="102" t="s">
+      <c r="F22" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="G22" s="102"/>
-      <c r="H22" s="102"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="102"/>
+      <c r="G22" s="107"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4025,13 +4025,13 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="102" t="s">
+      <c r="F23" s="107" t="s">
         <v>124</v>
       </c>
-      <c r="G23" s="102"/>
-      <c r="H23" s="102"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="102"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="107"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4046,13 +4046,13 @@
       <c r="E24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F24" s="102" t="s">
+      <c r="F24" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="G24" s="102"/>
-      <c r="H24" s="102"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4067,13 +4067,13 @@
       <c r="E25" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F25" s="102" t="s">
+      <c r="F25" s="107" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="102"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="107"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.45">
       <c r="C26" s="9"/>
@@ -4097,16 +4097,16 @@
         <v>47</v>
       </c>
       <c r="E29" s="11"/>
-      <c r="F29" s="104" t="s">
+      <c r="F29" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="104"/>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="104"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B30" s="8" t="s">
@@ -4373,11 +4373,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="F17:J17"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
     <mergeCell ref="F29:M29"/>
@@ -4391,6 +4386,11 @@
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F20:J20"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="F17:J17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4413,25 +4413,25 @@
       <c r="B2" s="109" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="104" t="s">
+      <c r="D2" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="108" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104" t="s">
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="110"/>
-      <c r="D3" s="104"/>
+      <c r="D3" s="108"/>
       <c r="E3" s="7" t="s">
         <v>114</v>
       </c>
@@ -5619,7 +5619,7 @@
       <c r="C3" s="117" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="118" t="s">
+      <c r="D3" s="119" t="s">
         <v>178</v>
       </c>
       <c r="F3" s="114" t="s">
@@ -5633,15 +5633,15 @@
       </c>
       <c r="K3" s="117"/>
       <c r="L3" s="117"/>
-      <c r="M3" s="121"/>
+      <c r="M3" s="122"/>
       <c r="N3" s="111" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B4" s="115"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="119"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="120"/>
       <c r="F4" s="61" t="s">
         <v>114</v>
       </c>
@@ -5669,9 +5669,9 @@
       <c r="N4" s="112"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="122"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="124"/>
+      <c r="B5" s="116"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="121"/>
       <c r="F5" s="71">
         <v>1</v>
       </c>
@@ -6097,7 +6097,7 @@
       <c r="C19" s="117" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="118" t="s">
+      <c r="D19" s="119" t="s">
         <v>178</v>
       </c>
       <c r="F19" s="114" t="s">
@@ -6111,15 +6111,15 @@
       </c>
       <c r="K19" s="117"/>
       <c r="L19" s="117"/>
-      <c r="M19" s="121"/>
+      <c r="M19" s="122"/>
       <c r="N19" s="111" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="115"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="119"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="120"/>
       <c r="F20" s="61" t="s">
         <v>114</v>
       </c>
@@ -6147,9 +6147,9 @@
       <c r="N20" s="112"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="116"/>
+      <c r="B21" s="123"/>
       <c r="C21" s="109"/>
-      <c r="D21" s="120"/>
+      <c r="D21" s="124"/>
       <c r="F21" s="91">
         <v>12</v>
       </c>
@@ -6679,18 +6679,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="J19:M19"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC6695B-A9AE-43F7-BD66-6B47B3AB8B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D35644-5C9D-4E87-BC66-C11AF2F682DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="222">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -318,10 +318,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>명령에 따른 가변 길이 데이터, "2. Command 목록" 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2. Command 목록</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -496,22 +492,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>선택 Bar 점등 (Data = 0 → 전체 Bar 점등), "xc xd mapping" 시트 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택 Bar 소등 (Data = 0 → 전체 Bar 소등), "xc xd mapping" 시트 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택 Block 점등 (Data= 0 → 전체 Block 점등), "xc xd mapping" 시트 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택 Block 소등 (Data= 0 → 전체 Block 소등), "xc xd mapping" 시트 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BLOCK #141</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -869,6 +849,42 @@
   </si>
   <si>
     <t>4. Example Screenshot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low Current Mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 or 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명령에 따른 가변 길이 데이터, "2. Command 목록" 참조, 최대 160byte까지 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 Bar 점등 (Data = 0 → 전체 Bar 점등), "xc xd mapping" 시트 참조, multi-byte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 Bar 소등 (Data = 0 → 전체 Bar 소등), "xc xd mapping" 시트 참조, multi-byte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 Block 점등 (Data= 0 → 전체 Block 점등), "xc xd mapping" 시트 참조, multi-byte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 Block 소등 (Data= 0 → 전체 Block 소등), "xc xd mapping" 시트 참조, multi-byte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data = 0 → Disable Low Currnet Mode / Data = 1 → Enable Low Currnet Mode; Low Current Mode : 31.2uA (XD04 최소 전류 resolution) 설정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -940,7 +956,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -971,6 +987,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="47">
     <border>
@@ -1584,7 +1606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1889,6 +1911,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1901,14 +1926,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1992,13 +2029,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>28258</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2042,7 +2079,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2113,7 +2150,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2186,13 +2223,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>28257</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2236,7 +2273,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2307,7 +2344,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2380,13 +2417,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2437,13 +2474,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1590675</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2494,7 +2531,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -2577,7 +2614,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>537156</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -2660,13 +2697,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>28256</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2710,7 +2747,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2781,7 +2818,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2854,13 +2891,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2911,13 +2948,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1581150</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2968,7 +3005,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -3051,7 +3088,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>527629</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -3679,7 +3716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M108"/>
+  <dimension ref="B2:M109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="6" customWidth="1"/>
@@ -3699,14 +3736,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="102" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
+      <c r="B3" s="103" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3758,14 +3795,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="106" t="s">
+      <c r="E7" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3777,14 +3814,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="107" t="s">
+      <c r="E8" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="107"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3796,14 +3833,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="103" t="s">
-        <v>174</v>
-      </c>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="105"/>
+      <c r="E9" s="104" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="106"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3815,33 +3852,33 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="107" t="s">
+      <c r="E10" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="107"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="102" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="103" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="105"/>
+      <c r="E11" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3853,14 +3890,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="107" t="s">
+      <c r="E12" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="107"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="107"/>
-      <c r="I12" s="107"/>
-      <c r="J12" s="107"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="113"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3872,18 +3909,18 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="103" t="s">
+      <c r="E13" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="106"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.45">
@@ -3899,13 +3936,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="F17" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="110"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -3920,13 +3957,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="107" t="s">
-        <v>210</v>
-      </c>
-      <c r="G18" s="107"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="107"/>
+      <c r="F18" s="113" t="s">
+        <v>205</v>
+      </c>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="113"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -3941,34 +3978,34 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="107" t="s">
-        <v>205</v>
-      </c>
-      <c r="G19" s="107"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="107"/>
+      <c r="F19" s="113" t="s">
+        <v>200</v>
+      </c>
+      <c r="G19" s="113"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="113"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="113" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="107" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="107"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="113"/>
+      <c r="J20" s="113"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -3983,13 +4020,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="107" t="s">
+      <c r="F21" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="107"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -3998,19 +4035,19 @@
       <c r="C22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
+      <c r="D22" s="102" t="s">
+        <v>6</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="107" t="s">
-        <v>123</v>
-      </c>
-      <c r="G22" s="107"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
+      <c r="F22" s="111" t="s">
+        <v>217</v>
+      </c>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="111"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4019,19 +4056,19 @@
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
+      <c r="D23" s="102" t="s">
+        <v>6</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="107" t="s">
-        <v>124</v>
-      </c>
-      <c r="G23" s="107"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="107"/>
+      <c r="F23" s="111" t="s">
+        <v>218</v>
+      </c>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="111"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4040,19 +4077,19 @@
       <c r="C24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
+      <c r="D24" s="102" t="s">
+        <v>6</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="107" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="107"/>
-      <c r="H24" s="107"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="107"/>
+        <v>121</v>
+      </c>
+      <c r="F24" s="111" t="s">
+        <v>219</v>
+      </c>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="111"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4061,155 +4098,157 @@
       <c r="C25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="102" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="111" t="s">
+        <v>220</v>
+      </c>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="111"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B26" s="102" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" s="102" t="s">
+        <v>214</v>
+      </c>
+      <c r="D26" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="107" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="107"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B28" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="E26" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="F26" s="111" t="s">
+        <v>221</v>
+      </c>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="111"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B30" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="7" t="s">
+      <c r="C30" s="9"/>
+      <c r="D30" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="108" t="s">
+      <c r="E30" s="11"/>
+      <c r="F30" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="108"/>
-      <c r="H29" s="108"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="108"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="L30" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="M30" s="17" t="s">
-        <v>127</v>
-      </c>
+      <c r="G30" s="112"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="112"/>
+      <c r="J30" s="112"/>
+      <c r="K30" s="112"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B31" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="I31" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="J31" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="K31" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="L31" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="22" t="s">
-        <v>128</v>
+        <v>36</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B32" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="M32" s="22" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B33" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -4222,13 +4261,13 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B34" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
@@ -4241,11 +4280,13 @@
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="D35" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
@@ -4258,13 +4299,11 @@
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B36" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>46</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C36" s="12"/>
       <c r="D36" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
@@ -4277,13 +4316,13 @@
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B37" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
@@ -4296,13 +4335,13 @@
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B38" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
@@ -4315,13 +4354,13 @@
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B39" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
@@ -4334,13 +4373,13 @@
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B40" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -4351,31 +4390,50 @@
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B43" s="5" t="s">
-        <v>217</v>
-      </c>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B41" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B44" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B76" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B108" s="6" t="s">
-        <v>208</v>
+      <c r="B44" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B45" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B77" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B109" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F30:M30"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E10:J10"/>
     <mergeCell ref="E12:J12"/>
@@ -4386,6 +4444,7 @@
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F20:J20"/>
+    <mergeCell ref="F26:J26"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
@@ -4410,56 +4469,56 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="109" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" s="108" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="108" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108" t="s">
+      <c r="B2" s="114" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="112" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="110"/>
-      <c r="D3" s="108"/>
+      <c r="B3" s="115"/>
+      <c r="D3" s="112"/>
       <c r="E3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="I3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="28" t="s">
         <v>116</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B4" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>46</v>
@@ -4501,7 +4560,7 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B5" s="23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>46</v>
@@ -4543,7 +4602,7 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B6" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>46</v>
@@ -4585,7 +4644,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B7" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>46</v>
@@ -4627,7 +4686,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B8" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>46</v>
@@ -4669,13 +4728,13 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" s="24">
         <v>6</v>
@@ -4711,13 +4770,13 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" s="24">
         <v>7</v>
@@ -4753,13 +4812,13 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B11" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" s="24">
         <v>8</v>
@@ -4795,13 +4854,13 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B12" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" s="24">
         <v>9</v>
@@ -4837,13 +4896,13 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B13" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" s="24">
         <v>10</v>
@@ -4879,13 +4938,13 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B14" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="24">
         <v>11</v>
@@ -4921,13 +4980,13 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B15" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" s="24">
         <v>12</v>
@@ -4963,13 +5022,13 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B16" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" s="24">
         <v>13</v>
@@ -5005,13 +5064,13 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B17" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" s="24">
         <v>14</v>
@@ -5047,13 +5106,13 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B18" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" s="24">
         <v>15</v>
@@ -5089,13 +5148,13 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B19" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" s="24">
         <v>16</v>
@@ -5131,7 +5190,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B20" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="27" t="s">
         <v>46</v>
@@ -5173,7 +5232,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B21" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" s="27" t="s">
         <v>46</v>
@@ -5215,7 +5274,7 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B22" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" s="27" t="s">
         <v>46</v>
@@ -5257,7 +5316,7 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B23" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="27" t="s">
         <v>46</v>
@@ -5335,37 +5394,37 @@
     <row r="1" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="39" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C2" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="I2" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="J2" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="K2" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="H2" s="35" t="s">
+      <c r="L2" s="39" t="s">
         <v>131</v>
-      </c>
-      <c r="I2" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="J2" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="K2" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="L2" s="39" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
@@ -5373,22 +5432,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D3" s="45"/>
       <c r="E3" s="32"/>
       <c r="F3" s="46"/>
       <c r="G3" s="37" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
       <c r="K3" s="52"/>
       <c r="L3" s="55" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -5396,32 +5455,32 @@
         <v>2</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K4" s="53"/>
       <c r="L4" s="56" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -5429,32 +5488,32 @@
         <v>3</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K5" s="53"/>
       <c r="L5" s="56" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -5462,26 +5521,26 @@
         <v>4</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="38" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I6" s="30"/>
       <c r="J6" s="30"/>
       <c r="K6" s="53"/>
       <c r="L6" s="56" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -5489,30 +5548,30 @@
         <v>5</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="48"/>
       <c r="G7" s="38" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="K7" s="53" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="L7" s="56" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -5520,38 +5579,38 @@
         <v>6</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G8" s="101" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I8" s="31"/>
       <c r="J8" s="31"/>
       <c r="K8" s="54"/>
       <c r="L8" s="57" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" s="29" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B11" s="29" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -5576,13 +5635,13 @@
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="W2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5609,69 +5668,69 @@
   <sheetData>
     <row r="2" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="114" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" s="117" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" s="114" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117" t="s">
+      <c r="B3" s="119" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="122" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="124" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="111" t="s">
-        <v>176</v>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="116" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="115"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="120"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="125"/>
       <c r="F4" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="J4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="73" t="s">
         <v>116</v>
       </c>
-      <c r="M4" s="73" t="s">
-        <v>117</v>
-      </c>
-      <c r="N4" s="112"/>
+      <c r="N4" s="117"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="116"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="121"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="126"/>
       <c r="F5" s="71">
         <v>1</v>
       </c>
@@ -5703,7 +5762,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="113"/>
+      <c r="N5" s="118"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="67">
@@ -5740,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="77" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.45">
@@ -5748,7 +5807,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D7" s="63">
         <v>50</v>
@@ -5778,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="78" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.45">
@@ -5816,7 +5875,7 @@
         <v>50</v>
       </c>
       <c r="N8" s="78" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.45">
@@ -5854,7 +5913,7 @@
         <v>50</v>
       </c>
       <c r="N9" s="78" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.45">
@@ -5892,7 +5951,7 @@
         <v>50</v>
       </c>
       <c r="N10" s="78" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.45">
@@ -5930,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="78" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.45">
@@ -5968,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="78" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.45">
@@ -5976,7 +6035,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D13" s="63">
         <v>100</v>
@@ -6006,7 +6065,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="78" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.45">
@@ -6044,7 +6103,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="78" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -6052,7 +6111,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D15" s="66">
         <v>0</v>
@@ -6082,74 +6141,74 @@
         <v>0</v>
       </c>
       <c r="N15" s="79" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="6" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="114" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="117" t="s">
-        <v>177</v>
-      </c>
-      <c r="D19" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="F19" s="114" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117" t="s">
+      <c r="B19" s="119" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="122" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="124" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="K19" s="117"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="122"/>
-      <c r="N19" s="111" t="s">
-        <v>176</v>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="122" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19" s="122"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="116" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="115"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="120"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="125"/>
       <c r="F20" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="I20" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="J20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="M20" s="73" t="s">
         <v>116</v>
       </c>
-      <c r="M20" s="73" t="s">
-        <v>117</v>
-      </c>
-      <c r="N20" s="112"/>
+      <c r="N20" s="117"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="123"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="124"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="129"/>
       <c r="F21" s="91">
         <v>12</v>
       </c>
@@ -6181,7 +6240,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="113"/>
+      <c r="N21" s="118"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="86">
@@ -6218,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="89" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.45">
@@ -6226,7 +6285,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D23" s="63">
         <v>25</v>
@@ -6256,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="90" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.45">
@@ -6294,7 +6353,7 @@
         <v>25</v>
       </c>
       <c r="N24" s="90" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.45">
@@ -6332,7 +6391,7 @@
         <v>25</v>
       </c>
       <c r="N25" s="90" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.45">
@@ -6370,7 +6429,7 @@
         <v>25</v>
       </c>
       <c r="N26" s="90" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.45">
@@ -6408,7 +6467,7 @@
         <v>25</v>
       </c>
       <c r="N27" s="90" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.45">
@@ -6446,7 +6505,7 @@
         <v>25</v>
       </c>
       <c r="N28" s="90" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.45">
@@ -6484,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="90" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.45">
@@ -6492,7 +6551,7 @@
         <v>9</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D30" s="63">
         <v>75</v>
@@ -6522,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="90" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.45">
@@ -6560,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="90" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.45">
@@ -6598,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="90" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.45">
@@ -6636,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="90" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -6674,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="100" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D35644-5C9D-4E87-BC66-C11AF2F682DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41125BE-95C0-4A0D-81B6-EEB0890E0757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="227">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -884,7 +884,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Data = 0 → Disable Low Currnet Mode / Data = 1 → Enable Low Currnet Mode; Low Current Mode : 31.2uA (XD04 최소 전류 resolution) 설정</t>
+    <t>PAM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data = 0 → Disable Low Currnet Mode / Data = 1 → Enable Low Currnet Mode; Low Current Mode : 우측 PAM, PWM 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effective</t>
+  </si>
+  <si>
+    <t>Vref</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -892,11 +911,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="&quot;B-&quot;0"/>
     <numFmt numFmtId="177" formatCode="&quot;Blk-&quot;0"/>
+    <numFmt numFmtId="185" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -955,6 +975,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1603,10 +1630,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1914,6 +1944,18 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1935,68 +1977,63 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="백분율" xfId="1" builtinId="5"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -2036,7 +2073,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>28258</xdr:rowOff>
+      <xdr:rowOff>31433</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2230,7 +2267,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
       <xdr:row>106</xdr:row>
-      <xdr:rowOff>28257</xdr:rowOff>
+      <xdr:rowOff>31432</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2704,7 +2741,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
       <xdr:row>138</xdr:row>
-      <xdr:rowOff>28256</xdr:rowOff>
+      <xdr:rowOff>31431</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3716,7 +3753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M109"/>
+  <dimension ref="B2:P109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="6" customWidth="1"/>
@@ -3736,14 +3773,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="107" t="s">
         <v>185</v>
       </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3795,14 +3832,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="110" t="s">
+      <c r="E7" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3814,14 +3851,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="113" t="s">
+      <c r="E8" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="106"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3833,14 +3870,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="104" t="s">
+      <c r="E9" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="106"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="109"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="110"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3852,14 +3889,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="113" t="s">
+      <c r="E10" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3871,14 +3908,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="107" t="s">
+      <c r="E11" s="111" t="s">
         <v>216</v>
       </c>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3890,14 +3927,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="113" t="s">
+      <c r="E12" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3909,21 +3946,21 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="E13" s="108" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="106"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="110"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
@@ -3936,15 +3973,15 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="110" t="s">
+      <c r="F17" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
@@ -3957,15 +3994,15 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="113" t="s">
+      <c r="F18" s="106" t="s">
         <v>205</v>
       </c>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113"/>
-      <c r="J18" s="113"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G18" s="106"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
@@ -3978,15 +4015,15 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="113" t="s">
+      <c r="F19" s="106" t="s">
         <v>200</v>
       </c>
-      <c r="G19" s="113"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="113"/>
-      <c r="J19" s="113"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G19" s="106"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="106"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>117</v>
       </c>
@@ -3999,15 +4036,15 @@
       <c r="E20" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="113" t="s">
+      <c r="F20" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="G20" s="113"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="113"/>
-      <c r="J20" s="113"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
@@ -4020,15 +4057,15 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="113" t="s">
+      <c r="F21" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
-      <c r="J21" s="113"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="106"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
@@ -4041,15 +4078,15 @@
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="111" t="s">
+      <c r="F22" s="103" t="s">
         <v>217</v>
       </c>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="103"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
@@ -4062,15 +4099,15 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="111" t="s">
+      <c r="F23" s="103" t="s">
         <v>218</v>
       </c>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G23" s="103"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="103"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>22</v>
       </c>
@@ -4083,15 +4120,15 @@
       <c r="E24" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F24" s="111" t="s">
+      <c r="F24" s="103" t="s">
         <v>219</v>
       </c>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="103"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>23</v>
       </c>
@@ -4104,15 +4141,30 @@
       <c r="E25" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F25" s="111" t="s">
+      <c r="F25" s="103" t="s">
         <v>220</v>
       </c>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="103"/>
+      <c r="L25" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B26" s="102" t="s">
         <v>213</v>
       </c>
@@ -4125,15 +4177,33 @@
       <c r="E26" s="102" t="s">
         <v>215</v>
       </c>
-      <c r="F26" s="111" t="s">
-        <v>221</v>
-      </c>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="F26" s="103" t="s">
+        <v>223</v>
+      </c>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="103"/>
+      <c r="L26" s="6">
+        <v>800</v>
+      </c>
+      <c r="M26" s="130">
+        <f>L26/4095*128</f>
+        <v>25.006105006105006</v>
+      </c>
+      <c r="N26" s="6">
+        <v>20</v>
+      </c>
+      <c r="O26" s="131">
+        <f>N26/16383</f>
+        <v>1.2207776353537203E-3</v>
+      </c>
+      <c r="P26" s="130">
+        <f>M26*O26</f>
+        <v>3.0526893738759699E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C27" s="9"/>
       <c r="D27" s="10"/>
       <c r="E27" s="9"/>
@@ -4141,12 +4211,12 @@
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B29" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B30" s="7" t="s">
         <v>48</v>
       </c>
@@ -4155,18 +4225,18 @@
         <v>47</v>
       </c>
       <c r="E30" s="11"/>
-      <c r="F30" s="112" t="s">
+      <c r="F30" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="112"/>
-      <c r="H30" s="112"/>
-      <c r="I30" s="112"/>
-      <c r="J30" s="112"/>
-      <c r="K30" s="112"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="112"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="G30" s="105"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="105"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="105"/>
+      <c r="M30" s="105"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B31" s="8" t="s">
         <v>25</v>
       </c>
@@ -4204,7 +4274,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B32" s="8" t="s">
         <v>26</v>
       </c>
@@ -4431,6 +4501,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="F17:J17"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
     <mergeCell ref="F30:M30"/>
@@ -4445,11 +4520,6 @@
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F26:J26"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="F17:J17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4472,25 +4542,25 @@
       <c r="B2" s="114" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="112" t="s">
+      <c r="D2" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="112" t="s">
+      <c r="E2" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112" t="s">
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="115"/>
-      <c r="D3" s="112"/>
+      <c r="D3" s="105"/>
       <c r="E3" s="7" t="s">
         <v>113</v>
       </c>
@@ -5678,7 +5748,7 @@
       <c r="C3" s="122" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="124" t="s">
+      <c r="D3" s="123" t="s">
         <v>173</v>
       </c>
       <c r="F3" s="119" t="s">
@@ -5692,15 +5762,15 @@
       </c>
       <c r="K3" s="122"/>
       <c r="L3" s="122"/>
-      <c r="M3" s="127"/>
+      <c r="M3" s="126"/>
       <c r="N3" s="116" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B4" s="120"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="125"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="124"/>
       <c r="F4" s="61" t="s">
         <v>113</v>
       </c>
@@ -5728,9 +5798,9 @@
       <c r="N4" s="117"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="121"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="126"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="129"/>
       <c r="F5" s="71">
         <v>1</v>
       </c>
@@ -6156,7 +6226,7 @@
       <c r="C19" s="122" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="124" t="s">
+      <c r="D19" s="123" t="s">
         <v>173</v>
       </c>
       <c r="F19" s="119" t="s">
@@ -6170,15 +6240,15 @@
       </c>
       <c r="K19" s="122"/>
       <c r="L19" s="122"/>
-      <c r="M19" s="127"/>
+      <c r="M19" s="126"/>
       <c r="N19" s="116" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="120"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="125"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="124"/>
       <c r="F20" s="61" t="s">
         <v>113</v>
       </c>
@@ -6206,9 +6276,9 @@
       <c r="N20" s="117"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="128"/>
+      <c r="B21" s="121"/>
       <c r="C21" s="114"/>
-      <c r="D21" s="129"/>
+      <c r="D21" s="125"/>
       <c r="F21" s="91">
         <v>12</v>
       </c>
@@ -6738,18 +6808,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="N19:N21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41125BE-95C0-4A0D-81B6-EEB0890E0757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487D53EE-A432-467C-B5D0-D1A048A21047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -740,10 +740,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 1ms delay 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Example with LED Bar No. 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -888,22 +884,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PWM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Data = 0 → Disable Low Currnet Mode / Data = 1 → Enable Low Currnet Mode; Low Current Mode : 우측 PAM, PWM 참조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Effective</t>
-  </si>
-  <si>
     <t>Vref</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>LD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effective Current</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWM Duty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10ms delay</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 필요</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -914,9 +940,9 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="&quot;B-&quot;0"/>
     <numFmt numFmtId="177" formatCode="&quot;Blk-&quot;0"/>
-    <numFmt numFmtId="185" formatCode="0.0000"/>
+    <numFmt numFmtId="180" formatCode="0.000&quot;mA&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -982,6 +1008,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1636,7 +1671,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1941,10 +1976,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1956,79 +1997,76 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3763,7 +3801,9 @@
     <col min="5" max="5" width="11" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="23.5" style="6" customWidth="1"/>
     <col min="11" max="13" width="10.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="9" style="6" customWidth="1"/>
+    <col min="14" max="14" width="9" style="6" customWidth="1"/>
+    <col min="15" max="15" width="9.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.25" style="6" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
@@ -3773,14 +3813,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="107" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
+      <c r="B3" s="102" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3832,14 +3872,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="104" t="s">
+      <c r="E7" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3851,14 +3891,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="106" t="s">
+      <c r="E8" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="106"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="106"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="108"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3870,14 +3910,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="108" t="s">
+      <c r="E9" s="103" t="s">
         <v>169</v>
       </c>
-      <c r="F9" s="109"/>
-      <c r="G9" s="109"/>
-      <c r="H9" s="109"/>
-      <c r="I9" s="109"/>
-      <c r="J9" s="110"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="105"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3889,33 +3929,33 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="106" t="s">
+      <c r="E10" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="128" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="111" t="s">
-        <v>216</v>
-      </c>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
+      <c r="E11" s="125" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11" s="126"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="127"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3927,14 +3967,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="106" t="s">
+      <c r="E12" s="108" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="108"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3946,14 +3986,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="108" t="s">
+      <c r="E13" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="110"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -3973,13 +4013,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="104" t="s">
+      <c r="F17" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -3994,13 +4034,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="106" t="s">
-        <v>205</v>
-      </c>
-      <c r="G18" s="106"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
+      <c r="F18" s="108" t="s">
+        <v>204</v>
+      </c>
+      <c r="G18" s="108"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="108"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4015,13 +4055,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="106" t="s">
-        <v>200</v>
-      </c>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
+      <c r="F19" s="108" t="s">
+        <v>199</v>
+      </c>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -4036,13 +4076,13 @@
       <c r="E20" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="106" t="s">
+      <c r="F20" s="108" t="s">
         <v>120</v>
       </c>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -4057,13 +4097,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="106" t="s">
+      <c r="F21" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="108"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4072,19 +4112,19 @@
       <c r="C22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="102" t="s">
+      <c r="D22" s="128" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="103" t="s">
-        <v>217</v>
-      </c>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="103"/>
+      <c r="F22" s="129" t="s">
+        <v>216</v>
+      </c>
+      <c r="G22" s="129"/>
+      <c r="H22" s="129"/>
+      <c r="I22" s="129"/>
+      <c r="J22" s="129"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4093,19 +4133,19 @@
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="102" t="s">
+      <c r="D23" s="128" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="103" t="s">
-        <v>218</v>
-      </c>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="103"/>
-      <c r="J23" s="103"/>
+      <c r="F23" s="129" t="s">
+        <v>217</v>
+      </c>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="129"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4114,19 +4154,19 @@
       <c r="C24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="102" t="s">
+      <c r="D24" s="128" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F24" s="103" t="s">
-        <v>219</v>
-      </c>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="103"/>
+      <c r="F24" s="129" t="s">
+        <v>218</v>
+      </c>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4135,70 +4175,70 @@
       <c r="C25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="102" t="s">
+      <c r="D25" s="128" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F25" s="103" t="s">
+      <c r="F25" s="129" t="s">
+        <v>219</v>
+      </c>
+      <c r="G25" s="129"/>
+      <c r="H25" s="129"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="129"/>
+      <c r="L25" s="130" t="s">
+        <v>222</v>
+      </c>
+      <c r="M25" s="130" t="s">
         <v>220</v>
       </c>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="103"/>
-      <c r="L25" s="6" t="s">
+      <c r="N25" s="130" t="s">
+        <v>223</v>
+      </c>
+      <c r="O25" s="130" t="s">
         <v>225</v>
       </c>
-      <c r="M25" s="6" t="s">
+      <c r="P25" s="130" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B26" s="128" t="s">
+        <v>212</v>
+      </c>
+      <c r="C26" s="128" t="s">
+        <v>213</v>
+      </c>
+      <c r="D26" s="128" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="128" t="s">
+        <v>214</v>
+      </c>
+      <c r="F26" s="129" t="s">
         <v>221</v>
       </c>
-      <c r="N25" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="O25" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="P25" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B26" s="102" t="s">
-        <v>213</v>
-      </c>
-      <c r="C26" s="102" t="s">
-        <v>214</v>
-      </c>
-      <c r="D26" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="102" t="s">
-        <v>215</v>
-      </c>
-      <c r="F26" s="103" t="s">
-        <v>223</v>
-      </c>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="103"/>
+      <c r="G26" s="129"/>
+      <c r="H26" s="129"/>
+      <c r="I26" s="129"/>
+      <c r="J26" s="129"/>
       <c r="L26" s="6">
         <v>800</v>
       </c>
-      <c r="M26" s="130">
+      <c r="M26" s="131">
         <f>L26/4095*128</f>
         <v>25.006105006105006</v>
       </c>
       <c r="N26" s="6">
         <v>20</v>
       </c>
-      <c r="O26" s="131">
+      <c r="O26" s="132">
         <f>N26/16383</f>
         <v>1.2207776353537203E-3</v>
       </c>
-      <c r="P26" s="130">
+      <c r="P26" s="131">
         <f>M26*O26</f>
         <v>3.0526893738759699E-2</v>
       </c>
@@ -4213,7 +4253,7 @@
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B29" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.45">
@@ -4225,16 +4265,16 @@
         <v>47</v>
       </c>
       <c r="E30" s="11"/>
-      <c r="F30" s="105" t="s">
+      <c r="F30" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="105"/>
-      <c r="J30" s="105"/>
-      <c r="K30" s="105"/>
-      <c r="L30" s="105"/>
-      <c r="M30" s="105"/>
+      <c r="G30" s="107"/>
+      <c r="H30" s="107"/>
+      <c r="I30" s="107"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="107"/>
+      <c r="L30" s="107"/>
+      <c r="M30" s="107"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B31" s="8" t="s">
@@ -4481,31 +4521,26 @@
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B44" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B45" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B77" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B109" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="F17:J17"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
     <mergeCell ref="F30:M30"/>
@@ -4520,6 +4555,11 @@
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F26:J26"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="F17:J17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4539,28 +4579,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="109" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="105" t="s">
+      <c r="D2" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="105" t="s">
+      <c r="E2" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105" t="s">
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="115"/>
-      <c r="D3" s="105"/>
+      <c r="B3" s="110"/>
+      <c r="D3" s="107"/>
       <c r="E3" s="7" t="s">
         <v>113</v>
       </c>
@@ -5534,7 +5574,7 @@
         <v>143</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>158</v>
@@ -5601,7 +5641,7 @@
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>140</v>
@@ -5638,7 +5678,7 @@
         <v>157</v>
       </c>
       <c r="K7" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L7" s="56" t="s">
         <v>133</v>
@@ -5661,7 +5701,7 @@
         <v>165</v>
       </c>
       <c r="G8" s="101" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H8" s="31" t="s">
         <v>132</v>
@@ -5675,12 +5715,12 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B11" s="29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -5738,39 +5778,39 @@
   <sheetData>
     <row r="2" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="114" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="122" t="s">
+      <c r="C3" s="117" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="123" t="s">
+      <c r="D3" s="119" t="s">
         <v>173</v>
       </c>
-      <c r="F3" s="119" t="s">
+      <c r="F3" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122" t="s">
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="116" t="s">
+      <c r="K3" s="117"/>
+      <c r="L3" s="117"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="111" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="120"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="124"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="120"/>
       <c r="F4" s="61" t="s">
         <v>113</v>
       </c>
@@ -5795,12 +5835,12 @@
       <c r="M4" s="73" t="s">
         <v>116</v>
       </c>
-      <c r="N4" s="117"/>
+      <c r="N4" s="112"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="127"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="129"/>
+      <c r="B5" s="116"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="121"/>
       <c r="F5" s="71">
         <v>1</v>
       </c>
@@ -5832,7 +5872,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="118"/>
+      <c r="N5" s="113"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="67">
@@ -6216,39 +6256,39 @@
     </row>
     <row r="18" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="114" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="122" t="s">
+      <c r="C19" s="117" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="123" t="s">
+      <c r="D19" s="119" t="s">
         <v>173</v>
       </c>
-      <c r="F19" s="119" t="s">
+      <c r="F19" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="G19" s="122"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="122"/>
-      <c r="J19" s="122" t="s">
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="K19" s="122"/>
-      <c r="L19" s="122"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="116" t="s">
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="122"/>
+      <c r="N19" s="111" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="120"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="124"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="120"/>
       <c r="F20" s="61" t="s">
         <v>113</v>
       </c>
@@ -6273,12 +6313,12 @@
       <c r="M20" s="73" t="s">
         <v>116</v>
       </c>
-      <c r="N20" s="117"/>
+      <c r="N20" s="112"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="121"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="125"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="124"/>
       <c r="F21" s="91">
         <v>12</v>
       </c>
@@ -6310,7 +6350,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="118"/>
+      <c r="N21" s="113"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="86">
@@ -6385,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="90" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.45">
@@ -6423,7 +6463,7 @@
         <v>25</v>
       </c>
       <c r="N24" s="90" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.45">
@@ -6461,7 +6501,7 @@
         <v>25</v>
       </c>
       <c r="N25" s="90" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.45">
@@ -6499,7 +6539,7 @@
         <v>25</v>
       </c>
       <c r="N26" s="90" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.45">
@@ -6537,7 +6577,7 @@
         <v>25</v>
       </c>
       <c r="N27" s="90" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.45">
@@ -6575,7 +6615,7 @@
         <v>25</v>
       </c>
       <c r="N28" s="90" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.45">
@@ -6613,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="90" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.45">
@@ -6651,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="90" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.45">
@@ -6689,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="90" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.45">
@@ -6727,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="90" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.45">
@@ -6765,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="90" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -6803,23 +6843,23 @@
         <v>0</v>
       </c>
       <c r="N34" s="100" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="J19:M19"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
